--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E82E84A-214A-4862-A513-2B85E24FC81B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ABFC026-E085-437B-859F-0993365537B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3148" uniqueCount="1344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="1349">
   <si>
     <t>旧规格</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -2828,10 +2828,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>NF.SC4643VB-Q-DE-4643</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SC69401DC-Q-HD-4XCR-69401</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4434,6 +4430,29 @@
   </si>
   <si>
     <t>SC60228DC-DC-00AR-NM</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643VB-P-Q-DF-40AK-4643</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643VB-P-Q-DF-06AK-4643</t>
+  </si>
+  <si>
+    <t>NF.SC4643VB-Q-DF-4643</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9D03F</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SC4643VB-Q-DF-40CK-4643</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>STC9D03F</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -4622,7 +4641,197 @@
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="943">
+  <dxfs count="962">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -14447,7 +14656,7 @@
         <v>25</v>
       </c>
       <c r="G2" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H2" t="s">
         <v>65</v>
@@ -14485,7 +14694,7 @@
         <v>29</v>
       </c>
       <c r="G3" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H3" t="s">
         <v>65</v>
@@ -14523,7 +14732,7 @@
         <v>34</v>
       </c>
       <c r="G4" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H4" t="s">
         <v>65</v>
@@ -14537,22 +14746,22 @@
         <v>60</v>
       </c>
       <c r="E5" t="s">
+        <v>1269</v>
+      </c>
+      <c r="F5" t="s">
         <v>1270</v>
       </c>
-      <c r="F5" t="s">
-        <v>1271</v>
-      </c>
       <c r="G5" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H5" t="s">
         <v>65</v>
       </c>
       <c r="I5" s="10" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J5" t="s">
-        <v>1272</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="6" spans="1:23">
@@ -14566,7 +14775,7 @@
         <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H6" t="s">
         <v>578</v>
@@ -14604,10 +14813,10 @@
         <v>136</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="G7" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H7" t="s">
         <v>65</v>
@@ -14616,7 +14825,7 @@
         <v>601</v>
       </c>
       <c r="J7" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="8" spans="1:23">
@@ -14627,10 +14836,10 @@
         <v>136</v>
       </c>
       <c r="F8" t="s">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="G8" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H8" t="s">
         <v>65</v>
@@ -14639,7 +14848,7 @@
         <v>601</v>
       </c>
       <c r="J8" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="9" spans="1:23">
@@ -14650,10 +14859,10 @@
         <v>136</v>
       </c>
       <c r="F9" t="s">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="G9" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H9" t="s">
         <v>65</v>
@@ -14662,7 +14871,7 @@
         <v>601</v>
       </c>
       <c r="J9" t="s">
-        <v>1167</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="10" spans="1:23">
@@ -14685,7 +14894,7 @@
         <v>41</v>
       </c>
       <c r="G10" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H10" t="s">
         <v>578</v>
@@ -14702,13 +14911,13 @@
         <v>51</v>
       </c>
       <c r="F11" s="10" t="s">
-        <v>1257</v>
+        <v>1256</v>
       </c>
       <c r="G11" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H11" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I11" t="s">
         <v>595</v>
@@ -14720,7 +14929,7 @@
         <v>51</v>
       </c>
       <c r="N11" t="s">
-        <v>1105</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="12" spans="1:23">
@@ -14743,10 +14952,10 @@
         <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H12" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="I12" t="s">
         <v>595</v>
@@ -14778,13 +14987,13 @@
         <v>47</v>
       </c>
       <c r="F13" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G13" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H13" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I13" t="s">
         <v>598</v>
@@ -14814,7 +15023,7 @@
         <v>47</v>
       </c>
       <c r="T13" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="U13" s="8" t="s">
         <v>43</v>
@@ -14843,10 +15052,10 @@
         <v>57</v>
       </c>
       <c r="F14" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="G14" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H14" t="s">
         <v>813</v>
@@ -14893,7 +15102,7 @@
         <v>64</v>
       </c>
       <c r="G15" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H15" t="s">
         <v>65</v>
@@ -14913,19 +15122,19 @@
         <v>821</v>
       </c>
       <c r="F16" t="s">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="G16" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H16" t="s">
         <v>65</v>
       </c>
       <c r="I16" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="J16" t="s">
-        <v>1291</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="17" spans="1:23">
@@ -14939,7 +15148,7 @@
         <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H17" t="s">
         <v>65</v>
@@ -14956,13 +15165,13 @@
         <v>376</v>
       </c>
       <c r="E18" s="10" t="s">
+        <v>1328</v>
+      </c>
+      <c r="F18" s="10" t="s">
         <v>1329</v>
       </c>
-      <c r="F18" s="10" t="s">
-        <v>1330</v>
-      </c>
       <c r="G18" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H18" t="s">
         <v>65</v>
@@ -14974,10 +15183,10 @@
         <v>376</v>
       </c>
       <c r="M18" t="s">
-        <v>1332</v>
+        <v>1331</v>
       </c>
       <c r="N18" t="s">
-        <v>1331</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="19" spans="1:23">
@@ -14997,13 +15206,13 @@
         <v>73</v>
       </c>
       <c r="F19" t="s">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="G19" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H19" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I19" t="s">
         <v>595</v>
@@ -15024,7 +15233,7 @@
         <v>73</v>
       </c>
       <c r="Q19" t="s">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="R19" t="s">
         <v>46</v>
@@ -15042,7 +15251,7 @@
         <v>73</v>
       </c>
       <c r="W19" t="s">
-        <v>1278</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="20" spans="1:23">
@@ -15062,13 +15271,13 @@
         <v>78</v>
       </c>
       <c r="F20" s="10" t="s">
-        <v>1254</v>
+        <v>1253</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H20" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I20" t="s">
         <v>595</v>
@@ -15092,7 +15301,7 @@
         <v>78</v>
       </c>
       <c r="Q20" t="s">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="R20" t="s">
         <v>46</v>
@@ -15101,7 +15310,7 @@
         <v>78</v>
       </c>
       <c r="T20" t="s">
-        <v>1277</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="21" spans="1:23">
@@ -15121,10 +15330,10 @@
         <v>80</v>
       </c>
       <c r="F21" t="s">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="G21" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H21" t="s">
         <v>65</v>
@@ -15142,7 +15351,7 @@
         <v>80</v>
       </c>
       <c r="N21" t="s">
-        <v>1206</v>
+        <v>1205</v>
       </c>
     </row>
     <row r="22" spans="1:23">
@@ -15165,7 +15374,7 @@
         <v>408</v>
       </c>
       <c r="G22" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H22" t="s">
         <v>579</v>
@@ -15191,13 +15400,13 @@
         <v>84</v>
       </c>
       <c r="F23" t="s">
-        <v>1256</v>
+        <v>1255</v>
       </c>
       <c r="G23" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H23" s="10" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I23" t="s">
         <v>595</v>
@@ -15209,7 +15418,7 @@
         <v>84</v>
       </c>
       <c r="N23" t="s">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="O23" t="s">
         <v>46</v>
@@ -15227,7 +15436,7 @@
         <v>84</v>
       </c>
       <c r="T23" t="s">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="U23" s="8" t="s">
         <v>46</v>
@@ -15247,10 +15456,10 @@
         <v>89</v>
       </c>
       <c r="F24" t="s">
-        <v>1326</v>
+        <v>1325</v>
       </c>
       <c r="G24" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H24" t="s">
         <v>65</v>
@@ -15265,7 +15474,7 @@
         <v>89</v>
       </c>
       <c r="N24" t="s">
-        <v>1325</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="25" spans="1:23">
@@ -15276,10 +15485,10 @@
         <v>73</v>
       </c>
       <c r="F25" s="10" t="s">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="G25" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H25" t="s">
         <v>579</v>
@@ -15294,7 +15503,7 @@
         <v>73</v>
       </c>
       <c r="N25" s="10" t="s">
-        <v>1328</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="26" spans="1:23">
@@ -15317,7 +15526,7 @@
         <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H26" t="s">
         <v>579</v>
@@ -15361,13 +15570,13 @@
         <v>98</v>
       </c>
       <c r="F27" t="s">
-        <v>1203</v>
+        <v>1202</v>
       </c>
       <c r="G27" t="s">
+        <v>1199</v>
+      </c>
+      <c r="H27" t="s">
         <v>1200</v>
-      </c>
-      <c r="H27" t="s">
-        <v>1201</v>
       </c>
       <c r="I27" t="s">
         <v>595</v>
@@ -15411,7 +15620,7 @@
         <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H28" t="s">
         <v>578</v>
@@ -15440,7 +15649,7 @@
         <v>801</v>
       </c>
       <c r="G29" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H29" t="s">
         <v>65</v>
@@ -15481,7 +15690,7 @@
         <v>748</v>
       </c>
       <c r="G30" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H30" t="s">
         <v>65</v>
@@ -15507,10 +15716,10 @@
         <v>632</v>
       </c>
       <c r="F31" t="s">
-        <v>1338</v>
+        <v>1337</v>
       </c>
       <c r="G31" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H31" t="s">
         <v>65</v>
@@ -15536,31 +15745,31 @@
         <v>111</v>
       </c>
       <c r="E32" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="F32" t="s">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="G32" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H32" t="s">
         <v>65</v>
       </c>
       <c r="I32" t="s">
-        <v>1280</v>
+        <v>1279</v>
       </c>
       <c r="J32" t="s">
-        <v>1279</v>
+        <v>1278</v>
       </c>
       <c r="L32" t="s">
         <v>111</v>
       </c>
       <c r="M32" t="s">
-        <v>1162</v>
+        <v>1161</v>
       </c>
       <c r="N32" t="s">
-        <v>1161</v>
+        <v>1160</v>
       </c>
     </row>
     <row r="33" spans="1:17">
@@ -15583,10 +15792,10 @@
         <v>114</v>
       </c>
       <c r="G33" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H33" t="s">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="I33" t="s">
         <v>603</v>
@@ -15612,7 +15821,7 @@
         <v>118</v>
       </c>
       <c r="G34" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H34" t="s">
         <v>578</v>
@@ -15641,7 +15850,7 @@
         <v>123</v>
       </c>
       <c r="G35" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H35" t="s">
         <v>65</v>
@@ -15673,7 +15882,7 @@
         <v>128</v>
       </c>
       <c r="G36" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H36" t="s">
         <v>579</v>
@@ -15697,7 +15906,7 @@
         <v>127</v>
       </c>
       <c r="Q36" t="s">
-        <v>1168</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="37" spans="1:17">
@@ -15720,10 +15929,10 @@
         <v>807</v>
       </c>
       <c r="G37" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H37" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="I37" t="s">
         <v>595</v>
@@ -15761,7 +15970,7 @@
         <v>137</v>
       </c>
       <c r="G38" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H38" t="s">
         <v>65</v>
@@ -15790,7 +15999,7 @@
         <v>139</v>
       </c>
       <c r="G39" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H39" t="s">
         <v>65</v>
@@ -15822,7 +16031,7 @@
         <v>141</v>
       </c>
       <c r="G40" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H40" t="s">
         <v>65</v>
@@ -15840,7 +16049,7 @@
         <v>136</v>
       </c>
       <c r="N40" t="s">
-        <v>1333</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="41" spans="1:17">
@@ -15863,7 +16072,7 @@
         <v>143</v>
       </c>
       <c r="G41" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H41" t="s">
         <v>65</v>
@@ -15895,7 +16104,7 @@
         <v>584</v>
       </c>
       <c r="G42" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H42" t="s">
         <v>65</v>
@@ -15927,7 +16136,7 @@
         <v>147</v>
       </c>
       <c r="G43" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H43" t="s">
         <v>65</v>
@@ -15956,7 +16165,7 @@
         <v>152</v>
       </c>
       <c r="G44" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H44" t="s">
         <v>65</v>
@@ -15985,7 +16194,7 @@
         <v>155</v>
       </c>
       <c r="G45" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H45" t="s">
         <v>65</v>
@@ -16014,7 +16223,7 @@
         <v>749</v>
       </c>
       <c r="G46" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H46" t="s">
         <v>65</v>
@@ -16055,7 +16264,7 @@
         <v>163</v>
       </c>
       <c r="G47" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H47" t="s">
         <v>65</v>
@@ -16084,7 +16293,7 @@
         <v>169</v>
       </c>
       <c r="G48" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H48" t="s">
         <v>65</v>
@@ -16134,7 +16343,7 @@
         <v>173</v>
       </c>
       <c r="G49" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H49" t="s">
         <v>65</v>
@@ -16166,7 +16375,7 @@
         <v>580</v>
       </c>
       <c r="G50" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H50" t="s">
         <v>65</v>
@@ -16216,7 +16425,7 @@
         <v>158</v>
       </c>
       <c r="G51" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H51" t="s">
         <v>65</v>
@@ -16248,7 +16457,7 @@
         <v>182</v>
       </c>
       <c r="G52" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H52" t="s">
         <v>65</v>
@@ -16268,7 +16477,7 @@
         <v>164</v>
       </c>
       <c r="C53" t="s">
-        <v>1275</v>
+        <v>1274</v>
       </c>
       <c r="D53" t="s">
         <v>156</v>
@@ -16280,7 +16489,7 @@
         <v>185</v>
       </c>
       <c r="G53" t="s">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="H53" t="s">
         <v>65</v>
@@ -16309,7 +16518,7 @@
         <v>184</v>
       </c>
       <c r="G54" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H54" t="s">
         <v>65</v>
@@ -16359,7 +16568,7 @@
         <v>791</v>
       </c>
       <c r="G55" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H55" t="s">
         <v>65</v>
@@ -16400,7 +16609,7 @@
         <v>190</v>
       </c>
       <c r="G56" t="s">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="H56" t="s">
         <v>65</v>
@@ -16420,7 +16629,7 @@
         <v>194</v>
       </c>
       <c r="G57" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H57" t="s">
         <v>65</v>
@@ -16461,7 +16670,7 @@
         <v>197</v>
       </c>
       <c r="G58" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H58" t="s">
         <v>65</v>
@@ -16511,7 +16720,7 @@
         <v>203</v>
       </c>
       <c r="G59" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H59" t="s">
         <v>65</v>
@@ -16540,7 +16749,7 @@
         <v>751</v>
       </c>
       <c r="G60" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H60" t="s">
         <v>65</v>
@@ -16572,7 +16781,7 @@
         <v>207</v>
       </c>
       <c r="G61" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H61" t="s">
         <v>579</v>
@@ -16601,7 +16810,7 @@
         <v>753</v>
       </c>
       <c r="G62" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H62" t="s">
         <v>578</v>
@@ -16630,7 +16839,7 @@
         <v>210</v>
       </c>
       <c r="G63" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H63" t="s">
         <v>65</v>
@@ -16662,7 +16871,7 @@
         <v>218</v>
       </c>
       <c r="G64" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H64" t="s">
         <v>579</v>
@@ -16700,7 +16909,7 @@
         <v>223</v>
       </c>
       <c r="G65" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H65" t="s">
         <v>65</v>
@@ -16729,7 +16938,7 @@
         <v>754</v>
       </c>
       <c r="G66" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H66" t="s">
         <v>65</v>
@@ -16761,7 +16970,7 @@
         <v>229</v>
       </c>
       <c r="G67" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H67" t="s">
         <v>578</v>
@@ -16776,10 +16985,10 @@
         <v>225</v>
       </c>
       <c r="M67" t="s">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="N67" t="s">
-        <v>1123</v>
+        <v>1122</v>
       </c>
     </row>
     <row r="68" spans="1:23">
@@ -16802,7 +17011,7 @@
         <v>251</v>
       </c>
       <c r="G68" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H68" t="s">
         <v>65</v>
@@ -16814,34 +17023,34 @@
         <v>233</v>
       </c>
       <c r="L68" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="M68" t="s">
         <v>228</v>
       </c>
       <c r="N68" t="s">
-        <v>1295</v>
+        <v>1294</v>
       </c>
       <c r="O68" t="s">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="P68" t="s">
         <v>228</v>
       </c>
       <c r="Q68" t="s">
+        <v>1295</v>
+      </c>
+      <c r="R68" t="s">
         <v>1296</v>
-      </c>
-      <c r="R68" t="s">
-        <v>1297</v>
       </c>
       <c r="S68" t="s">
         <v>228</v>
       </c>
       <c r="T68" t="s">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="U68" t="s">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="V68" t="s">
         <v>228</v>
@@ -16861,7 +17070,7 @@
         <v>241</v>
       </c>
       <c r="G69" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H69" t="s">
         <v>578</v>
@@ -16884,7 +17093,7 @@
         <v>755</v>
       </c>
       <c r="G70" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H70" t="s">
         <v>578</v>
@@ -16907,7 +17116,7 @@
         <v>236</v>
       </c>
       <c r="G71" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H71" t="s">
         <v>65</v>
@@ -16930,7 +17139,7 @@
         <v>239</v>
       </c>
       <c r="G72" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H72" t="s">
         <v>578</v>
@@ -16953,7 +17162,7 @@
         <v>244</v>
       </c>
       <c r="G73" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H73" t="s">
         <v>578</v>
@@ -16976,7 +17185,7 @@
         <v>246</v>
       </c>
       <c r="G74" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H74" t="s">
         <v>578</v>
@@ -16999,7 +17208,7 @@
         <v>247</v>
       </c>
       <c r="G75" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H75" t="s">
         <v>578</v>
@@ -17017,7 +17226,7 @@
         <v>245</v>
       </c>
       <c r="N75" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="O75" t="s">
         <v>242</v>
@@ -17026,7 +17235,7 @@
         <v>245</v>
       </c>
       <c r="Q75" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="76" spans="1:23">
@@ -17040,7 +17249,7 @@
         <v>248</v>
       </c>
       <c r="G76" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H76" t="s">
         <v>578</v>
@@ -17063,7 +17272,7 @@
         <v>249</v>
       </c>
       <c r="G77" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H77" t="s">
         <v>578</v>
@@ -17086,7 +17295,7 @@
         <v>250</v>
       </c>
       <c r="G78" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H78" t="s">
         <v>578</v>
@@ -17109,7 +17318,7 @@
         <v>252</v>
       </c>
       <c r="G79" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H79" t="s">
         <v>578</v>
@@ -17132,7 +17341,7 @@
         <v>697</v>
       </c>
       <c r="G80" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H80" t="s">
         <v>578</v>
@@ -17164,7 +17373,7 @@
         <v>257</v>
       </c>
       <c r="G81" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H81" t="s">
         <v>65</v>
@@ -17193,7 +17402,7 @@
         <v>263</v>
       </c>
       <c r="G82" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H82" t="s">
         <v>65</v>
@@ -17225,7 +17434,7 @@
         <v>270</v>
       </c>
       <c r="G83" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H83" t="s">
         <v>65</v>
@@ -17257,7 +17466,7 @@
         <v>262</v>
       </c>
       <c r="G84" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H84" t="s">
         <v>65</v>
@@ -17289,7 +17498,7 @@
         <v>264</v>
       </c>
       <c r="G85" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H85" t="s">
         <v>65</v>
@@ -17321,7 +17530,7 @@
         <v>266</v>
       </c>
       <c r="G86" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H86" t="s">
         <v>65</v>
@@ -17344,7 +17553,7 @@
         <v>616</v>
       </c>
       <c r="G87" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H87" t="s">
         <v>65</v>
@@ -17376,7 +17585,7 @@
         <v>280</v>
       </c>
       <c r="G88" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H88" t="s">
         <v>578</v>
@@ -17405,7 +17614,7 @@
         <v>757</v>
       </c>
       <c r="G89" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H89" t="s">
         <v>65</v>
@@ -17425,7 +17634,7 @@
         <v>581</v>
       </c>
       <c r="G90" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H90" t="s">
         <v>578</v>
@@ -17463,7 +17672,7 @@
         <v>287</v>
       </c>
       <c r="G91" t="s">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="H91" t="s">
         <v>578</v>
@@ -17492,7 +17701,7 @@
         <v>288</v>
       </c>
       <c r="G92" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H92" t="s">
         <v>578</v>
@@ -17512,7 +17721,7 @@
         <v>785</v>
       </c>
       <c r="G93" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H93" t="s">
         <v>578</v>
@@ -17527,7 +17736,7 @@
         <v>283</v>
       </c>
       <c r="N93" t="s">
-        <v>1125</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="94" spans="1:17">
@@ -17550,7 +17759,7 @@
         <v>292</v>
       </c>
       <c r="G94" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H94" t="s">
         <v>65</v>
@@ -17570,16 +17779,16 @@
         <v>293</v>
       </c>
       <c r="D95" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="E95" t="s">
         <v>291</v>
       </c>
       <c r="F95" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G95" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H95" t="s">
         <v>65</v>
@@ -17629,16 +17838,16 @@
         <v>298</v>
       </c>
       <c r="G96" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H96" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I96" t="s">
         <v>597</v>
       </c>
       <c r="J96" t="s">
-        <v>1276</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="97" spans="1:20">
@@ -17661,7 +17870,7 @@
         <v>303</v>
       </c>
       <c r="G97" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H97" t="s">
         <v>579</v>
@@ -17690,7 +17899,7 @@
         <v>623</v>
       </c>
       <c r="G98" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H98" t="s">
         <v>579</v>
@@ -17716,13 +17925,13 @@
         <v>310</v>
       </c>
       <c r="F99" t="s">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="G99" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H99" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="I99" t="s">
         <v>595</v>
@@ -17734,7 +17943,7 @@
         <v>310</v>
       </c>
       <c r="N99" t="s">
-        <v>1227</v>
+        <v>1226</v>
       </c>
     </row>
     <row r="100" spans="1:20">
@@ -17757,7 +17966,7 @@
         <v>312</v>
       </c>
       <c r="G100" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H100" t="s">
         <v>65</v>
@@ -17771,16 +17980,16 @@
         <v>313</v>
       </c>
       <c r="E101" t="s">
+        <v>1235</v>
+      </c>
+      <c r="F101" t="s">
         <v>1236</v>
       </c>
-      <c r="F101" t="s">
-        <v>1237</v>
-      </c>
       <c r="G101" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H101" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I101" t="s">
         <v>595</v>
@@ -17789,10 +17998,10 @@
         <v>313</v>
       </c>
       <c r="M101" t="s">
-        <v>1236</v>
+        <v>1235</v>
       </c>
       <c r="N101" t="s">
-        <v>1238</v>
+        <v>1237</v>
       </c>
     </row>
     <row r="102" spans="1:20">
@@ -17812,13 +18021,13 @@
         <v>316</v>
       </c>
       <c r="F102" t="s">
-        <v>1235</v>
+        <v>1234</v>
       </c>
       <c r="G102" t="s">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="H102" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I102" t="s">
         <v>595</v>
@@ -17862,7 +18071,7 @@
         <v>324</v>
       </c>
       <c r="G103" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H103" t="s">
         <v>65</v>
@@ -17891,13 +18100,13 @@
         <v>325</v>
       </c>
       <c r="F104" t="s">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="G104" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H104" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I104" t="s">
         <v>595</v>
@@ -17927,7 +18136,7 @@
         <v>325</v>
       </c>
       <c r="T104" t="s">
-        <v>1229</v>
+        <v>1228</v>
       </c>
     </row>
     <row r="105" spans="1:20">
@@ -17950,7 +18159,7 @@
         <v>330</v>
       </c>
       <c r="G105" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H105" t="s">
         <v>65</v>
@@ -17982,7 +18191,7 @@
         <v>760</v>
       </c>
       <c r="G106" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H106" t="s">
         <v>579</v>
@@ -18011,7 +18220,7 @@
         <v>337</v>
       </c>
       <c r="G107" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H107" t="s">
         <v>65</v>
@@ -18043,7 +18252,7 @@
         <v>341</v>
       </c>
       <c r="G108" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H108" t="s">
         <v>65</v>
@@ -18072,13 +18281,13 @@
         <v>344</v>
       </c>
       <c r="F109" t="s">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="G109" s="10" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H109" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I109" t="s">
         <v>595</v>
@@ -18113,7 +18322,7 @@
         <v>347</v>
       </c>
       <c r="G110" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H110" t="s">
         <v>65</v>
@@ -18145,7 +18354,7 @@
         <v>351</v>
       </c>
       <c r="G111" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H111" t="s">
         <v>65</v>
@@ -18174,10 +18383,10 @@
         <v>356</v>
       </c>
       <c r="G112" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H112" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I112" t="s">
         <v>595</v>
@@ -18212,7 +18421,7 @@
         <v>361</v>
       </c>
       <c r="G113" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H113" t="s">
         <v>65</v>
@@ -18232,7 +18441,7 @@
         <v>362</v>
       </c>
       <c r="G114" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H114" t="s">
         <v>65</v>
@@ -18270,7 +18479,7 @@
         <v>367</v>
       </c>
       <c r="G115" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H115" t="s">
         <v>65</v>
@@ -18296,13 +18505,13 @@
         <v>370</v>
       </c>
       <c r="F116" t="s">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="G116" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H116" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I116" t="s">
         <v>595</v>
@@ -18314,7 +18523,7 @@
         <v>370</v>
       </c>
       <c r="N116" t="s">
-        <v>1268</v>
+        <v>1267</v>
       </c>
     </row>
     <row r="117" spans="1:17">
@@ -18334,13 +18543,13 @@
         <v>374</v>
       </c>
       <c r="F117" t="s">
+        <v>1198</v>
+      </c>
+      <c r="G117" t="s">
         <v>1199</v>
       </c>
-      <c r="G117" t="s">
+      <c r="H117" t="s">
         <v>1200</v>
-      </c>
-      <c r="H117" t="s">
-        <v>1201</v>
       </c>
       <c r="I117" t="s">
         <v>595</v>
@@ -18375,10 +18584,10 @@
         <v>380</v>
       </c>
       <c r="G118" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H118" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="I118" t="s">
         <v>595</v>
@@ -18390,7 +18599,7 @@
         <v>379</v>
       </c>
       <c r="N118" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="119" spans="1:17">
@@ -18401,13 +18610,13 @@
         <v>628</v>
       </c>
       <c r="F119" t="s">
-        <v>1233</v>
+        <v>1232</v>
       </c>
       <c r="G119" t="s">
-        <v>1232</v>
+        <v>1231</v>
       </c>
       <c r="H119" s="10" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I119" t="s">
         <v>595</v>
@@ -18419,7 +18628,7 @@
         <v>628</v>
       </c>
       <c r="N119" t="s">
-        <v>1234</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="120" spans="1:17">
@@ -18430,13 +18639,13 @@
         <v>628</v>
       </c>
       <c r="F120" t="s">
+        <v>1230</v>
+      </c>
+      <c r="G120" t="s">
         <v>1231</v>
       </c>
-      <c r="G120" t="s">
-        <v>1232</v>
-      </c>
       <c r="H120" s="10" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I120" t="s">
         <v>595</v>
@@ -18453,7 +18662,7 @@
         <v>629</v>
       </c>
       <c r="G121" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H121" t="s">
         <v>873</v>
@@ -18473,16 +18682,16 @@
         <v>386</v>
       </c>
       <c r="G122" t="s">
+        <v>1257</v>
+      </c>
+      <c r="H122" t="s">
         <v>1258</v>
-      </c>
-      <c r="H122" t="s">
-        <v>1259</v>
       </c>
       <c r="I122" t="s">
         <v>595</v>
       </c>
       <c r="J122" t="s">
-        <v>1273</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="123" spans="1:17">
@@ -18496,7 +18705,7 @@
         <v>741</v>
       </c>
       <c r="G123" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H123" t="s">
         <v>579</v>
@@ -18525,7 +18734,7 @@
         <v>384</v>
       </c>
       <c r="G124" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H124" t="s">
         <v>579</v>
@@ -18540,7 +18749,7 @@
         <v>383</v>
       </c>
       <c r="N124" t="s">
-        <v>1239</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="125" spans="1:17">
@@ -18560,13 +18769,13 @@
         <v>333</v>
       </c>
       <c r="F125" t="s">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="G125" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H125" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I125" t="s">
         <v>595</v>
@@ -18578,7 +18787,7 @@
         <v>333</v>
       </c>
       <c r="N125" t="s">
-        <v>1241</v>
+        <v>1240</v>
       </c>
     </row>
     <row r="126" spans="1:17">
@@ -18598,13 +18807,13 @@
         <v>774</v>
       </c>
       <c r="F126" t="s">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="G126" s="10" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H126" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I126" t="s">
         <v>595</v>
@@ -18616,7 +18825,7 @@
         <v>774</v>
       </c>
       <c r="N126" t="s">
-        <v>1244</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="127" spans="1:17">
@@ -18636,13 +18845,13 @@
         <v>392</v>
       </c>
       <c r="F127" s="10" t="s">
-        <v>1269</v>
+        <v>1268</v>
       </c>
       <c r="G127" s="10" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H127" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I127" t="s">
         <v>595</v>
@@ -18674,13 +18883,13 @@
         <v>73</v>
       </c>
       <c r="F128" t="s">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="G128" t="s">
-        <v>1230</v>
+        <v>1229</v>
       </c>
       <c r="H128" t="s">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="I128" t="s">
         <v>595</v>
@@ -18701,7 +18910,7 @@
         <v>73</v>
       </c>
       <c r="Q128" t="s">
-        <v>1263</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="129" spans="1:23">
@@ -18724,7 +18933,7 @@
         <v>402</v>
       </c>
       <c r="G129" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H129" t="s">
         <v>65</v>
@@ -18750,13 +18959,13 @@
         <v>396</v>
       </c>
       <c r="F130" s="8" t="s">
-        <v>1247</v>
+        <v>1246</v>
       </c>
       <c r="G130" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H130" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I130" t="s">
         <v>595</v>
@@ -18768,7 +18977,7 @@
         <v>396</v>
       </c>
       <c r="N130" s="8" t="s">
-        <v>1248</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="131" spans="1:23">
@@ -18779,13 +18988,13 @@
         <v>405</v>
       </c>
       <c r="F131" t="s">
-        <v>1252</v>
+        <v>1251</v>
       </c>
       <c r="G131" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H131" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I131" t="s">
         <v>595</v>
@@ -18806,7 +19015,7 @@
         <v>405</v>
       </c>
       <c r="Q131" t="s">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="132" spans="1:23">
@@ -18829,7 +19038,7 @@
         <v>412</v>
       </c>
       <c r="G132" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H132" t="s">
         <v>579</v>
@@ -18867,7 +19076,7 @@
         <v>417</v>
       </c>
       <c r="G133" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H133" t="s">
         <v>579</v>
@@ -18887,7 +19096,7 @@
         <v>419</v>
       </c>
       <c r="G134" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H134" t="s">
         <v>579</v>
@@ -18922,10 +19131,10 @@
         <v>423</v>
       </c>
       <c r="F135" t="s">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="G135" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H135" t="s">
         <v>65</v>
@@ -18943,7 +19152,7 @@
         <v>423</v>
       </c>
       <c r="N135" t="s">
-        <v>1207</v>
+        <v>1206</v>
       </c>
       <c r="O135" t="s">
         <v>46</v>
@@ -18961,7 +19170,7 @@
         <v>423</v>
       </c>
       <c r="T135" s="11" t="s">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="U135" t="s">
         <v>420</v>
@@ -18970,7 +19179,7 @@
         <v>423</v>
       </c>
       <c r="W135" t="s">
-        <v>1261</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="136" spans="1:23">
@@ -18984,7 +19193,7 @@
         <v>430</v>
       </c>
       <c r="G136" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H136" t="s">
         <v>813</v>
@@ -19005,7 +19214,7 @@
         <v>427</v>
       </c>
       <c r="D137" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="E137" t="s">
         <v>428</v>
@@ -19014,16 +19223,16 @@
         <v>429</v>
       </c>
       <c r="G137" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H137" t="s">
-        <v>1287</v>
+        <v>1286</v>
       </c>
       <c r="I137" t="s">
         <v>611</v>
       </c>
       <c r="J137" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
     </row>
     <row r="138" spans="1:23">
@@ -19037,7 +19246,7 @@
         <v>762</v>
       </c>
       <c r="G138" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H138" t="s">
         <v>747</v>
@@ -19046,7 +19255,7 @@
         <v>611</v>
       </c>
       <c r="J138" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="L138" t="s">
         <v>425</v>
@@ -19078,7 +19287,7 @@
         <v>667</v>
       </c>
       <c r="G139" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H139" t="s">
         <v>579</v>
@@ -19119,7 +19328,7 @@
         <v>597</v>
       </c>
       <c r="J140" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
       <c r="L140" t="s">
         <v>436</v>
@@ -19151,7 +19360,7 @@
         <v>597</v>
       </c>
       <c r="J141" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="142" spans="1:23">
@@ -19174,7 +19383,7 @@
         <v>597</v>
       </c>
       <c r="J142" t="s">
-        <v>1093</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="143" spans="1:23">
@@ -19197,7 +19406,7 @@
         <v>445</v>
       </c>
       <c r="G143" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H143" t="s">
         <v>65</v>
@@ -19226,13 +19435,13 @@
         <v>451</v>
       </c>
       <c r="F144" t="s">
+        <v>1281</v>
+      </c>
+      <c r="G144" t="s">
         <v>1282</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>1283</v>
-      </c>
-      <c r="H144" t="s">
-        <v>1284</v>
       </c>
       <c r="I144" t="s">
         <v>611</v>
@@ -19244,7 +19453,7 @@
         <v>451</v>
       </c>
       <c r="N144" t="s">
-        <v>1310</v>
+        <v>1309</v>
       </c>
     </row>
     <row r="145" spans="1:14">
@@ -19267,10 +19476,10 @@
         <v>452</v>
       </c>
       <c r="G145" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H145" t="s">
-        <v>1285</v>
+        <v>1284</v>
       </c>
       <c r="I145" t="s">
         <v>611</v>
@@ -19290,7 +19499,7 @@
         <v>455</v>
       </c>
       <c r="G146" t="s">
-        <v>1283</v>
+        <v>1282</v>
       </c>
       <c r="H146" t="s">
         <v>813</v>
@@ -19299,13 +19508,13 @@
         <v>611</v>
       </c>
       <c r="L146" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="M146" t="s">
         <v>453</v>
       </c>
       <c r="N146" t="s">
-        <v>1309</v>
+        <v>1308</v>
       </c>
     </row>
     <row r="147" spans="1:14">
@@ -19316,10 +19525,10 @@
         <v>63</v>
       </c>
       <c r="F147" s="10" t="s">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="G147" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H147" t="s">
         <v>813</v>
@@ -19328,7 +19537,7 @@
         <v>599</v>
       </c>
       <c r="J147" t="s">
-        <v>1321</v>
+        <v>1320</v>
       </c>
     </row>
     <row r="148" spans="1:14">
@@ -19339,10 +19548,10 @@
         <v>172</v>
       </c>
       <c r="F148" t="s">
-        <v>1322</v>
+        <v>1321</v>
       </c>
       <c r="G148" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H148" t="s">
         <v>813</v>
@@ -19354,13 +19563,13 @@
         <v>174</v>
       </c>
       <c r="L148" s="10" t="s">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="M148" t="s">
         <v>172</v>
       </c>
       <c r="N148" t="s">
-        <v>1324</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="149" spans="1:14">
@@ -19383,7 +19592,7 @@
         <v>454</v>
       </c>
       <c r="G149" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H149" t="s">
         <v>875</v>
@@ -19415,7 +19624,7 @@
         <v>864</v>
       </c>
       <c r="G150" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H150" t="s">
         <v>869</v>
@@ -19433,7 +19642,7 @@
         <v>464</v>
       </c>
       <c r="N150" t="s">
-        <v>1214</v>
+        <v>1213</v>
       </c>
     </row>
     <row r="151" spans="1:14">
@@ -19456,7 +19665,7 @@
         <v>865</v>
       </c>
       <c r="G151" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H151" t="s">
         <v>869</v>
@@ -19474,7 +19683,7 @@
         <v>467</v>
       </c>
       <c r="N151" t="s">
-        <v>1215</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="152" spans="1:14">
@@ -19497,7 +19706,7 @@
         <v>866</v>
       </c>
       <c r="G152" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H152" t="s">
         <v>869</v>
@@ -19515,7 +19724,7 @@
         <v>470</v>
       </c>
       <c r="N152" t="s">
-        <v>1216</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="153" spans="1:14">
@@ -19538,7 +19747,7 @@
         <v>867</v>
       </c>
       <c r="G153" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H153" t="s">
         <v>869</v>
@@ -19556,7 +19765,7 @@
         <v>671</v>
       </c>
       <c r="N153" t="s">
-        <v>1217</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="154" spans="1:14">
@@ -19579,7 +19788,7 @@
         <v>872</v>
       </c>
       <c r="G154" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H154" t="s">
         <v>873</v>
@@ -19588,7 +19797,7 @@
         <v>870</v>
       </c>
       <c r="J154" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="155" spans="1:14">
@@ -19611,7 +19820,7 @@
         <v>868</v>
       </c>
       <c r="G155" t="s">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="H155" t="s">
         <v>869</v>
@@ -19629,7 +19838,7 @@
         <v>474</v>
       </c>
       <c r="N155" t="s">
-        <v>1213</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="156" spans="1:14">
@@ -19670,7 +19879,7 @@
         <v>475</v>
       </c>
       <c r="N156" t="s">
-        <v>1218</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="157" spans="1:14">
@@ -19693,7 +19902,7 @@
         <v>876</v>
       </c>
       <c r="G157" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H157" t="s">
         <v>877</v>
@@ -19725,7 +19934,7 @@
         <v>880</v>
       </c>
       <c r="G158" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H158" t="s">
         <v>881</v>
@@ -19763,7 +19972,7 @@
         <v>883</v>
       </c>
       <c r="G159" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H159" t="s">
         <v>881</v>
@@ -19801,7 +20010,7 @@
         <v>884</v>
       </c>
       <c r="G160" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H160" t="s">
         <v>877</v>
@@ -19822,7 +20031,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="161" spans="1:20">
+    <row r="161" spans="1:23">
       <c r="A161" t="s">
         <v>488</v>
       </c>
@@ -19842,7 +20051,7 @@
         <v>886</v>
       </c>
       <c r="G161" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H161" t="s">
         <v>877</v>
@@ -19863,7 +20072,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="162" spans="1:20">
+    <row r="162" spans="1:23">
       <c r="A162" t="s">
         <v>492</v>
       </c>
@@ -19883,7 +20092,7 @@
         <v>888</v>
       </c>
       <c r="G162" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H162" t="s">
         <v>881</v>
@@ -19901,7 +20110,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="163" spans="1:20">
+    <row r="163" spans="1:23">
       <c r="A163" t="s">
         <v>492</v>
       </c>
@@ -19921,7 +20130,7 @@
         <v>889</v>
       </c>
       <c r="G163" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H163" t="s">
         <v>881</v>
@@ -19939,10 +20148,10 @@
         <v>498</v>
       </c>
       <c r="N163" t="s">
-        <v>1092</v>
-      </c>
-    </row>
-    <row r="164" spans="1:20">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23">
       <c r="A164" t="s">
         <v>492</v>
       </c>
@@ -19962,7 +20171,7 @@
         <v>890</v>
       </c>
       <c r="G164" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H164" t="s">
         <v>873</v>
@@ -19971,7 +20180,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="165" spans="1:20">
+    <row r="165" spans="1:23">
       <c r="A165" t="s">
         <v>492</v>
       </c>
@@ -19991,7 +20200,7 @@
         <v>892</v>
       </c>
       <c r="G165" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H165" t="s">
         <v>881</v>
@@ -20000,7 +20209,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="166" spans="1:20">
+    <row r="166" spans="1:23">
       <c r="D166" t="s">
         <v>492</v>
       </c>
@@ -20011,7 +20220,7 @@
         <v>893</v>
       </c>
       <c r="G166" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H166" t="s">
         <v>877</v>
@@ -20023,7 +20232,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="167" spans="1:20">
+    <row r="167" spans="1:23">
       <c r="A167" t="s">
         <v>492</v>
       </c>
@@ -20043,7 +20252,7 @@
         <v>896</v>
       </c>
       <c r="G167" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H167" t="s">
         <v>877</v>
@@ -20055,7 +20264,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="168" spans="1:20">
+    <row r="168" spans="1:23">
       <c r="A168" t="s">
         <v>492</v>
       </c>
@@ -20075,7 +20284,7 @@
         <v>897</v>
       </c>
       <c r="G168" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H168" t="s">
         <v>877</v>
@@ -20087,7 +20296,7 @@
         <v>899</v>
       </c>
     </row>
-    <row r="169" spans="1:20">
+    <row r="169" spans="1:23">
       <c r="A169" t="s">
         <v>492</v>
       </c>
@@ -20098,16 +20307,16 @@
         <v>512</v>
       </c>
       <c r="D169" t="s">
-        <v>492</v>
+        <v>1348</v>
       </c>
       <c r="E169" t="s">
         <v>513</v>
       </c>
       <c r="F169" t="s">
-        <v>900</v>
+        <v>1343</v>
       </c>
       <c r="G169" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H169" t="s">
         <v>877</v>
@@ -20136,8 +20345,26 @@
       <c r="Q169" t="s">
         <v>514</v>
       </c>
-    </row>
-    <row r="170" spans="1:20">
+      <c r="R169" t="s">
+        <v>492</v>
+      </c>
+      <c r="S169" t="s">
+        <v>513</v>
+      </c>
+      <c r="T169" t="s">
+        <v>900</v>
+      </c>
+      <c r="U169" t="s">
+        <v>492</v>
+      </c>
+      <c r="V169" t="s">
+        <v>513</v>
+      </c>
+      <c r="W169" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23">
       <c r="A170" t="s">
         <v>492</v>
       </c>
@@ -20157,7 +20384,7 @@
         <v>902</v>
       </c>
       <c r="G170" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H170" t="s">
         <v>877</v>
@@ -20169,7 +20396,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="171" spans="1:20">
+    <row r="171" spans="1:23">
       <c r="A171" t="s">
         <v>492</v>
       </c>
@@ -20189,7 +20416,7 @@
         <v>904</v>
       </c>
       <c r="G171" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H171" t="s">
         <v>877</v>
@@ -20201,16 +20428,16 @@
         <v>903</v>
       </c>
       <c r="L171" t="s">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="M171" t="s">
         <v>516</v>
       </c>
       <c r="N171" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="172" spans="1:20">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23">
       <c r="A172" t="s">
         <v>492</v>
       </c>
@@ -20227,10 +20454,10 @@
         <v>515</v>
       </c>
       <c r="F172" t="s">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="G172" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H172" t="s">
         <v>877</v>
@@ -20239,7 +20466,7 @@
         <v>898</v>
       </c>
       <c r="J172" t="s">
-        <v>906</v>
+        <v>1345</v>
       </c>
       <c r="L172" t="s">
         <v>492</v>
@@ -20266,10 +20493,19 @@
         <v>515</v>
       </c>
       <c r="T172" t="s">
-        <v>1341</v>
-      </c>
-    </row>
-    <row r="173" spans="1:20">
+        <v>1340</v>
+      </c>
+      <c r="U172" t="s">
+        <v>1346</v>
+      </c>
+      <c r="V172" t="s">
+        <v>515</v>
+      </c>
+      <c r="W172" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23">
       <c r="A173" t="s">
         <v>624</v>
       </c>
@@ -20286,10 +20522,10 @@
         <v>627</v>
       </c>
       <c r="F173" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G173" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H173" t="s">
         <v>873</v>
@@ -20298,7 +20534,7 @@
         <v>882</v>
       </c>
       <c r="J173" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="L173" t="s">
         <v>624</v>
@@ -20319,7 +20555,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="174" spans="1:20">
+    <row r="174" spans="1:23">
       <c r="A174" t="s">
         <v>533</v>
       </c>
@@ -20336,19 +20572,19 @@
         <v>540</v>
       </c>
       <c r="F174" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G174" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H174" t="s">
         <v>881</v>
       </c>
       <c r="I174" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="175" spans="1:20">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23">
       <c r="A175" t="s">
         <v>533</v>
       </c>
@@ -20365,22 +20601,22 @@
         <v>541</v>
       </c>
       <c r="F175" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G175" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H175" t="s">
         <v>877</v>
       </c>
       <c r="I175" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J175" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="176" spans="1:20">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23">
       <c r="A176" t="s">
         <v>533</v>
       </c>
@@ -20397,16 +20633,16 @@
         <v>542</v>
       </c>
       <c r="F176" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G176" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H176" t="s">
         <v>881</v>
       </c>
       <c r="I176" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="177" spans="1:23">
@@ -20414,10 +20650,10 @@
         <v>533</v>
       </c>
       <c r="B177" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C177" t="s">
         <v>1071</v>
-      </c>
-      <c r="C177" t="s">
-        <v>1072</v>
       </c>
       <c r="D177" t="s">
         <v>533</v>
@@ -20426,19 +20662,19 @@
         <v>542</v>
       </c>
       <c r="F177" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G177" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H177" t="s">
         <v>877</v>
       </c>
       <c r="I177" t="s">
+        <v>912</v>
+      </c>
+      <c r="J177" t="s">
         <v>913</v>
-      </c>
-      <c r="J177" t="s">
-        <v>914</v>
       </c>
     </row>
     <row r="178" spans="1:23">
@@ -20458,10 +20694,10 @@
         <v>545</v>
       </c>
       <c r="F178" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="G178" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H178" t="s">
         <v>877</v>
@@ -20470,7 +20706,7 @@
         <v>870</v>
       </c>
       <c r="J178" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="179" spans="1:23">
@@ -20490,16 +20726,16 @@
         <v>549</v>
       </c>
       <c r="F179" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="G179" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H179" t="s">
         <v>881</v>
       </c>
       <c r="I179" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="180" spans="1:23">
@@ -20519,16 +20755,16 @@
         <v>552</v>
       </c>
       <c r="F180" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="G180" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H180" t="s">
         <v>875</v>
       </c>
       <c r="I180" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="181" spans="1:23">
@@ -20548,16 +20784,16 @@
         <v>556</v>
       </c>
       <c r="F181" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="G181" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H181" t="s">
         <v>875</v>
       </c>
       <c r="I181" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="182" spans="1:23">
@@ -20577,16 +20813,16 @@
         <v>283</v>
       </c>
       <c r="F182" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="G182" t="s">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="H182" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I182" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L182" t="s">
         <v>557</v>
@@ -20627,22 +20863,22 @@
     </row>
     <row r="183" spans="1:23">
       <c r="D183" t="s">
+        <v>1312</v>
+      </c>
+      <c r="E183" t="s">
         <v>1313</v>
       </c>
-      <c r="E183" t="s">
+      <c r="F183" t="s">
         <v>1314</v>
       </c>
-      <c r="F183" t="s">
+      <c r="L183" s="10" t="s">
+        <v>1312</v>
+      </c>
+      <c r="M183" s="10" t="s">
+        <v>1313</v>
+      </c>
+      <c r="N183" s="10" t="s">
         <v>1315</v>
-      </c>
-      <c r="L183" s="10" t="s">
-        <v>1313</v>
-      </c>
-      <c r="M183" s="10" t="s">
-        <v>1314</v>
-      </c>
-      <c r="N183" s="10" t="s">
-        <v>1316</v>
       </c>
     </row>
     <row r="184" spans="1:23">
@@ -20662,19 +20898,19 @@
         <v>291</v>
       </c>
       <c r="F184" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="G184" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H184" t="s">
         <v>881</v>
       </c>
       <c r="I184" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J184" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="185" spans="1:23">
@@ -20685,19 +20921,19 @@
         <v>291</v>
       </c>
       <c r="F185" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="G185" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H185" t="s">
         <v>881</v>
       </c>
       <c r="I185" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J185" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="186" spans="1:23">
@@ -20717,16 +20953,16 @@
         <v>291</v>
       </c>
       <c r="F186" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="G186" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H186" t="s">
         <v>881</v>
       </c>
       <c r="I186" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="187" spans="1:23">
@@ -20746,19 +20982,19 @@
         <v>291</v>
       </c>
       <c r="F187" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="G187" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H187" t="s">
         <v>881</v>
       </c>
       <c r="I187" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J187" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="188" spans="1:23">
@@ -20778,19 +21014,19 @@
         <v>291</v>
       </c>
       <c r="F188" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="G188" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H188" t="s">
         <v>881</v>
       </c>
       <c r="I188" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J188" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="189" spans="1:23">
@@ -20801,7 +21037,7 @@
         <v>286</v>
       </c>
       <c r="C189" t="s">
-        <v>1127</v>
+        <v>1126</v>
       </c>
       <c r="D189" t="s">
         <v>561</v>
@@ -20810,16 +21046,16 @@
         <v>283</v>
       </c>
       <c r="F189" t="s">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="G189" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H189" t="s">
         <v>813</v>
       </c>
       <c r="I189" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L189" t="s">
         <v>561</v>
@@ -20837,7 +21073,7 @@
         <v>283</v>
       </c>
       <c r="Q189" t="s">
-        <v>1129</v>
+        <v>1128</v>
       </c>
     </row>
     <row r="190" spans="1:23">
@@ -20857,16 +21093,16 @@
         <v>459</v>
       </c>
       <c r="F190" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="G190" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H190" t="s">
         <v>881</v>
       </c>
       <c r="I190" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="L190" t="s">
         <v>458</v>
@@ -20898,13 +21134,13 @@
         <v>570</v>
       </c>
       <c r="G191" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H191" t="s">
         <v>813</v>
       </c>
       <c r="I191" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="192" spans="1:23">
@@ -20924,16 +21160,16 @@
         <v>569</v>
       </c>
       <c r="F192" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="G192" t="s">
-        <v>1281</v>
+        <v>1280</v>
       </c>
       <c r="H192" t="s">
         <v>875</v>
       </c>
       <c r="I192" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="193" spans="1:20">
@@ -20953,16 +21189,16 @@
         <v>573</v>
       </c>
       <c r="F193" t="s">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="G193" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H193" t="s">
         <v>813</v>
       </c>
       <c r="I193" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="L193" t="s">
         <v>458</v>
@@ -20971,7 +21207,7 @@
         <v>573</v>
       </c>
       <c r="N193" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="194" spans="1:20">
@@ -20991,10 +21227,10 @@
         <v>577</v>
       </c>
       <c r="F194" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G194" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H194" t="s">
         <v>873</v>
@@ -21003,7 +21239,7 @@
         <v>870</v>
       </c>
       <c r="J194" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="195" spans="1:20">
@@ -21014,10 +21250,10 @@
         <v>577</v>
       </c>
       <c r="F195" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="G195" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H195" t="s">
         <v>877</v>
@@ -21026,7 +21262,7 @@
         <v>870</v>
       </c>
       <c r="J195" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="196" spans="1:20">
@@ -21037,10 +21273,10 @@
         <v>577</v>
       </c>
       <c r="F196" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="G196" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H196" t="s">
         <v>877</v>
@@ -21049,7 +21285,7 @@
         <v>870</v>
       </c>
       <c r="J196" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="197" spans="1:20">
@@ -21063,10 +21299,10 @@
         <v>587</v>
       </c>
       <c r="G197" t="s">
+        <v>937</v>
+      </c>
+      <c r="H197" t="s">
         <v>938</v>
-      </c>
-      <c r="H197" t="s">
-        <v>939</v>
       </c>
       <c r="I197" t="s">
         <v>607</v>
@@ -21083,10 +21319,10 @@
         <v>590</v>
       </c>
       <c r="G198" t="s">
+        <v>937</v>
+      </c>
+      <c r="H198" t="s">
         <v>938</v>
-      </c>
-      <c r="H198" t="s">
-        <v>939</v>
       </c>
       <c r="I198" t="s">
         <v>607</v>
@@ -21103,10 +21339,10 @@
         <v>593</v>
       </c>
       <c r="G199" t="s">
+        <v>937</v>
+      </c>
+      <c r="H199" t="s">
         <v>938</v>
-      </c>
-      <c r="H199" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="200" spans="1:20">
@@ -21117,16 +21353,16 @@
         <v>336</v>
       </c>
       <c r="F200" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="G200" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H200" t="s">
         <v>881</v>
       </c>
       <c r="I200" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="L200" t="s">
         <v>313</v>
@@ -21155,16 +21391,16 @@
         <v>637</v>
       </c>
       <c r="F201" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="G201" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H201" t="s">
         <v>875</v>
       </c>
       <c r="I201" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="202" spans="1:20">
@@ -21184,16 +21420,16 @@
         <v>641</v>
       </c>
       <c r="F202" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G202" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H202" t="s">
         <v>875</v>
       </c>
       <c r="I202" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L202" t="s">
         <v>638</v>
@@ -21222,16 +21458,16 @@
         <v>643</v>
       </c>
       <c r="F203" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G203" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H203" t="s">
         <v>875</v>
       </c>
       <c r="I203" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="204" spans="1:20">
@@ -21251,16 +21487,16 @@
         <v>648</v>
       </c>
       <c r="F204" t="s">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="G204" t="s">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="H204" t="s">
         <v>875</v>
       </c>
       <c r="I204" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="L204" t="s">
         <v>645</v>
@@ -21269,7 +21505,7 @@
         <v>648</v>
       </c>
       <c r="N204" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="205" spans="1:20">
@@ -21277,13 +21513,13 @@
         <v>814</v>
       </c>
       <c r="E205" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="F205" t="s">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="G205" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H205" t="s">
         <v>65</v>
@@ -21295,10 +21531,10 @@
         <v>814</v>
       </c>
       <c r="M205" t="s">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="N205" t="s">
-        <v>1294</v>
+        <v>1293</v>
       </c>
     </row>
     <row r="206" spans="1:20">
@@ -21318,10 +21554,10 @@
         <v>654</v>
       </c>
       <c r="F206" t="s">
-        <v>1293</v>
+        <v>1292</v>
       </c>
       <c r="G206" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H206" t="s">
         <v>65</v>
@@ -21345,7 +21581,7 @@
         <v>654</v>
       </c>
       <c r="Q206" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="R206" t="s">
         <v>814</v>
@@ -21354,12 +21590,12 @@
         <v>654</v>
       </c>
       <c r="T206" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="207" spans="1:20">
       <c r="D207" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="E207" t="s">
         <v>655</v>
@@ -21368,13 +21604,13 @@
         <v>656</v>
       </c>
       <c r="G207" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H207" t="s">
         <v>875</v>
       </c>
       <c r="I207" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="L207" t="s">
         <v>815</v>
@@ -21383,7 +21619,7 @@
         <v>655</v>
       </c>
       <c r="N207" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="208" spans="1:20">
@@ -21394,19 +21630,19 @@
         <v>658</v>
       </c>
       <c r="F208" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G208" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H208" t="s">
         <v>881</v>
       </c>
       <c r="I208" t="s">
+        <v>949</v>
+      </c>
+      <c r="J208" t="s">
         <v>950</v>
-      </c>
-      <c r="J208" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="209" spans="1:14">
@@ -21417,19 +21653,19 @@
         <v>659</v>
       </c>
       <c r="F209" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G209" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H209" t="s">
         <v>881</v>
       </c>
       <c r="I209" t="s">
+        <v>949</v>
+      </c>
+      <c r="J209" t="s">
         <v>950</v>
-      </c>
-      <c r="J209" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="210" spans="1:14">
@@ -21440,19 +21676,19 @@
         <v>799</v>
       </c>
       <c r="F210" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G210" t="s">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="H210" t="s">
         <v>881</v>
       </c>
       <c r="I210" t="s">
+        <v>949</v>
+      </c>
+      <c r="J210" t="s">
         <v>950</v>
-      </c>
-      <c r="J210" t="s">
-        <v>951</v>
       </c>
     </row>
     <row r="211" spans="1:14">
@@ -21472,10 +21708,10 @@
         <v>663</v>
       </c>
       <c r="F211" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G211" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H211" t="s">
         <v>877</v>
@@ -21484,7 +21720,7 @@
         <v>870</v>
       </c>
       <c r="J211" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="212" spans="1:14">
@@ -21495,16 +21731,16 @@
         <v>668</v>
       </c>
       <c r="F212" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G212" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H212" t="s">
         <v>869</v>
       </c>
       <c r="I212" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="L212" t="s">
         <v>458</v>
@@ -21533,10 +21769,10 @@
         <v>675</v>
       </c>
       <c r="F213" t="s">
+        <v>956</v>
+      </c>
+      <c r="G213" t="s">
         <v>957</v>
-      </c>
-      <c r="G213" t="s">
-        <v>958</v>
       </c>
       <c r="H213" t="s">
         <v>881</v>
@@ -21562,10 +21798,10 @@
         <v>679</v>
       </c>
       <c r="F214" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G214" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H214" t="s">
         <v>881</v>
@@ -21582,19 +21818,19 @@
         <v>521</v>
       </c>
       <c r="F215" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G215" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H215" t="s">
         <v>877</v>
       </c>
       <c r="I215" t="s">
+        <v>960</v>
+      </c>
+      <c r="J215" t="s">
         <v>961</v>
-      </c>
-      <c r="J215" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="216" spans="1:14">
@@ -21605,19 +21841,19 @@
         <v>526</v>
       </c>
       <c r="F216" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G216" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H216" t="s">
         <v>877</v>
       </c>
       <c r="I216" t="s">
+        <v>960</v>
+      </c>
+      <c r="J216" t="s">
         <v>961</v>
-      </c>
-      <c r="J216" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="217" spans="1:14">
@@ -21628,19 +21864,19 @@
         <v>681</v>
       </c>
       <c r="F217" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G217" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H217" t="s">
         <v>877</v>
       </c>
       <c r="I217" t="s">
+        <v>960</v>
+      </c>
+      <c r="J217" t="s">
         <v>961</v>
-      </c>
-      <c r="J217" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="218" spans="1:14">
@@ -21651,19 +21887,19 @@
         <v>682</v>
       </c>
       <c r="F218" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G218" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H218" t="s">
         <v>877</v>
       </c>
       <c r="I218" t="s">
+        <v>960</v>
+      </c>
+      <c r="J218" t="s">
         <v>961</v>
-      </c>
-      <c r="J218" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="219" spans="1:14">
@@ -21674,19 +21910,19 @@
         <v>683</v>
       </c>
       <c r="F219" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="G219" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H219" t="s">
         <v>877</v>
       </c>
       <c r="I219" t="s">
+        <v>960</v>
+      </c>
+      <c r="J219" t="s">
         <v>961</v>
-      </c>
-      <c r="J219" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="220" spans="1:14">
@@ -21697,19 +21933,19 @@
         <v>684</v>
       </c>
       <c r="F220" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G220" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H220" t="s">
         <v>877</v>
       </c>
       <c r="I220" t="s">
+        <v>960</v>
+      </c>
+      <c r="J220" t="s">
         <v>961</v>
-      </c>
-      <c r="J220" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="221" spans="1:14">
@@ -21720,19 +21956,19 @@
         <v>685</v>
       </c>
       <c r="F221" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G221" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H221" t="s">
         <v>877</v>
       </c>
       <c r="I221" t="s">
+        <v>960</v>
+      </c>
+      <c r="J221" t="s">
         <v>961</v>
-      </c>
-      <c r="J221" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="222" spans="1:14">
@@ -21743,19 +21979,19 @@
         <v>522</v>
       </c>
       <c r="F222" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G222" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H222" t="s">
         <v>877</v>
       </c>
       <c r="I222" t="s">
+        <v>960</v>
+      </c>
+      <c r="J222" t="s">
         <v>961</v>
-      </c>
-      <c r="J222" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="223" spans="1:14">
@@ -21766,19 +22002,19 @@
         <v>686</v>
       </c>
       <c r="F223" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="G223" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H223" t="s">
         <v>877</v>
       </c>
       <c r="I223" t="s">
+        <v>960</v>
+      </c>
+      <c r="J223" t="s">
         <v>961</v>
-      </c>
-      <c r="J223" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="224" spans="1:14">
@@ -21789,19 +22025,19 @@
         <v>527</v>
       </c>
       <c r="F224" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="G224" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H224" t="s">
         <v>877</v>
       </c>
       <c r="I224" t="s">
+        <v>960</v>
+      </c>
+      <c r="J224" t="s">
         <v>961</v>
-      </c>
-      <c r="J224" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="225" spans="1:17">
@@ -21812,19 +22048,19 @@
         <v>528</v>
       </c>
       <c r="F225" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G225" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H225" t="s">
         <v>877</v>
       </c>
       <c r="I225" t="s">
+        <v>960</v>
+      </c>
+      <c r="J225" t="s">
         <v>961</v>
-      </c>
-      <c r="J225" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="226" spans="1:17">
@@ -21835,19 +22071,19 @@
         <v>529</v>
       </c>
       <c r="F226" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="G226" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H226" t="s">
         <v>877</v>
       </c>
       <c r="I226" t="s">
+        <v>960</v>
+      </c>
+      <c r="J226" t="s">
         <v>961</v>
-      </c>
-      <c r="J226" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="227" spans="1:17">
@@ -21858,19 +22094,19 @@
         <v>687</v>
       </c>
       <c r="F227" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G227" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H227" t="s">
         <v>877</v>
       </c>
       <c r="I227" t="s">
+        <v>960</v>
+      </c>
+      <c r="J227" t="s">
         <v>961</v>
-      </c>
-      <c r="J227" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="228" spans="1:17">
@@ -21881,19 +22117,19 @@
         <v>688</v>
       </c>
       <c r="F228" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G228" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H228" t="s">
         <v>877</v>
       </c>
       <c r="I228" t="s">
+        <v>960</v>
+      </c>
+      <c r="J228" t="s">
         <v>961</v>
-      </c>
-      <c r="J228" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="229" spans="1:17">
@@ -21904,19 +22140,19 @@
         <v>689</v>
       </c>
       <c r="F229" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G229" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H229" t="s">
         <v>877</v>
       </c>
       <c r="I229" t="s">
+        <v>960</v>
+      </c>
+      <c r="J229" t="s">
         <v>961</v>
-      </c>
-      <c r="J229" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="230" spans="1:17">
@@ -21927,19 +22163,19 @@
         <v>680</v>
       </c>
       <c r="F230" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G230" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H230" t="s">
         <v>877</v>
       </c>
       <c r="I230" t="s">
+        <v>960</v>
+      </c>
+      <c r="J230" t="s">
         <v>961</v>
-      </c>
-      <c r="J230" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="231" spans="1:17">
@@ -21950,19 +22186,19 @@
         <v>530</v>
       </c>
       <c r="F231" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G231" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H231" t="s">
         <v>877</v>
       </c>
       <c r="I231" t="s">
+        <v>960</v>
+      </c>
+      <c r="J231" t="s">
         <v>961</v>
-      </c>
-      <c r="J231" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="232" spans="1:17">
@@ -21973,19 +22209,19 @@
         <v>531</v>
       </c>
       <c r="F232" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G232" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H232" t="s">
         <v>877</v>
       </c>
       <c r="I232" t="s">
+        <v>960</v>
+      </c>
+      <c r="J232" t="s">
         <v>961</v>
-      </c>
-      <c r="J232" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="233" spans="1:17">
@@ -22005,19 +22241,19 @@
         <v>738</v>
       </c>
       <c r="F233" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G233" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H233" t="s">
         <v>877</v>
       </c>
       <c r="I233" t="s">
+        <v>960</v>
+      </c>
+      <c r="J233" t="s">
         <v>961</v>
-      </c>
-      <c r="J233" t="s">
-        <v>962</v>
       </c>
     </row>
     <row r="234" spans="1:17">
@@ -22037,10 +22273,10 @@
         <v>525</v>
       </c>
       <c r="F234" t="s">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="G234" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H234" t="s">
         <v>881</v>
@@ -22055,7 +22291,7 @@
         <v>525</v>
       </c>
       <c r="N234" t="s">
-        <v>1343</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="235" spans="1:17">
@@ -22075,10 +22311,10 @@
         <v>525</v>
       </c>
       <c r="F235" t="s">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="G235" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H235" t="s">
         <v>881</v>
@@ -22093,7 +22329,7 @@
         <v>525</v>
       </c>
       <c r="N235" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="236" spans="1:17">
@@ -22104,42 +22340,42 @@
         <v>690</v>
       </c>
       <c r="F236" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G236" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H236" t="s">
         <v>881</v>
       </c>
       <c r="I236" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="J236" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="237" spans="1:17">
       <c r="D237" t="s">
+        <v>1304</v>
+      </c>
+      <c r="E237" t="s">
         <v>1305</v>
       </c>
-      <c r="E237" t="s">
+      <c r="F237" t="s">
         <v>1306</v>
       </c>
-      <c r="F237" t="s">
-        <v>1307</v>
-      </c>
       <c r="G237" t="s">
+        <v>1302</v>
+      </c>
+      <c r="H237" t="s">
         <v>1303</v>
       </c>
-      <c r="H237" t="s">
-        <v>1304</v>
-      </c>
       <c r="I237" t="s">
-        <v>1302</v>
+        <v>1301</v>
       </c>
       <c r="J237" t="s">
-        <v>1301</v>
+        <v>1300</v>
       </c>
     </row>
     <row r="238" spans="1:17">
@@ -22153,7 +22389,7 @@
         <v>692</v>
       </c>
       <c r="G238" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H238" t="s">
         <v>877</v>
@@ -22162,7 +22398,7 @@
         <v>882</v>
       </c>
       <c r="J238" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="239" spans="1:17">
@@ -22179,19 +22415,19 @@
         <v>624</v>
       </c>
       <c r="E239" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="F239" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G239" t="s">
         <v>1075</v>
-      </c>
-      <c r="G239" t="s">
-        <v>1076</v>
       </c>
       <c r="H239" t="s">
         <v>869</v>
       </c>
       <c r="J239" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="L239" t="s">
         <v>624</v>
@@ -22209,7 +22445,7 @@
         <v>862</v>
       </c>
       <c r="Q239" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="240" spans="1:17">
@@ -22232,13 +22468,13 @@
         <v>699</v>
       </c>
       <c r="G240" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H240" t="s">
         <v>875</v>
       </c>
       <c r="I240" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="241" spans="1:14">
@@ -22252,13 +22488,13 @@
         <v>701</v>
       </c>
       <c r="G241" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H241" t="s">
         <v>875</v>
       </c>
       <c r="I241" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="242" spans="1:14">
@@ -22269,16 +22505,16 @@
         <v>702</v>
       </c>
       <c r="F242" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="G242" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H242" t="s">
         <v>881</v>
       </c>
       <c r="I242" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="243" spans="1:14">
@@ -22289,10 +22525,10 @@
         <v>704</v>
       </c>
       <c r="F243" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G243" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H243" t="s">
         <v>881</v>
@@ -22309,16 +22545,16 @@
         <v>706</v>
       </c>
       <c r="F244" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G244" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H244" t="s">
         <v>881</v>
       </c>
       <c r="I244" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="245" spans="1:14">
@@ -22332,7 +22568,7 @@
         <v>707</v>
       </c>
       <c r="G245" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H245" t="s">
         <v>873</v>
@@ -22349,28 +22585,28 @@
         <v>451</v>
       </c>
       <c r="F246" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G246" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H246" t="s">
         <v>869</v>
       </c>
       <c r="I246" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="J246" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="L246" t="s">
-        <v>1308</v>
+        <v>1307</v>
       </c>
       <c r="M246" t="s">
         <v>451</v>
       </c>
       <c r="N246" t="s">
-        <v>1311</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="247" spans="1:14">
@@ -22381,16 +22617,16 @@
         <v>444</v>
       </c>
       <c r="F247" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G247" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H247" t="s">
         <v>881</v>
       </c>
       <c r="I247" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="248" spans="1:14">
@@ -22410,16 +22646,16 @@
         <v>713</v>
       </c>
       <c r="F248" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G248" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H248" t="s">
         <v>881</v>
       </c>
       <c r="I248" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="249" spans="1:14">
@@ -22433,7 +22669,7 @@
         <v>717</v>
       </c>
       <c r="G249" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H249" t="s">
         <v>873</v>
@@ -22459,16 +22695,16 @@
         <v>719</v>
       </c>
       <c r="F250" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="G250" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H250" t="s">
         <v>881</v>
       </c>
       <c r="I250" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="251" spans="1:14">
@@ -22479,16 +22715,16 @@
         <v>720</v>
       </c>
       <c r="F251" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="G251" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H251" t="s">
         <v>881</v>
       </c>
       <c r="I251" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="252" spans="1:14">
@@ -22499,16 +22735,16 @@
         <v>721</v>
       </c>
       <c r="F252" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="G252" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H252" t="s">
         <v>881</v>
       </c>
       <c r="I252" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="253" spans="1:14">
@@ -22519,16 +22755,16 @@
         <v>722</v>
       </c>
       <c r="F253" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="G253" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H253" t="s">
         <v>873</v>
       </c>
       <c r="I253" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="254" spans="1:14">
@@ -22539,16 +22775,16 @@
         <v>329</v>
       </c>
       <c r="F254" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G254" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H254" t="s">
         <v>881</v>
       </c>
       <c r="I254" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="255" spans="1:14">
@@ -22568,16 +22804,16 @@
         <v>401</v>
       </c>
       <c r="F255" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G255" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H255" t="s">
         <v>881</v>
       </c>
       <c r="I255" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="256" spans="1:14">
@@ -22588,16 +22824,16 @@
         <v>723</v>
       </c>
       <c r="F256" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G256" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H256" t="s">
         <v>873</v>
       </c>
       <c r="I256" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="257" spans="1:14">
@@ -22608,16 +22844,16 @@
         <v>724</v>
       </c>
       <c r="F257" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="G257" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H257" t="s">
         <v>873</v>
       </c>
       <c r="I257" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="258" spans="1:14">
@@ -22628,16 +22864,16 @@
         <v>411</v>
       </c>
       <c r="F258" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G258" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H258" t="s">
         <v>881</v>
       </c>
       <c r="I258" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="259" spans="1:14">
@@ -22648,16 +22884,16 @@
         <v>725</v>
       </c>
       <c r="F259" t="s">
-        <v>1108</v>
+        <v>1107</v>
       </c>
       <c r="G259" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H259" t="s">
         <v>873</v>
       </c>
       <c r="I259" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="260" spans="1:14">
@@ -22668,16 +22904,16 @@
         <v>726</v>
       </c>
       <c r="F260" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G260" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H260" t="s">
         <v>873</v>
       </c>
       <c r="I260" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="261" spans="1:14">
@@ -22688,16 +22924,16 @@
         <v>727</v>
       </c>
       <c r="F261" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="G261" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H261" t="s">
         <v>873</v>
       </c>
       <c r="I261" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="262" spans="1:14">
@@ -22714,19 +22950,19 @@
         <v>225</v>
       </c>
       <c r="E262" t="s">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="F262" t="s">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="G262" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H262" t="s">
         <v>873</v>
       </c>
       <c r="I262" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="263" spans="1:14">
@@ -22740,13 +22976,13 @@
         <v>731</v>
       </c>
       <c r="G263" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H263" t="s">
         <v>873</v>
       </c>
       <c r="I263" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="264" spans="1:14">
@@ -22757,10 +22993,10 @@
         <v>485</v>
       </c>
       <c r="F264" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="G264" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H264" t="s">
         <v>881</v>
@@ -22786,10 +23022,10 @@
         <v>732</v>
       </c>
       <c r="F265" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="G265" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H265" t="s">
         <v>873</v>
@@ -22798,7 +23034,7 @@
         <v>882</v>
       </c>
       <c r="J265" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="266" spans="1:14">
@@ -22809,10 +23045,10 @@
         <v>733</v>
       </c>
       <c r="F266" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="G266" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H266" t="s">
         <v>875</v>
@@ -22829,10 +23065,10 @@
         <v>734</v>
       </c>
       <c r="F267" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G267" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H267" t="s">
         <v>875</v>
@@ -22849,10 +23085,10 @@
         <v>735</v>
       </c>
       <c r="F268" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G268" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H268" t="s">
         <v>873</v>
@@ -22869,16 +23105,16 @@
         <v>743</v>
       </c>
       <c r="F269" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="G269" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H269" t="s">
         <v>881</v>
       </c>
       <c r="I269" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="270" spans="1:14">
@@ -22889,19 +23125,19 @@
         <v>711</v>
       </c>
       <c r="F270" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G270" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H270" t="s">
         <v>877</v>
       </c>
       <c r="I270" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="J270" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="271" spans="1:14">
@@ -22912,19 +23148,19 @@
         <v>745</v>
       </c>
       <c r="F271" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="G271" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H271" t="s">
         <v>881</v>
       </c>
       <c r="I271" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="J271" t="s">
-        <v>1096</v>
+        <v>1095</v>
       </c>
       <c r="L271" t="s">
         <v>744</v>
@@ -22933,7 +23169,7 @@
         <v>745</v>
       </c>
       <c r="N271" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="272" spans="1:14">
@@ -22944,16 +23180,16 @@
         <v>764</v>
       </c>
       <c r="F272" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G272" t="s">
+        <v>937</v>
+      </c>
+      <c r="H272" t="s">
+        <v>938</v>
+      </c>
+      <c r="I272" t="s">
         <v>1018</v>
-      </c>
-      <c r="G272" t="s">
-        <v>938</v>
-      </c>
-      <c r="H272" t="s">
-        <v>939</v>
-      </c>
-      <c r="I272" t="s">
-        <v>1019</v>
       </c>
     </row>
     <row r="273" spans="1:20">
@@ -22964,10 +23200,10 @@
         <v>783</v>
       </c>
       <c r="F273" t="s">
-        <v>1220</v>
+        <v>1219</v>
       </c>
       <c r="G273" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H273" t="s">
         <v>813</v>
@@ -22976,7 +23212,7 @@
         <v>600</v>
       </c>
       <c r="J273" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="274" spans="1:20">
@@ -22987,19 +23223,19 @@
         <v>766</v>
       </c>
       <c r="F274" t="s">
+        <v>1019</v>
+      </c>
+      <c r="G274" t="s">
         <v>1020</v>
-      </c>
-      <c r="G274" t="s">
-        <v>1021</v>
       </c>
       <c r="H274" t="s">
         <v>881</v>
       </c>
       <c r="I274" t="s">
+        <v>1021</v>
+      </c>
+      <c r="J274" t="s">
         <v>1022</v>
-      </c>
-      <c r="J274" t="s">
-        <v>1023</v>
       </c>
     </row>
     <row r="275" spans="1:20" ht="16.5">
@@ -23010,19 +23246,19 @@
         <v>769</v>
       </c>
       <c r="F275" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="G275" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H275" t="s">
         <v>881</v>
       </c>
       <c r="I275" s="9" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="J275" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="L275" t="s">
         <v>192</v>
@@ -23031,7 +23267,7 @@
         <v>769</v>
       </c>
       <c r="N275" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="276" spans="1:20">
@@ -23054,7 +23290,7 @@
         <v>776</v>
       </c>
       <c r="G276" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H276" t="s">
         <v>877</v>
@@ -23063,7 +23299,7 @@
         <v>870</v>
       </c>
       <c r="J276" t="s">
-        <v>1300</v>
+        <v>1299</v>
       </c>
       <c r="L276" t="s">
         <v>703</v>
@@ -23072,7 +23308,7 @@
         <v>307</v>
       </c>
       <c r="N276" t="s">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="O276" t="s">
         <v>703</v>
@@ -23084,13 +23320,13 @@
         <v>759</v>
       </c>
       <c r="R276" t="s">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="S276" t="s">
         <v>307</v>
       </c>
       <c r="T276" t="s">
-        <v>1172</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="277" spans="1:20">
@@ -23101,16 +23337,16 @@
         <v>773</v>
       </c>
       <c r="F277" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="G277" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H277" t="s">
         <v>881</v>
       </c>
       <c r="I277" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="278" spans="1:20" ht="16.5">
@@ -23121,16 +23357,16 @@
         <v>344</v>
       </c>
       <c r="F278" t="s">
-        <v>1245</v>
+        <v>1244</v>
       </c>
       <c r="G278" s="10" t="s">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="H278" s="10" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I278" s="9" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L278" t="s">
         <v>376</v>
@@ -23139,7 +23375,7 @@
         <v>344</v>
       </c>
       <c r="N278" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="279" spans="1:20">
@@ -23150,10 +23386,10 @@
         <v>775</v>
       </c>
       <c r="F279" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="G279" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H279" t="s">
         <v>877</v>
@@ -23170,16 +23406,16 @@
         <v>459</v>
       </c>
       <c r="F280" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="G280" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H280" t="s">
         <v>881</v>
       </c>
       <c r="I280" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="281" spans="1:20">
@@ -23190,13 +23426,13 @@
         <v>779</v>
       </c>
       <c r="F281" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="G281" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H281" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I281" t="s">
         <v>595</v>
@@ -23208,7 +23444,7 @@
         <v>779</v>
       </c>
       <c r="N281" t="s">
-        <v>1202</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="282" spans="1:20">
@@ -23219,16 +23455,16 @@
         <v>781</v>
       </c>
       <c r="F282" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="G282" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H282" t="s">
         <v>881</v>
       </c>
       <c r="I282" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="L282" t="s">
         <v>46</v>
@@ -23237,7 +23473,7 @@
         <v>781</v>
       </c>
       <c r="N282" t="s">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="283" spans="1:20">
@@ -23248,10 +23484,10 @@
         <v>782</v>
       </c>
       <c r="F283" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G283" t="s">
         <v>1030</v>
-      </c>
-      <c r="G283" t="s">
-        <v>1031</v>
       </c>
       <c r="H283" t="s">
         <v>881</v>
@@ -23260,7 +23496,7 @@
         <v>898</v>
       </c>
       <c r="J283" t="s">
-        <v>1339</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="284" spans="1:20">
@@ -23271,16 +23507,16 @@
         <v>783</v>
       </c>
       <c r="F284" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="G284" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H284" t="s">
         <v>881</v>
       </c>
       <c r="I284" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="285" spans="1:20">
@@ -23291,19 +23527,19 @@
         <v>787</v>
       </c>
       <c r="F285" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="G285" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H285" t="s">
         <v>881</v>
       </c>
       <c r="I285" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="J285" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="286" spans="1:20">
@@ -23314,16 +23550,16 @@
         <v>794</v>
       </c>
       <c r="F286" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G286" t="s">
         <v>1035</v>
-      </c>
-      <c r="G286" t="s">
-        <v>1036</v>
       </c>
       <c r="H286" t="s">
         <v>881</v>
       </c>
       <c r="I286" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="287" spans="1:20">
@@ -23334,28 +23570,28 @@
         <v>783</v>
       </c>
       <c r="C287" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="D287" s="10" t="s">
         <v>765</v>
       </c>
       <c r="E287" s="10" t="s">
+        <v>1221</v>
+      </c>
+      <c r="F287" s="10" t="s">
         <v>1222</v>
       </c>
-      <c r="F287" s="10" t="s">
-        <v>1223</v>
-      </c>
       <c r="G287" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H287" t="s">
         <v>881</v>
       </c>
       <c r="I287" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="J287" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="288" spans="1:20">
@@ -23366,10 +23602,10 @@
         <v>796</v>
       </c>
       <c r="F288" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
       <c r="G288" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H288" t="s">
         <v>873</v>
@@ -23386,16 +23622,16 @@
         <v>798</v>
       </c>
       <c r="F289" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="G289" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="H289" t="s">
         <v>881</v>
       </c>
       <c r="I289" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="290" spans="1:14">
@@ -23406,10 +23642,10 @@
         <v>800</v>
       </c>
       <c r="F290" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="G290" t="s">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="H290" t="s">
         <v>875</v>
@@ -23432,16 +23668,16 @@
         <v>348</v>
       </c>
       <c r="F291" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="G291" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H291" t="s">
         <v>65</v>
       </c>
       <c r="I291" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="J291" t="s">
         <v>351</v>
@@ -23464,16 +23700,16 @@
         <v>78</v>
       </c>
       <c r="F292" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="G292" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H292" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="I292" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L292" t="s">
         <v>403</v>
@@ -23482,7 +23718,7 @@
         <v>78</v>
       </c>
       <c r="N292" t="s">
-        <v>1264</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="293" spans="1:14">
@@ -23502,19 +23738,19 @@
         <v>790</v>
       </c>
       <c r="F293" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="G293" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H293" t="s">
         <v>881</v>
       </c>
       <c r="I293" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J293" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="294" spans="1:14">
@@ -23534,16 +23770,16 @@
         <v>821</v>
       </c>
       <c r="F294" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="G294" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H294" t="s">
         <v>881</v>
       </c>
       <c r="I294" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="295" spans="1:14">
@@ -23554,16 +23790,16 @@
         <v>851</v>
       </c>
       <c r="F295" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="G295" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H295" t="s">
         <v>877</v>
       </c>
       <c r="I295" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="296" spans="1:14">
@@ -23571,13 +23807,13 @@
         <v>624</v>
       </c>
       <c r="E296" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F296" t="s">
         <v>1159</v>
       </c>
-      <c r="F296" t="s">
-        <v>1160</v>
-      </c>
       <c r="G296" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H296" t="s">
         <v>873</v>
@@ -23586,7 +23822,7 @@
         <v>882</v>
       </c>
       <c r="J296" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="297" spans="1:14">
@@ -23597,10 +23833,10 @@
         <v>852</v>
       </c>
       <c r="F297" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="G297" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H297" t="s">
         <v>873</v>
@@ -23609,7 +23845,7 @@
         <v>882</v>
       </c>
       <c r="J297" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="298" spans="1:14">
@@ -23620,13 +23856,13 @@
         <v>854</v>
       </c>
       <c r="F298" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="G298" t="s">
+        <v>937</v>
+      </c>
+      <c r="H298" t="s">
         <v>938</v>
-      </c>
-      <c r="H298" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="299" spans="1:14">
@@ -23637,13 +23873,13 @@
         <v>855</v>
       </c>
       <c r="F299" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="G299" t="s">
+        <v>937</v>
+      </c>
+      <c r="H299" t="s">
         <v>938</v>
-      </c>
-      <c r="H299" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="300" spans="1:14">
@@ -23654,13 +23890,13 @@
         <v>856</v>
       </c>
       <c r="F300" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="G300" t="s">
+        <v>937</v>
+      </c>
+      <c r="H300" t="s">
         <v>938</v>
-      </c>
-      <c r="H300" t="s">
-        <v>939</v>
       </c>
     </row>
     <row r="301" spans="1:14">
@@ -23671,19 +23907,19 @@
         <v>858</v>
       </c>
       <c r="F301" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="G301" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H301" t="s">
         <v>877</v>
       </c>
       <c r="I301" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="J301" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="302" spans="1:14">
@@ -23694,16 +23930,16 @@
         <v>780</v>
       </c>
       <c r="F302" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="G302" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H302" t="s">
         <v>873</v>
       </c>
       <c r="I302" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="303" spans="1:14">
@@ -23714,16 +23950,16 @@
         <v>127</v>
       </c>
       <c r="F303" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="G303" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H303" t="s">
         <v>873</v>
       </c>
       <c r="I303" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="L303" t="s">
         <v>119</v>
@@ -23732,7 +23968,7 @@
         <v>127</v>
       </c>
       <c r="N303" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="304" spans="1:14">
@@ -23743,19 +23979,19 @@
         <v>861</v>
       </c>
       <c r="F304" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="G304" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="H304" t="s">
         <v>881</v>
       </c>
       <c r="I304" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="J304" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="305" spans="1:14">
@@ -23766,68 +24002,68 @@
         <v>193</v>
       </c>
       <c r="F305" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="G305" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H305" t="s">
         <v>813</v>
       </c>
       <c r="I305" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="J305" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="306" spans="1:14">
       <c r="D306" t="s">
+        <v>1060</v>
+      </c>
+      <c r="E306" t="s">
         <v>1061</v>
       </c>
-      <c r="E306" t="s">
-        <v>1062</v>
-      </c>
       <c r="F306" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
       <c r="G306" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H306" t="s">
         <v>875</v>
       </c>
       <c r="I306" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="L306" t="s">
+        <v>1062</v>
+      </c>
+      <c r="M306" t="s">
+        <v>1061</v>
+      </c>
+      <c r="N306" t="s">
         <v>1063</v>
-      </c>
-      <c r="M306" t="s">
-        <v>1062</v>
-      </c>
-      <c r="N306" t="s">
-        <v>1064</v>
       </c>
     </row>
     <row r="307" spans="1:14">
       <c r="D307" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E307" t="s">
         <v>1067</v>
       </c>
-      <c r="E307" t="s">
-        <v>1068</v>
-      </c>
       <c r="F307" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="G307" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="H307" t="s">
         <v>875</v>
       </c>
       <c r="I307" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="308" spans="1:14">
@@ -23838,10 +24074,10 @@
         <v>439</v>
       </c>
       <c r="F308" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G308" t="s">
         <v>1078</v>
-      </c>
-      <c r="G308" t="s">
-        <v>1079</v>
       </c>
       <c r="H308" t="s">
         <v>65</v>
@@ -23850,7 +24086,7 @@
         <v>870</v>
       </c>
       <c r="J308" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="309" spans="1:14">
@@ -23858,7 +24094,7 @@
         <v>448</v>
       </c>
       <c r="B309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="C309" t="s">
         <v>860</v>
@@ -23867,30 +24103,30 @@
         <v>448</v>
       </c>
       <c r="E309" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="F309" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="G309" t="s">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="H309" t="s">
         <v>869</v>
       </c>
       <c r="I309" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="310" spans="1:14">
       <c r="A310" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="B310" t="s">
         <v>423</v>
       </c>
       <c r="C310" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="D310" t="s">
         <v>420</v>
@@ -23902,7 +24138,7 @@
         <v>424</v>
       </c>
       <c r="G310" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="H310" t="s">
         <v>65</v>
@@ -23922,13 +24158,13 @@
         <v>825</v>
       </c>
       <c r="G311" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H311" t="s">
         <v>65</v>
       </c>
       <c r="I311" t="s">
-        <v>1095</v>
+        <v>1094</v>
       </c>
     </row>
     <row r="312" spans="1:14">
@@ -23936,22 +24172,22 @@
         <v>60</v>
       </c>
       <c r="B312" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C312" t="s">
         <v>1097</v>
-      </c>
-      <c r="C312" t="s">
-        <v>1098</v>
       </c>
       <c r="D312" t="s">
         <v>60</v>
       </c>
       <c r="E312" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F312" t="s">
         <v>1099</v>
       </c>
-      <c r="F312" t="s">
-        <v>1100</v>
-      </c>
       <c r="G312" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H312" t="s">
         <v>65</v>
@@ -23960,7 +24196,7 @@
         <v>596</v>
       </c>
       <c r="J312" t="s">
-        <v>1101</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="313" spans="1:14">
@@ -23968,22 +24204,22 @@
         <v>156</v>
       </c>
       <c r="E313" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F313" t="s">
         <v>1119</v>
       </c>
-      <c r="F313" t="s">
-        <v>1120</v>
-      </c>
       <c r="G313" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H313" t="s">
         <v>65</v>
       </c>
       <c r="I313" t="s">
+        <v>1120</v>
+      </c>
+      <c r="J313" t="s">
         <v>1121</v>
-      </c>
-      <c r="J313" t="s">
-        <v>1122</v>
       </c>
     </row>
     <row r="314" spans="1:14">
@@ -23994,10 +24230,10 @@
         <v>80</v>
       </c>
       <c r="F314" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="G314" t="s">
-        <v>1258</v>
+        <v>1257</v>
       </c>
       <c r="H314" t="s">
         <v>65</v>
@@ -24006,7 +24242,7 @@
         <v>601</v>
       </c>
       <c r="J314" t="s">
-        <v>1169</v>
+        <v>1168</v>
       </c>
     </row>
     <row r="315" spans="1:14">
@@ -24017,10 +24253,10 @@
         <v>80</v>
       </c>
       <c r="F315" t="s">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="G315" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H315" t="s">
         <v>65</v>
@@ -24034,19 +24270,19 @@
         <v>642</v>
       </c>
       <c r="E316" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F316" t="s">
         <v>1130</v>
       </c>
-      <c r="F316" t="s">
-        <v>1131</v>
-      </c>
       <c r="G316" t="s">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="H316" t="s">
         <v>875</v>
       </c>
       <c r="I316" t="s">
-        <v>1132</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="317" spans="1:14">
@@ -24054,22 +24290,22 @@
         <v>533</v>
       </c>
       <c r="E317" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F317" t="s">
         <v>1133</v>
       </c>
-      <c r="F317" t="s">
-        <v>1134</v>
-      </c>
       <c r="G317" t="s">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="H317" t="s">
         <v>873</v>
       </c>
       <c r="I317" t="s">
+        <v>1134</v>
+      </c>
+      <c r="J317" t="s">
         <v>1135</v>
-      </c>
-      <c r="J317" t="s">
-        <v>1136</v>
       </c>
     </row>
     <row r="318" spans="1:14">
@@ -24077,40 +24313,40 @@
         <v>480</v>
       </c>
       <c r="B318" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C318" t="s">
-        <v>1286</v>
+        <v>1285</v>
       </c>
       <c r="D318" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="E318" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F318" t="s">
+        <v>1287</v>
+      </c>
+      <c r="G318" t="s">
         <v>1137</v>
       </c>
-      <c r="F318" t="s">
-        <v>1288</v>
-      </c>
-      <c r="G318" t="s">
+      <c r="H318" t="s">
         <v>1138</v>
-      </c>
-      <c r="H318" t="s">
-        <v>1139</v>
       </c>
       <c r="I318" t="s">
         <v>606</v>
       </c>
       <c r="J318" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="L318" t="s">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="M318" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="N318" t="s">
-        <v>1289</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="319" spans="1:14">
@@ -24118,16 +24354,16 @@
         <v>376</v>
       </c>
       <c r="E319" t="s">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="F319" t="s">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="G319" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="H319" t="s">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="I319" t="s">
         <v>595</v>
@@ -24136,10 +24372,10 @@
         <v>376</v>
       </c>
       <c r="M319" t="s">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="N319" t="s">
-        <v>1195</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="320" spans="1:14">
@@ -24150,13 +24386,13 @@
         <v>73</v>
       </c>
       <c r="F320" t="s">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="G320" t="s">
+        <v>1264</v>
+      </c>
+      <c r="H320" t="s">
         <v>1265</v>
-      </c>
-      <c r="H320" t="s">
-        <v>1266</v>
       </c>
       <c r="I320" t="s">
         <v>595</v>
@@ -24168,7 +24404,7 @@
         <v>73</v>
       </c>
       <c r="N320" t="s">
-        <v>1249</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="321" spans="1:17">
@@ -24179,19 +24415,19 @@
         <v>423</v>
       </c>
       <c r="F321" t="s">
+        <v>1209</v>
+      </c>
+      <c r="G321" t="s">
+        <v>1181</v>
+      </c>
+      <c r="H321" t="s">
         <v>1210</v>
-      </c>
-      <c r="G321" t="s">
-        <v>1182</v>
-      </c>
-      <c r="H321" t="s">
-        <v>1211</v>
       </c>
       <c r="I321" t="s">
         <v>601</v>
       </c>
       <c r="J321" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="L321" t="s">
         <v>46</v>
@@ -24200,7 +24436,7 @@
         <v>423</v>
       </c>
       <c r="N321" t="s">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="O321" t="s">
         <v>46</v>
@@ -24217,25 +24453,25 @@
         <v>480</v>
       </c>
       <c r="B322" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C322" t="s">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="D322" t="s">
         <v>480</v>
       </c>
       <c r="E322" t="s">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="F322" t="s">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="G322" t="s">
+        <v>1137</v>
+      </c>
+      <c r="H322" t="s">
         <v>1138</v>
-      </c>
-      <c r="H322" t="s">
-        <v>1139</v>
       </c>
       <c r="I322" t="s">
         <v>606</v>
@@ -24249,33 +24485,33 @@
         <v>725</v>
       </c>
       <c r="F323" t="s">
-        <v>1208</v>
+        <v>1207</v>
       </c>
       <c r="G323" t="s">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="H323" t="s">
         <v>579</v>
       </c>
       <c r="I323" t="s">
-        <v>1209</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="324" spans="1:17">
       <c r="D324" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
       <c r="E324" t="s">
-        <v>1145</v>
+        <v>1144</v>
       </c>
       <c r="F324" t="s">
+        <v>1189</v>
+      </c>
+      <c r="G324" t="s">
         <v>1190</v>
       </c>
-      <c r="G324" t="s">
-        <v>1191</v>
-      </c>
       <c r="H324" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="I324" t="s">
         <v>595</v>
@@ -24283,16 +24519,16 @@
     </row>
     <row r="325" spans="1:17">
       <c r="D325" t="s">
-        <v>1144</v>
+        <v>1143</v>
       </c>
       <c r="E325" t="s">
+        <v>1145</v>
+      </c>
+      <c r="F325" t="s">
         <v>1146</v>
       </c>
-      <c r="F325" t="s">
-        <v>1147</v>
-      </c>
       <c r="G325" t="s">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="H325" t="s">
         <v>578</v>
@@ -24306,13 +24542,13 @@
         <v>742</v>
       </c>
       <c r="E326" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F326" t="s">
         <v>1148</v>
       </c>
-      <c r="F326" t="s">
-        <v>1149</v>
-      </c>
       <c r="G326" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H326" t="s">
         <v>65</v>
@@ -24323,16 +24559,16 @@
     </row>
     <row r="327" spans="1:17">
       <c r="D327" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E327" t="s">
         <v>1151</v>
       </c>
-      <c r="E327" t="s">
-        <v>1152</v>
-      </c>
       <c r="F327" t="s">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="G327" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H327" t="s">
         <v>65</v>
@@ -24343,16 +24579,16 @@
     </row>
     <row r="328" spans="1:17">
       <c r="D328" t="s">
+        <v>1150</v>
+      </c>
+      <c r="E328" t="s">
         <v>1151</v>
       </c>
-      <c r="E328" t="s">
+      <c r="F328" t="s">
         <v>1152</v>
       </c>
-      <c r="F328" t="s">
-        <v>1153</v>
-      </c>
       <c r="G328" t="s">
-        <v>1174</v>
+        <v>1173</v>
       </c>
       <c r="H328" t="s">
         <v>65</v>
@@ -24372,10 +24608,10 @@
         <v>585</v>
       </c>
       <c r="G329" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H329" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L329" t="s">
         <v>585</v>
@@ -24384,33 +24620,33 @@
         <v>585</v>
       </c>
       <c r="N329" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="330" spans="1:17">
       <c r="D330" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E330" t="s">
+        <v>1153</v>
+      </c>
+      <c r="F330" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G330" t="s">
+        <v>937</v>
+      </c>
+      <c r="H330" t="s">
         <v>1154</v>
       </c>
-      <c r="E330" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F330" t="s">
-        <v>1154</v>
-      </c>
-      <c r="G330" t="s">
-        <v>938</v>
-      </c>
-      <c r="H330" t="s">
-        <v>1155</v>
-      </c>
       <c r="L330" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="M330" t="s">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="N330" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="331" spans="1:17">
@@ -24424,10 +24660,10 @@
         <v>588</v>
       </c>
       <c r="G331" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="H331" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L331" t="s">
         <v>588</v>
@@ -24436,7 +24672,7 @@
         <v>588</v>
       </c>
       <c r="N331" t="s">
-        <v>1158</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="332" spans="1:17">
@@ -24450,10 +24686,10 @@
         <v>591</v>
       </c>
       <c r="G332" t="s">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="H332" t="s">
-        <v>1155</v>
+        <v>1154</v>
       </c>
       <c r="L332" t="s">
         <v>591</v>
@@ -24469,1199 +24705,1222 @@
   <autoFilter ref="A1:W332" xr:uid="{C88C89EB-B21D-4698-AC40-3A2D469B1E42}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="942" priority="1077"/>
-    <cfRule type="duplicateValues" dxfId="941" priority="1078"/>
-    <cfRule type="duplicateValues" dxfId="940" priority="1080"/>
-    <cfRule type="duplicateValues" dxfId="939" priority="1082"/>
-    <cfRule type="duplicateValues" dxfId="938" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="1096"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="1101"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="937" priority="1055"/>
-    <cfRule type="duplicateValues" dxfId="936" priority="1057"/>
-    <cfRule type="duplicateValues" dxfId="935" priority="1062"/>
-    <cfRule type="duplicateValues" dxfId="934" priority="1064"/>
-    <cfRule type="duplicateValues" dxfId="933" priority="1067"/>
-    <cfRule type="duplicateValues" dxfId="932" priority="1069"/>
-    <cfRule type="duplicateValues" dxfId="931" priority="1071"/>
-    <cfRule type="duplicateValues" dxfId="930" priority="1073"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="1086"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="1076"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C10">
-    <cfRule type="duplicateValues" dxfId="929" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="985"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C210">
-    <cfRule type="duplicateValues" dxfId="928" priority="1088"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="1107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C212">
-    <cfRule type="duplicateValues" dxfId="927" priority="1013"/>
-    <cfRule type="duplicateValues" dxfId="926" priority="1014"/>
-    <cfRule type="duplicateValues" dxfId="925" priority="1015"/>
-    <cfRule type="duplicateValues" dxfId="924" priority="1016"/>
-    <cfRule type="duplicateValues" dxfId="923" priority="1017"/>
-    <cfRule type="duplicateValues" dxfId="922" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="945" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="1037"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C241:C286 C1:C9 C288:C1048576 C11:C239">
-    <cfRule type="duplicateValues" dxfId="921" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="1017"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C241:C286 F215:F232 C211 C213:C214 C1:C9 C233:C239 C288:C1048576 C11:C209">
-    <cfRule type="duplicateValues" dxfId="920" priority="1051"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="1070"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C287">
-    <cfRule type="duplicateValues" dxfId="919" priority="620"/>
-    <cfRule type="duplicateValues" dxfId="918" priority="621"/>
-    <cfRule type="duplicateValues" dxfId="917" priority="622"/>
-    <cfRule type="duplicateValues" dxfId="916" priority="623"/>
-    <cfRule type="duplicateValues" dxfId="915" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="642"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="639"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="914" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="1095"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="913" priority="1081"/>
-    <cfRule type="duplicateValues" dxfId="912" priority="1083"/>
-    <cfRule type="duplicateValues" dxfId="911" priority="1085"/>
-    <cfRule type="duplicateValues" dxfId="910" priority="1086"/>
-    <cfRule type="duplicateValues" dxfId="909" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="1100"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="1102"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="1106"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="908" priority="1054"/>
-    <cfRule type="duplicateValues" dxfId="907" priority="1056"/>
-    <cfRule type="duplicateValues" dxfId="906" priority="1058"/>
-    <cfRule type="duplicateValues" dxfId="905" priority="1059"/>
-    <cfRule type="duplicateValues" dxfId="904" priority="1060"/>
-    <cfRule type="duplicateValues" dxfId="903" priority="1061"/>
-    <cfRule type="duplicateValues" dxfId="902" priority="1063"/>
-    <cfRule type="duplicateValues" dxfId="901" priority="1066"/>
-    <cfRule type="duplicateValues" dxfId="900" priority="1068"/>
-    <cfRule type="duplicateValues" dxfId="899" priority="1070"/>
-    <cfRule type="duplicateValues" dxfId="898" priority="1072"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="1082"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="1077"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="1089"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="1073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F7">
-    <cfRule type="duplicateValues" dxfId="897" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="896" priority="351"/>
-    <cfRule type="duplicateValues" dxfId="895" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="894" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="893" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="892" priority="355"/>
-    <cfRule type="duplicateValues" dxfId="891" priority="356"/>
-    <cfRule type="duplicateValues" dxfId="890" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="889" priority="358"/>
-    <cfRule type="duplicateValues" dxfId="888" priority="359"/>
-    <cfRule type="duplicateValues" dxfId="887" priority="360"/>
-    <cfRule type="duplicateValues" dxfId="886" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="885" priority="362"/>
-    <cfRule type="duplicateValues" dxfId="884" priority="363"/>
-    <cfRule type="duplicateValues" dxfId="883" priority="364"/>
-    <cfRule type="duplicateValues" dxfId="882" priority="365"/>
-    <cfRule type="duplicateValues" dxfId="881" priority="366"/>
-    <cfRule type="duplicateValues" dxfId="880" priority="367"/>
-    <cfRule type="duplicateValues" dxfId="879" priority="368"/>
-    <cfRule type="duplicateValues" dxfId="878" priority="369"/>
-    <cfRule type="duplicateValues" dxfId="877" priority="370"/>
-    <cfRule type="duplicateValues" dxfId="876" priority="371"/>
-    <cfRule type="duplicateValues" dxfId="875" priority="372"/>
-    <cfRule type="duplicateValues" dxfId="874" priority="373"/>
-    <cfRule type="duplicateValues" dxfId="873" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="872" priority="375"/>
-    <cfRule type="duplicateValues" dxfId="871" priority="376"/>
-    <cfRule type="duplicateValues" dxfId="870" priority="377"/>
-    <cfRule type="duplicateValues" dxfId="869" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="387"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="385"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="379"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="372"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F10">
-    <cfRule type="duplicateValues" dxfId="868" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="984"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="867" priority="469"/>
-    <cfRule type="duplicateValues" dxfId="866" priority="470"/>
-    <cfRule type="duplicateValues" dxfId="865" priority="471"/>
-    <cfRule type="duplicateValues" dxfId="864" priority="472"/>
-    <cfRule type="duplicateValues" dxfId="863" priority="473"/>
-    <cfRule type="duplicateValues" dxfId="862" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="861" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="860" priority="476"/>
-    <cfRule type="duplicateValues" dxfId="859" priority="477"/>
-    <cfRule type="duplicateValues" dxfId="858" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="857" priority="479"/>
-    <cfRule type="duplicateValues" dxfId="856" priority="480"/>
-    <cfRule type="duplicateValues" dxfId="855" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="854" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="853" priority="483"/>
-    <cfRule type="duplicateValues" dxfId="852" priority="484"/>
-    <cfRule type="duplicateValues" dxfId="851" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="489"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="504"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F14">
-    <cfRule type="duplicateValues" dxfId="850" priority="848"/>
-    <cfRule type="duplicateValues" dxfId="849" priority="849"/>
-    <cfRule type="duplicateValues" dxfId="848" priority="850"/>
-    <cfRule type="duplicateValues" dxfId="847" priority="851"/>
-    <cfRule type="duplicateValues" dxfId="846" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="845" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="844" priority="854"/>
-    <cfRule type="duplicateValues" dxfId="843" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="870"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="874"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="873"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="871"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16">
-    <cfRule type="duplicateValues" dxfId="842" priority="328"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="347"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F18">
-    <cfRule type="duplicateValues" dxfId="841" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="840" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="839" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="838" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="837" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="836" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="835" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="834" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="833" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="832" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="831" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="830" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="829" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="828" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="827" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="826" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="825" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="824" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="823" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="822" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="821" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="820" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="819" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="818" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="817" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="816" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="815" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="814" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="813" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="832" priority="79"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F20">
-    <cfRule type="duplicateValues" dxfId="812" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="811" priority="507"/>
-    <cfRule type="duplicateValues" dxfId="810" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="809" priority="509"/>
-    <cfRule type="duplicateValues" dxfId="808" priority="510"/>
-    <cfRule type="duplicateValues" dxfId="807" priority="511"/>
-    <cfRule type="duplicateValues" dxfId="806" priority="512"/>
-    <cfRule type="duplicateValues" dxfId="805" priority="513"/>
-    <cfRule type="duplicateValues" dxfId="804" priority="514"/>
-    <cfRule type="duplicateValues" dxfId="803" priority="515"/>
-    <cfRule type="duplicateValues" dxfId="802" priority="516"/>
-    <cfRule type="duplicateValues" dxfId="801" priority="517"/>
-    <cfRule type="duplicateValues" dxfId="800" priority="518"/>
-    <cfRule type="duplicateValues" dxfId="799" priority="519"/>
-    <cfRule type="duplicateValues" dxfId="798" priority="520"/>
-    <cfRule type="duplicateValues" dxfId="797" priority="521"/>
-    <cfRule type="duplicateValues" dxfId="796" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="825" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="534"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="535"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="536"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="541"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="527"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F25">
-    <cfRule type="duplicateValues" dxfId="795" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="794" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="793" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="792" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="791" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="790" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="789" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="788" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="787" priority="114"/>
-    <cfRule type="duplicateValues" dxfId="786" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="785" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="784" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="783" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="782" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="781" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="780" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="779" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="778" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="777" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="776" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="775" priority="126"/>
-    <cfRule type="duplicateValues" dxfId="774" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="773" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="772" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="771" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="770" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="769" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="768" priority="133"/>
-    <cfRule type="duplicateValues" dxfId="767" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="148"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="137"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="142"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="129"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="151"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="127"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F91:F92">
-    <cfRule type="duplicateValues" dxfId="766" priority="738"/>
-    <cfRule type="duplicateValues" dxfId="765" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="757"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F101:F102">
-    <cfRule type="duplicateValues" dxfId="764" priority="840"/>
-    <cfRule type="duplicateValues" dxfId="763" priority="841"/>
-    <cfRule type="duplicateValues" dxfId="762" priority="842"/>
-    <cfRule type="duplicateValues" dxfId="761" priority="843"/>
-    <cfRule type="duplicateValues" dxfId="760" priority="844"/>
-    <cfRule type="duplicateValues" dxfId="759" priority="845"/>
-    <cfRule type="duplicateValues" dxfId="758" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="757" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="860"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F122">
-    <cfRule type="duplicateValues" dxfId="756" priority="467"/>
-    <cfRule type="duplicateValues" dxfId="755" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="487"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F127">
-    <cfRule type="duplicateValues" dxfId="754" priority="393"/>
-    <cfRule type="duplicateValues" dxfId="753" priority="394"/>
-    <cfRule type="duplicateValues" dxfId="752" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="751" priority="396"/>
-    <cfRule type="duplicateValues" dxfId="750" priority="397"/>
-    <cfRule type="duplicateValues" dxfId="749" priority="398"/>
-    <cfRule type="duplicateValues" dxfId="748" priority="399"/>
-    <cfRule type="duplicateValues" dxfId="747" priority="400"/>
-    <cfRule type="duplicateValues" dxfId="746" priority="401"/>
-    <cfRule type="duplicateValues" dxfId="745" priority="402"/>
-    <cfRule type="duplicateValues" dxfId="744" priority="403"/>
-    <cfRule type="duplicateValues" dxfId="743" priority="404"/>
-    <cfRule type="duplicateValues" dxfId="742" priority="405"/>
-    <cfRule type="duplicateValues" dxfId="741" priority="406"/>
-    <cfRule type="duplicateValues" dxfId="740" priority="407"/>
-    <cfRule type="duplicateValues" dxfId="739" priority="408"/>
-    <cfRule type="duplicateValues" dxfId="738" priority="409"/>
-    <cfRule type="duplicateValues" dxfId="737" priority="410"/>
-    <cfRule type="duplicateValues" dxfId="736" priority="411"/>
-    <cfRule type="duplicateValues" dxfId="735" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="422"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="426"/>
+    <cfRule type="duplicateValues" dxfId="767" priority="427"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="429"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="430"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="431"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="428"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="420"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="418"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F133">
-    <cfRule type="duplicateValues" dxfId="734" priority="701"/>
-    <cfRule type="duplicateValues" dxfId="733" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="720"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F135">
-    <cfRule type="duplicateValues" dxfId="732" priority="690"/>
-    <cfRule type="duplicateValues" dxfId="731" priority="691"/>
-    <cfRule type="duplicateValues" dxfId="730" priority="692"/>
-    <cfRule type="duplicateValues" dxfId="729" priority="693"/>
-    <cfRule type="duplicateValues" dxfId="728" priority="694"/>
-    <cfRule type="duplicateValues" dxfId="727" priority="695"/>
-    <cfRule type="duplicateValues" dxfId="726" priority="696"/>
-    <cfRule type="duplicateValues" dxfId="725" priority="697"/>
-    <cfRule type="duplicateValues" dxfId="724" priority="698"/>
-    <cfRule type="duplicateValues" dxfId="723" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="750" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="711"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="712"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="716"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="715"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F147">
-    <cfRule type="duplicateValues" dxfId="722" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="721" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="720" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="719" priority="150"/>
-    <cfRule type="duplicateValues" dxfId="718" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="717" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="716" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="715" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="714" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="713" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="712" priority="157"/>
-    <cfRule type="duplicateValues" dxfId="711" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="710" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="709" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="708" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="707" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="706" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="705" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="704" priority="165"/>
-    <cfRule type="duplicateValues" dxfId="703" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="702" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="701" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="700" priority="169"/>
-    <cfRule type="duplicateValues" dxfId="699" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="698" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="697" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="696" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="183"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="174"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="728" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="175"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="167"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="166"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="176"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="177"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="178"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="179"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="180"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="181"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F148">
-    <cfRule type="duplicateValues" dxfId="695" priority="144"/>
-    <cfRule type="duplicateValues" dxfId="694" priority="145"/>
-    <cfRule type="duplicateValues" dxfId="693" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="165"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F169">
-    <cfRule type="duplicateValues" dxfId="692" priority="951"/>
-    <cfRule type="duplicateValues" dxfId="691" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="971"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F197:F199">
-    <cfRule type="duplicateValues" dxfId="690" priority="736"/>
-    <cfRule type="duplicateValues" dxfId="689" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="756"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="755"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F204">
-    <cfRule type="duplicateValues" dxfId="688" priority="764"/>
-    <cfRule type="duplicateValues" dxfId="687" priority="765"/>
-    <cfRule type="duplicateValues" dxfId="686" priority="766"/>
-    <cfRule type="duplicateValues" dxfId="685" priority="767"/>
-    <cfRule type="duplicateValues" dxfId="684" priority="768"/>
-    <cfRule type="duplicateValues" dxfId="683" priority="769"/>
-    <cfRule type="duplicateValues" dxfId="682" priority="770"/>
-    <cfRule type="duplicateValues" dxfId="681" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="790"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F240">
-    <cfRule type="duplicateValues" dxfId="680" priority="379"/>
-    <cfRule type="duplicateValues" dxfId="679" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="399"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F241:F275 F1:F6 F8:F15 F33:F52 F192:F239 F128:F135 F149:F190 F137:F145 F17 F54:F126 F277:F323 F325:F1048576 F26:F31 F19:F24">
-    <cfRule type="duplicateValues" dxfId="678" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="455"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F259">
-    <cfRule type="duplicateValues" dxfId="677" priority="982"/>
-    <cfRule type="duplicateValues" dxfId="676" priority="983"/>
-    <cfRule type="duplicateValues" dxfId="675" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="696" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="1002"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="1001"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F270">
-    <cfRule type="duplicateValues" dxfId="674" priority="1045"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="1064"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F275">
-    <cfRule type="duplicateValues" dxfId="673" priority="865"/>
-    <cfRule type="duplicateValues" dxfId="672" priority="866"/>
-    <cfRule type="duplicateValues" dxfId="671" priority="867"/>
-    <cfRule type="duplicateValues" dxfId="670" priority="868"/>
-    <cfRule type="duplicateValues" dxfId="669" priority="869"/>
-    <cfRule type="duplicateValues" dxfId="668" priority="870"/>
-    <cfRule type="duplicateValues" dxfId="667" priority="871"/>
-    <cfRule type="duplicateValues" dxfId="666" priority="872"/>
-    <cfRule type="duplicateValues" dxfId="665" priority="873"/>
-    <cfRule type="duplicateValues" dxfId="664" priority="874"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="886"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="893"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="889"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F277:F323 F1:F17 F149:F275 F325:F1048576 F26:F146 F19:F24">
-    <cfRule type="duplicateValues" dxfId="663" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="299"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F282">
-    <cfRule type="duplicateValues" dxfId="662" priority="1041"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="1060"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F283">
-    <cfRule type="duplicateValues" dxfId="661" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="1058"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F285">
-    <cfRule type="duplicateValues" dxfId="660" priority="1033"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="1052"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F286">
-    <cfRule type="duplicateValues" dxfId="659" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="678" priority="1044"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F287">
-    <cfRule type="duplicateValues" dxfId="658" priority="603"/>
-    <cfRule type="duplicateValues" dxfId="657" priority="604"/>
-    <cfRule type="duplicateValues" dxfId="656" priority="605"/>
-    <cfRule type="duplicateValues" dxfId="655" priority="606"/>
-    <cfRule type="duplicateValues" dxfId="654" priority="607"/>
-    <cfRule type="duplicateValues" dxfId="653" priority="608"/>
-    <cfRule type="duplicateValues" dxfId="652" priority="609"/>
-    <cfRule type="duplicateValues" dxfId="651" priority="610"/>
-    <cfRule type="duplicateValues" dxfId="650" priority="611"/>
-    <cfRule type="duplicateValues" dxfId="649" priority="612"/>
-    <cfRule type="duplicateValues" dxfId="648" priority="613"/>
-    <cfRule type="duplicateValues" dxfId="647" priority="614"/>
-    <cfRule type="duplicateValues" dxfId="646" priority="615"/>
-    <cfRule type="duplicateValues" dxfId="645" priority="616"/>
-    <cfRule type="duplicateValues" dxfId="644" priority="617"/>
-    <cfRule type="duplicateValues" dxfId="643" priority="618"/>
-    <cfRule type="duplicateValues" dxfId="642" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="636"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="669" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="668" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="667" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="628"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="663" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="635"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="626"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F288:F313 F123:F126 F12:F15 F1:F6 F21:F24 F315:F323 F128:F134 F241:F275 F8:F10 F33:F52 F192:F239 F137:F145 F149:F190 F17 F54:F121 F277:F286 F325:F1048576 F26:F31 F19">
-    <cfRule type="duplicateValues" dxfId="641" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="719"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289">
-    <cfRule type="duplicateValues" dxfId="640" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296:F297">
-    <cfRule type="duplicateValues" dxfId="639" priority="959"/>
-    <cfRule type="duplicateValues" dxfId="638" priority="960"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="979"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F298:F299">
-    <cfRule type="duplicateValues" dxfId="637" priority="957"/>
-    <cfRule type="duplicateValues" dxfId="636" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="977"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F302">
-    <cfRule type="duplicateValues" dxfId="635" priority="944"/>
-    <cfRule type="duplicateValues" dxfId="634" priority="945"/>
-    <cfRule type="duplicateValues" dxfId="633" priority="946"/>
-    <cfRule type="duplicateValues" dxfId="632" priority="947"/>
-    <cfRule type="duplicateValues" dxfId="631" priority="948"/>
-    <cfRule type="duplicateValues" dxfId="630" priority="949"/>
-    <cfRule type="duplicateValues" dxfId="629" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="969"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="963"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="966"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F325">
-    <cfRule type="duplicateValues" dxfId="628" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="723"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 F30:F31 F1:F6 F300:F301 F288:F295 F157:F168 F303:F309 F103 F38:F52 F170:F190 F277:F286 F233:F239 F93:F100 F200:F203 G317 F329:F1048576 F319:F323 F134 F15 F260:F274 F205:F214 F21:F24 F12:F13 F105:F121 F123:F126 F312:F313 F315:F317 F128:F132 F241:F258 F8:F9 F33:F36 F192:F196 F137:F145 F149:F155 F17 F54:F90 F26:F28 F19">
-    <cfRule type="duplicateValues" dxfId="627" priority="1021"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="1040"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 F103 F38:F52 F157:F190 F93:F100 F200:F203 G317 F329:F1048576 F319:F323 F134 F277:F286 F15 F288:F309 F205:F239 F21:F24 F1:F6 F12:F13 F105:F121 F123:F126 F312:F313 F315:F317 F128:F132 F241:F274 F8:F10 F33:F36 F192:F196 F137:F145 F149:F155 F17 F54:F90 F26:F31 F19">
-    <cfRule type="duplicateValues" dxfId="626" priority="935"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="954"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 F290:F295 F288 F30:F31 F1:F6 F300:F301 F157:F168 F303:F309 F103 F38:F52 F170:F190 F277:F284 F233:F239 F93:F100 F200:F203 G317 F329:F1048576 F319:F323 F134 F15 F260:F274 F205:F214 F21:F24 F12:F13 F105:F121 F123:F126 F312:F313 F315:F317 F128:F132 F241:F258 F8:F9 F33:F36 F192:F196 F137:F145 F149:F155 F17 F54:F90 F26:F28 F19">
-    <cfRule type="duplicateValues" dxfId="625" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="1053"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 F290:F295 F288 F30:F31 F1:F6 F300:F301 F157:F168 F303:F309 F103 F38:F52 F170:F190 F277:F285 F233:F239 F93:F100 F200:F203 G317 F329:F1048576 F319:F323 F134 F15 F260:F274 F205:F214 F21:F24 F12:F13 F105:F121 F123:F126 F312:F313 F315:F317 F128:F132 F241:F258 F8:F9 F33:F36 F192:F196 F137:F145 F149:F155 F17 F54:F90 F26:F28 F19">
-    <cfRule type="duplicateValues" dxfId="624" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="1051"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 F290:F295 F288 F284 C211:C214 F260:F269 C1:C9 F30:F31 F1:F6 F300:F301 F157:F168 F303:F309 F103 F277:F281 F38:F52 F170:F190 G317 F329:F1048576 F319:F323 F15 F271:F274 C233:C239 F21:F24 F12:F13 F105:F126 F312:F313 F315:F317 F128:F134 F205:F258 C241:C286 F8:F9 F33:F36 F192:F203 F137:F145 F149:F155 C288:C1048576 F17 F54:F100 F26:F28 F19 C11:C209">
-    <cfRule type="duplicateValues" dxfId="623" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="642" priority="1072"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 F290:F295 F288 F284 F30:F31 F1:F6 F300:F301 F157:F168 F303:F309 F103 F38:F52 F170:F190 F277:F282 F233:F239 F93:F100 F200:F203 G317 F329:F1048576 F319:F323 F134 F15 F260:F274 F205:F214 F21:F24 F12:F13 F105:F121 F123:F126 F312:F313 F315:F317 F128:F132 F241:F258 F8:F9 F33:F36 F192:F196 F137:F145 F149:F155 F17 F54:F90 F26:F28 F19">
-    <cfRule type="duplicateValues" dxfId="622" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="1059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 F290:F295 F288 F284 F260:F269 F30:F31 F1:F6 F300:F301 F157:F168 F303:F309 F103 F38:F52 F170:F190 F277:F281 F233:F239 F93:F100 F200:F203 G317 F329:F1048576 F319:F323 F134 F15 F271:F274 F205:F214 F21:F24 F12:F13 F105:F121 F123:F126 F312:F313 F315:F317 F128:F132 F241:F258 F8:F9 F33:F36 F192:F196 F137:F145 F149:F155 F17 F54:F90 F26:F28 F19">
-    <cfRule type="duplicateValues" dxfId="621" priority="1049"/>
-    <cfRule type="duplicateValues" dxfId="620" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="1068"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="1069"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F326:F327 E318 G317 F329:F1048576 F319:F323 F134 F1:F6 F12:F15 F21:F24 F123:F126 F288:F313 F315:F317 F128:F132 F241:F275 F8:F10 F33:F52 F192:F239 F137:F145 F149:F190 F17 F54:F121 F277:F286 F26:F31 F19">
-    <cfRule type="duplicateValues" dxfId="619" priority="705"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F328">
-    <cfRule type="duplicateValues" dxfId="618" priority="703"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="722"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F53:G53">
-    <cfRule type="duplicateValues" dxfId="617" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F310:G310">
-    <cfRule type="duplicateValues" dxfId="616" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="883"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G314:G315">
-    <cfRule type="duplicateValues" dxfId="615" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="725"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="duplicateValues" dxfId="614" priority="1065"/>
-    <cfRule type="duplicateValues" dxfId="613" priority="1074"/>
-    <cfRule type="duplicateValues" dxfId="612" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="1093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J156">
-    <cfRule type="duplicateValues" dxfId="611" priority="625"/>
-    <cfRule type="duplicateValues" dxfId="610" priority="626"/>
-    <cfRule type="duplicateValues" dxfId="609" priority="627"/>
-    <cfRule type="duplicateValues" dxfId="608" priority="628"/>
-    <cfRule type="duplicateValues" dxfId="607" priority="629"/>
-    <cfRule type="duplicateValues" dxfId="606" priority="630"/>
-    <cfRule type="duplicateValues" dxfId="605" priority="631"/>
-    <cfRule type="duplicateValues" dxfId="604" priority="632"/>
-    <cfRule type="duplicateValues" dxfId="603" priority="633"/>
-    <cfRule type="duplicateValues" dxfId="602" priority="634"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="649"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="648"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="645"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J235">
-    <cfRule type="duplicateValues" dxfId="601" priority="856"/>
-    <cfRule type="duplicateValues" dxfId="600" priority="857"/>
-    <cfRule type="duplicateValues" dxfId="599" priority="858"/>
-    <cfRule type="duplicateValues" dxfId="598" priority="859"/>
-    <cfRule type="duplicateValues" dxfId="597" priority="860"/>
-    <cfRule type="duplicateValues" dxfId="596" priority="861"/>
-    <cfRule type="duplicateValues" dxfId="595" priority="862"/>
-    <cfRule type="duplicateValues" dxfId="594" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="881"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="882"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J246">
-    <cfRule type="duplicateValues" dxfId="593" priority="382"/>
-    <cfRule type="duplicateValues" dxfId="592" priority="383"/>
-    <cfRule type="duplicateValues" dxfId="591" priority="384"/>
-    <cfRule type="duplicateValues" dxfId="590" priority="385"/>
-    <cfRule type="duplicateValues" dxfId="589" priority="386"/>
-    <cfRule type="duplicateValues" dxfId="588" priority="387"/>
-    <cfRule type="duplicateValues" dxfId="587" priority="388"/>
-    <cfRule type="duplicateValues" dxfId="586" priority="389"/>
-    <cfRule type="duplicateValues" dxfId="585" priority="390"/>
-    <cfRule type="duplicateValues" dxfId="584" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="583" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="611" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="410"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="411"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J326:J1048576 J157:J204 J247:J271 J236:J245 J207:J234 J154 J273:J280 J282:J323 J1:J149">
-    <cfRule type="duplicateValues" dxfId="582" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="1071"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="duplicateValues" dxfId="581" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="1098"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N15:N16">
-    <cfRule type="duplicateValues" dxfId="580" priority="1449"/>
-    <cfRule type="duplicateValues" dxfId="579" priority="1450"/>
-    <cfRule type="duplicateValues" dxfId="578" priority="1451"/>
-    <cfRule type="duplicateValues" dxfId="577" priority="1452"/>
-    <cfRule type="duplicateValues" dxfId="576" priority="1453"/>
-    <cfRule type="duplicateValues" dxfId="575" priority="1454"/>
-    <cfRule type="duplicateValues" dxfId="574" priority="1455"/>
-    <cfRule type="duplicateValues" dxfId="573" priority="1456"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="1473"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="1471"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="1470"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="1474"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="1469"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="1472"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="1468"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="1475"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N20">
-    <cfRule type="duplicateValues" dxfId="572" priority="523"/>
-    <cfRule type="duplicateValues" dxfId="571" priority="524"/>
-    <cfRule type="duplicateValues" dxfId="570" priority="525"/>
-    <cfRule type="duplicateValues" dxfId="569" priority="526"/>
-    <cfRule type="duplicateValues" dxfId="568" priority="527"/>
-    <cfRule type="duplicateValues" dxfId="567" priority="528"/>
-    <cfRule type="duplicateValues" dxfId="566" priority="529"/>
-    <cfRule type="duplicateValues" dxfId="565" priority="530"/>
-    <cfRule type="duplicateValues" dxfId="564" priority="531"/>
-    <cfRule type="duplicateValues" dxfId="563" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="547"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="548"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="542"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="550"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21:N22">
-    <cfRule type="duplicateValues" dxfId="562" priority="715"/>
-    <cfRule type="duplicateValues" dxfId="561" priority="716"/>
-    <cfRule type="duplicateValues" dxfId="560" priority="717"/>
-    <cfRule type="duplicateValues" dxfId="559" priority="718"/>
-    <cfRule type="duplicateValues" dxfId="558" priority="719"/>
-    <cfRule type="duplicateValues" dxfId="557" priority="720"/>
-    <cfRule type="duplicateValues" dxfId="556" priority="721"/>
-    <cfRule type="duplicateValues" dxfId="555" priority="722"/>
-    <cfRule type="duplicateValues" dxfId="554" priority="723"/>
-    <cfRule type="duplicateValues" dxfId="553" priority="724"/>
-    <cfRule type="duplicateValues" dxfId="552" priority="725"/>
-    <cfRule type="duplicateValues" dxfId="551" priority="726"/>
-    <cfRule type="duplicateValues" dxfId="550" priority="727"/>
-    <cfRule type="duplicateValues" dxfId="549" priority="728"/>
-    <cfRule type="duplicateValues" dxfId="548" priority="729"/>
-    <cfRule type="duplicateValues" dxfId="547" priority="730"/>
-    <cfRule type="duplicateValues" dxfId="546" priority="731"/>
-    <cfRule type="duplicateValues" dxfId="545" priority="732"/>
-    <cfRule type="duplicateValues" dxfId="544" priority="733"/>
-    <cfRule type="duplicateValues" dxfId="543" priority="734"/>
-    <cfRule type="duplicateValues" dxfId="542" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="742"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="741"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="740"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="739"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="738"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="744"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="745"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="746"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="743"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="748"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N24">
-    <cfRule type="duplicateValues" dxfId="541" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="540" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="539" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="538" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="537" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="536" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="559" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="158"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="duplicateValues" dxfId="535" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="534" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="533" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="532" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="531" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="530" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="529" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="528" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="527" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="526" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="525" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="524" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="523" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="522" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="521" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="520" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="519" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="518" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="517" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="516" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="515" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="514" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="513" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="512" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="511" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="510" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="509" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="508" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="507" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="116"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="534" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="533" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="532" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="531" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="530" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="529" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N27">
-    <cfRule type="duplicateValues" dxfId="506" priority="927"/>
-    <cfRule type="duplicateValues" dxfId="505" priority="928"/>
-    <cfRule type="duplicateValues" dxfId="504" priority="929"/>
-    <cfRule type="duplicateValues" dxfId="503" priority="930"/>
-    <cfRule type="duplicateValues" dxfId="502" priority="931"/>
-    <cfRule type="duplicateValues" dxfId="501" priority="932"/>
-    <cfRule type="duplicateValues" dxfId="500" priority="933"/>
-    <cfRule type="duplicateValues" dxfId="499" priority="934"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="953"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="949"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="947"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="946"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N29">
-    <cfRule type="duplicateValues" dxfId="498" priority="999"/>
-    <cfRule type="duplicateValues" dxfId="497" priority="1000"/>
-    <cfRule type="duplicateValues" dxfId="496" priority="1001"/>
-    <cfRule type="duplicateValues" dxfId="495" priority="1002"/>
-    <cfRule type="duplicateValues" dxfId="494" priority="1003"/>
-    <cfRule type="duplicateValues" dxfId="493" priority="1004"/>
-    <cfRule type="duplicateValues" dxfId="492" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="1020"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="1018"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="1024"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="1023"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="1022"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="1021"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N31">
-    <cfRule type="duplicateValues" dxfId="491" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="490" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="489" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="488" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="487" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="486" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="485" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="484" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="483" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="482" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="481" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="480" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="53"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32">
-    <cfRule type="duplicateValues" dxfId="479" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="498" priority="56"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N57">
-    <cfRule type="duplicateValues" dxfId="478" priority="1046"/>
-    <cfRule type="duplicateValues" dxfId="477" priority="1047"/>
-    <cfRule type="duplicateValues" dxfId="476" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="1067"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="1066"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="1065"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N99">
-    <cfRule type="duplicateValues" dxfId="475" priority="748"/>
-    <cfRule type="duplicateValues" dxfId="474" priority="749"/>
-    <cfRule type="duplicateValues" dxfId="473" priority="750"/>
-    <cfRule type="duplicateValues" dxfId="472" priority="751"/>
-    <cfRule type="duplicateValues" dxfId="471" priority="752"/>
-    <cfRule type="duplicateValues" dxfId="470" priority="753"/>
-    <cfRule type="duplicateValues" dxfId="469" priority="754"/>
-    <cfRule type="duplicateValues" dxfId="468" priority="755"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="767"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="490" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="489" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="488" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="770"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N103">
-    <cfRule type="duplicateValues" dxfId="467" priority="891"/>
-    <cfRule type="duplicateValues" dxfId="466" priority="892"/>
-    <cfRule type="duplicateValues" dxfId="465" priority="893"/>
-    <cfRule type="duplicateValues" dxfId="464" priority="894"/>
-    <cfRule type="duplicateValues" dxfId="463" priority="895"/>
-    <cfRule type="duplicateValues" dxfId="462" priority="896"/>
-    <cfRule type="duplicateValues" dxfId="461" priority="897"/>
-    <cfRule type="duplicateValues" dxfId="460" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="486" priority="912"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="917"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N109">
-    <cfRule type="duplicateValues" dxfId="459" priority="553"/>
-    <cfRule type="duplicateValues" dxfId="458" priority="554"/>
-    <cfRule type="duplicateValues" dxfId="457" priority="555"/>
-    <cfRule type="duplicateValues" dxfId="456" priority="556"/>
-    <cfRule type="duplicateValues" dxfId="455" priority="557"/>
-    <cfRule type="duplicateValues" dxfId="454" priority="558"/>
-    <cfRule type="duplicateValues" dxfId="453" priority="559"/>
-    <cfRule type="duplicateValues" dxfId="452" priority="560"/>
-    <cfRule type="duplicateValues" dxfId="451" priority="561"/>
-    <cfRule type="duplicateValues" dxfId="450" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="575"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N119">
-    <cfRule type="duplicateValues" dxfId="449" priority="583"/>
-    <cfRule type="duplicateValues" dxfId="448" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="604"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="603"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="605"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="606"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="607"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="608"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="609"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="610"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="611"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="602"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N120:N121">
+    <cfRule type="duplicateValues" dxfId="458" priority="928"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="929"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="930"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="931"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="932"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="933"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="927"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="926"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N124">
+    <cfRule type="duplicateValues" dxfId="450" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="591"/>
     <cfRule type="duplicateValues" dxfId="447" priority="585"/>
     <cfRule type="duplicateValues" dxfId="446" priority="586"/>
-    <cfRule type="duplicateValues" dxfId="445" priority="587"/>
-    <cfRule type="duplicateValues" dxfId="444" priority="588"/>
-    <cfRule type="duplicateValues" dxfId="443" priority="589"/>
-    <cfRule type="duplicateValues" dxfId="442" priority="590"/>
-    <cfRule type="duplicateValues" dxfId="441" priority="591"/>
-    <cfRule type="duplicateValues" dxfId="440" priority="592"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N120:N121">
-    <cfRule type="duplicateValues" dxfId="439" priority="907"/>
-    <cfRule type="duplicateValues" dxfId="438" priority="908"/>
-    <cfRule type="duplicateValues" dxfId="437" priority="909"/>
-    <cfRule type="duplicateValues" dxfId="436" priority="910"/>
-    <cfRule type="duplicateValues" dxfId="435" priority="911"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="912"/>
-    <cfRule type="duplicateValues" dxfId="433" priority="913"/>
-    <cfRule type="duplicateValues" dxfId="432" priority="914"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N124">
-    <cfRule type="duplicateValues" dxfId="431" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="430" priority="564"/>
-    <cfRule type="duplicateValues" dxfId="429" priority="565"/>
-    <cfRule type="duplicateValues" dxfId="428" priority="566"/>
-    <cfRule type="duplicateValues" dxfId="427" priority="567"/>
-    <cfRule type="duplicateValues" dxfId="426" priority="568"/>
-    <cfRule type="duplicateValues" dxfId="425" priority="569"/>
-    <cfRule type="duplicateValues" dxfId="424" priority="570"/>
-    <cfRule type="duplicateValues" dxfId="423" priority="571"/>
-    <cfRule type="duplicateValues" dxfId="422" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="582"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N127">
-    <cfRule type="duplicateValues" dxfId="421" priority="413"/>
-    <cfRule type="duplicateValues" dxfId="420" priority="414"/>
-    <cfRule type="duplicateValues" dxfId="419" priority="415"/>
-    <cfRule type="duplicateValues" dxfId="418" priority="416"/>
-    <cfRule type="duplicateValues" dxfId="417" priority="417"/>
-    <cfRule type="duplicateValues" dxfId="416" priority="418"/>
-    <cfRule type="duplicateValues" dxfId="415" priority="419"/>
-    <cfRule type="duplicateValues" dxfId="414" priority="420"/>
-    <cfRule type="duplicateValues" dxfId="413" priority="421"/>
-    <cfRule type="duplicateValues" dxfId="412" priority="422"/>
-    <cfRule type="duplicateValues" dxfId="411" priority="423"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="436"/>
+    <cfRule type="duplicateValues" dxfId="439" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="433"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="432"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="440"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="441"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="442"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="434"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="439"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="437"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="438"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N130">
-    <cfRule type="duplicateValues" dxfId="410" priority="832"/>
-    <cfRule type="duplicateValues" dxfId="409" priority="833"/>
-    <cfRule type="duplicateValues" dxfId="408" priority="834"/>
-    <cfRule type="duplicateValues" dxfId="407" priority="835"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="836"/>
-    <cfRule type="duplicateValues" dxfId="405" priority="837"/>
-    <cfRule type="duplicateValues" dxfId="404" priority="838"/>
-    <cfRule type="duplicateValues" dxfId="403" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="858"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="855"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="857"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N144">
-    <cfRule type="duplicateValues" dxfId="402" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="401" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="400" priority="221"/>
-    <cfRule type="duplicateValues" dxfId="399" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="398" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="397" priority="224"/>
-    <cfRule type="duplicateValues" dxfId="396" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="395" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="393" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="392" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="391" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="246"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="414" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="241"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N146:N147">
-    <cfRule type="duplicateValues" dxfId="390" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="250"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N148">
-    <cfRule type="duplicateValues" dxfId="389" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="388" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="387" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="160"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N155">
-    <cfRule type="duplicateValues" dxfId="386" priority="680"/>
-    <cfRule type="duplicateValues" dxfId="385" priority="681"/>
-    <cfRule type="duplicateValues" dxfId="384" priority="682"/>
-    <cfRule type="duplicateValues" dxfId="383" priority="683"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="684"/>
-    <cfRule type="duplicateValues" dxfId="381" priority="685"/>
-    <cfRule type="duplicateValues" dxfId="380" priority="686"/>
-    <cfRule type="duplicateValues" dxfId="379" priority="687"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="688"/>
-    <cfRule type="duplicateValues" dxfId="377" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="705"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="704"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="701"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="703"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N156">
-    <cfRule type="duplicateValues" dxfId="376" priority="645"/>
-    <cfRule type="duplicateValues" dxfId="375" priority="646"/>
-    <cfRule type="duplicateValues" dxfId="374" priority="647"/>
-    <cfRule type="duplicateValues" dxfId="373" priority="648"/>
-    <cfRule type="duplicateValues" dxfId="372" priority="649"/>
-    <cfRule type="duplicateValues" dxfId="371" priority="650"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="651"/>
-    <cfRule type="duplicateValues" dxfId="369" priority="652"/>
-    <cfRule type="duplicateValues" dxfId="368" priority="653"/>
-    <cfRule type="duplicateValues" dxfId="367" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="366" priority="655"/>
-    <cfRule type="duplicateValues" dxfId="365" priority="656"/>
-    <cfRule type="duplicateValues" dxfId="364" priority="657"/>
-    <cfRule type="duplicateValues" dxfId="363" priority="658"/>
-    <cfRule type="duplicateValues" dxfId="362" priority="659"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="660"/>
-    <cfRule type="duplicateValues" dxfId="360" priority="661"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="663"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="664"/>
-    <cfRule type="duplicateValues" dxfId="356" priority="665"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="666"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="667"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="668"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="671"/>
-    <cfRule type="duplicateValues" dxfId="349" priority="672"/>
-    <cfRule type="duplicateValues" dxfId="348" priority="673"/>
-    <cfRule type="duplicateValues" dxfId="347" priority="674"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="675"/>
-    <cfRule type="duplicateValues" dxfId="345" priority="676"/>
-    <cfRule type="duplicateValues" dxfId="344" priority="677"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="678"/>
-    <cfRule type="duplicateValues" dxfId="342" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="698"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="693"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="679"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="686"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="668"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="672"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="690"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N183">
-    <cfRule type="duplicateValues" dxfId="341" priority="174"/>
-    <cfRule type="duplicateValues" dxfId="340" priority="175"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="176"/>
-    <cfRule type="duplicateValues" dxfId="338" priority="177"/>
-    <cfRule type="duplicateValues" dxfId="337" priority="178"/>
-    <cfRule type="duplicateValues" dxfId="336" priority="179"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="181"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="182"/>
-    <cfRule type="duplicateValues" dxfId="332" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="329" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="326" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="325" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="324" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="192"/>
-    <cfRule type="duplicateValues" dxfId="322" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="321" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="202"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="211"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N193">
-    <cfRule type="duplicateValues" dxfId="320" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="314" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="225"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="216"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N204">
-    <cfRule type="duplicateValues" dxfId="308" priority="756"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="757"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="759"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="760"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="761"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="762"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="775"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N205">
-    <cfRule type="duplicateValues" dxfId="300" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="275"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N206">
-    <cfRule type="duplicateValues" dxfId="288" priority="963"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="982"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N207">
-    <cfRule type="duplicateValues" dxfId="286" priority="883"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="884"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="885"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="886"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="887"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="888"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="889"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="907"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N212:N213">
-    <cfRule type="duplicateValues" dxfId="278" priority="1026"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="1027"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="1028"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="1029"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="1030"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="1050"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="1049"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="1048"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="1046"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="1045"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="1047"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N239">
-    <cfRule type="duplicateValues" dxfId="272" priority="936"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="937"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="938"/>
-    <cfRule type="duplicateValues" dxfId="269" priority="939"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="940"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="941"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="942"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="960"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="957"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="956"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="961"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="958"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="959"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="955"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N246">
-    <cfRule type="duplicateValues" dxfId="265" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="264" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="263" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N259">
-    <cfRule type="duplicateValues" dxfId="253" priority="804"/>
-    <cfRule type="duplicateValues" dxfId="252" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="806"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="823"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="825"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N278">
-    <cfRule type="duplicateValues" dxfId="249" priority="543"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="544"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="545"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="546"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="547"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="548"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="549"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="550"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="551"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="571"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="566"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="565"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N282">
-    <cfRule type="duplicateValues" dxfId="239" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="236" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="232" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="58"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N292">
-    <cfRule type="duplicateValues" dxfId="229" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="443"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N302">
-    <cfRule type="duplicateValues" dxfId="228" priority="796"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="797"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="798"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="799"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="801"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="802"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="822"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="817"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="818"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N303">
-    <cfRule type="duplicateValues" dxfId="220" priority="740"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="741"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="742"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="743"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="744"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="745"/>
-    <cfRule type="duplicateValues" dxfId="214" priority="746"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="747"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="766"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="759"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="761"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="765"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6:Q9">
-    <cfRule type="duplicateValues" dxfId="212" priority="968"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="969"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="970"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="971"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="972"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="973"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q14">
-    <cfRule type="duplicateValues" dxfId="205" priority="707"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="708"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="709"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="710"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="711"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="712"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="713"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="733"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="731"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="729"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="727"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q20">
-    <cfRule type="duplicateValues" dxfId="197" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="497"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="498"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="499"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="502"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="503"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="504"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="524"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="522"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q29">
-    <cfRule type="duplicateValues" dxfId="187" priority="1006"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="1007"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="1008"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="1009"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="1010"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="1011"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="1025"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="1026"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="1027"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="1030"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q93">
-    <cfRule type="duplicateValues" dxfId="180" priority="1035"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="1036"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="1037"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="1057"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q95">
-    <cfRule type="duplicateValues" dxfId="176" priority="816"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="817"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="818"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="819"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="820"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="821"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="822"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="823"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="838"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="837"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="836"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="835"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q101:Q102">
-    <cfRule type="duplicateValues" dxfId="168" priority="573"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="574"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="575"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="576"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="577"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="578"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="579"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="580"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="581"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="600"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="601"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="599"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q128">
-    <cfRule type="duplicateValues" dxfId="158" priority="425"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="426"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="427"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="428"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="429"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="430"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="431"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="432"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="433"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="434"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="435"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="445"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="451"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="452"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="453"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="447"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="444"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="454"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="450"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="449"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="448"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q156">
-    <cfRule type="duplicateValues" dxfId="147" priority="635"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="636"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="637"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="638"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="639"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="640"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="641"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="642"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="643"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q169">
-    <cfRule type="duplicateValues" dxfId="137" priority="953"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="954"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="973"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q172">
-    <cfRule type="duplicateValues" dxfId="135" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="133" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="132" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="124" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="38"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q239">
-    <cfRule type="duplicateValues" dxfId="123" priority="824"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="825"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="826"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="827"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="828"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="829"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="830"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="843"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="846"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q259">
-    <cfRule type="duplicateValues" dxfId="115" priority="985"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="986"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="987"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="988"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="989"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="990"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="1008"/>
+    <cfRule type="duplicateValues" dxfId="133" priority="1004"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="1009"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="1006"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="1007"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q276:Q277">
-    <cfRule type="duplicateValues" dxfId="108" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="124" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="254"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T19">
-    <cfRule type="duplicateValues" dxfId="96" priority="533"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="534"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="535"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="536"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="537"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="538"/>
-    <cfRule type="duplicateValues" dxfId="90" priority="539"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="540"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="541"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="542"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="561"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="553"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T20">
-    <cfRule type="duplicateValues" dxfId="86" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="343"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="344"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="345"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="78" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="365"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="367"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="362"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="359"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T23">
-    <cfRule type="duplicateValues" dxfId="76" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="489"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="490"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="491"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="494"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="507"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="511"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="506"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T169">
+    <cfRule type="duplicateValues" dxfId="85" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T172">
-    <cfRule type="duplicateValues" dxfId="66" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="61" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="78" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="30"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T206">
-    <cfRule type="duplicateValues" dxfId="54" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="287"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="296"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W19">
-    <cfRule type="duplicateValues" dxfId="42" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="330"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="333"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="36" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="336"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="337"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="350"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W68">
-    <cfRule type="duplicateValues" dxfId="31" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="245"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="26" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="250"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="267"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="266"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W135:W136">
-    <cfRule type="duplicateValues" dxfId="19" priority="437"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="438"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="439"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="440"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="441"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="442"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="443"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="444"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="445"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="446"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="462"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="464"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="461"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="460"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="459"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="458"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="465"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="463"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="457"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="W172">
+    <cfRule type="duplicateValues" dxfId="21" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="10"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W310">
-    <cfRule type="duplicateValues" dxfId="9" priority="447"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="448"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="449"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="450"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="451"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="452"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="453"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="454"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="455"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="456"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="472"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="471"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="470"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="469"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="468"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="467"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="466"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/新旧料号.xlsx
+++ b/新旧料号.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Documents\WXWork\1688855728724396\WeDrive\赛卓电子科技(上海)股份有限公司\交付体系\05OP\06 - 主计划\新旧料号对照表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\wenqiang.ding\Desktop\0407\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA7FBF49-A55A-4BDC-BD7B-28E68A331281}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0E0FB4E-2B5D-4038-B5DA-4AF4B1613BFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26262,1382 +26262,1382 @@
   <autoFilter ref="A1:W339" xr:uid="{C88C89EB-B21D-4698-AC40-3A2D469B1E42}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B1">
-    <cfRule type="duplicateValues" dxfId="1087" priority="1222"/>
-    <cfRule type="duplicateValues" dxfId="1086" priority="1223"/>
-    <cfRule type="duplicateValues" dxfId="1085" priority="1225"/>
-    <cfRule type="duplicateValues" dxfId="1084" priority="1227"/>
-    <cfRule type="duplicateValues" dxfId="1083" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="1087" priority="1223"/>
+    <cfRule type="duplicateValues" dxfId="1086" priority="1222"/>
+    <cfRule type="duplicateValues" dxfId="1085" priority="1227"/>
+    <cfRule type="duplicateValues" dxfId="1084" priority="1229"/>
+    <cfRule type="duplicateValues" dxfId="1083" priority="1225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1">
-    <cfRule type="duplicateValues" dxfId="1082" priority="1200"/>
-    <cfRule type="duplicateValues" dxfId="1081" priority="1202"/>
-    <cfRule type="duplicateValues" dxfId="1080" priority="1207"/>
-    <cfRule type="duplicateValues" dxfId="1079" priority="1209"/>
-    <cfRule type="duplicateValues" dxfId="1078" priority="1212"/>
-    <cfRule type="duplicateValues" dxfId="1077" priority="1214"/>
-    <cfRule type="duplicateValues" dxfId="1076" priority="1216"/>
-    <cfRule type="duplicateValues" dxfId="1075" priority="1218"/>
+    <cfRule type="duplicateValues" dxfId="1082" priority="1209"/>
+    <cfRule type="duplicateValues" dxfId="1081" priority="1212"/>
+    <cfRule type="duplicateValues" dxfId="1080" priority="1218"/>
+    <cfRule type="duplicateValues" dxfId="1079" priority="1200"/>
+    <cfRule type="duplicateValues" dxfId="1078" priority="1216"/>
+    <cfRule type="duplicateValues" dxfId="1077" priority="1207"/>
+    <cfRule type="duplicateValues" dxfId="1076" priority="1214"/>
+    <cfRule type="duplicateValues" dxfId="1075" priority="1202"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7">
+    <cfRule type="duplicateValues" dxfId="1074" priority="5"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C11">
-    <cfRule type="duplicateValues" dxfId="1074" priority="1111"/>
+    <cfRule type="duplicateValues" dxfId="1073" priority="1111"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C48">
-    <cfRule type="duplicateValues" dxfId="1073" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="1072" priority="102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C152">
-    <cfRule type="duplicateValues" dxfId="1072" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="1071" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="1070" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="1069" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="1068" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="1067" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="1066" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="1065" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="1064" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="1063" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="1062" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="1061" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="1060" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="1059" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="1058" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="1057" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="1056" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="1055" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="1054" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="1053" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="1052" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="1051" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="1050" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="1049" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="1048" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="1047" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="1046" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="1045" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="1044" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="1043" priority="74"/>
-    <cfRule type="duplicateValues" dxfId="1042" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="1041" priority="76"/>
-    <cfRule type="duplicateValues" dxfId="1040" priority="77"/>
-    <cfRule type="duplicateValues" dxfId="1039" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="1038" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="1037" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="1036" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="1035" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="1034" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="1071" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="1070" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="1069" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="1068" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="1067" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="1066" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="1065" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="1064" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="1063" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="1062" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="1061" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="1060" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="1059" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="1058" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="1057" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="1056" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="1055" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="1054" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="1053" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="1052" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="1051" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="1050" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="1049" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="1048" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="1047" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="1046" priority="73"/>
+    <cfRule type="duplicateValues" dxfId="1045" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="1044" priority="75"/>
+    <cfRule type="duplicateValues" dxfId="1043" priority="76"/>
+    <cfRule type="duplicateValues" dxfId="1042" priority="77"/>
+    <cfRule type="duplicateValues" dxfId="1041" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="1040" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="1039" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="1038" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="1037" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="1036" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="1035" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="1034" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="1033" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C170">
-    <cfRule type="duplicateValues" dxfId="1033" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="1032" priority="87"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C174">
-    <cfRule type="duplicateValues" dxfId="1032" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="1031" priority="89"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C177">
-    <cfRule type="duplicateValues" dxfId="1031" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="1030" priority="84"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C217">
-    <cfRule type="duplicateValues" dxfId="1030" priority="1233"/>
+    <cfRule type="duplicateValues" dxfId="1029" priority="1233"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C219">
-    <cfRule type="duplicateValues" dxfId="1029" priority="1158"/>
-    <cfRule type="duplicateValues" dxfId="1028" priority="1159"/>
-    <cfRule type="duplicateValues" dxfId="1027" priority="1160"/>
-    <cfRule type="duplicateValues" dxfId="1026" priority="1161"/>
-    <cfRule type="duplicateValues" dxfId="1025" priority="1162"/>
-    <cfRule type="duplicateValues" dxfId="1024" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="1028" priority="1163"/>
+    <cfRule type="duplicateValues" dxfId="1027" priority="1158"/>
+    <cfRule type="duplicateValues" dxfId="1026" priority="1162"/>
+    <cfRule type="duplicateValues" dxfId="1025" priority="1161"/>
+    <cfRule type="duplicateValues" dxfId="1024" priority="1160"/>
+    <cfRule type="duplicateValues" dxfId="1023" priority="1159"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C248:C293 C1:C6 C295:C1048576 C12:C47 C175:C176 C171:C173 C178:C246 C49:C151 C153:C169 C8:C10">
-    <cfRule type="duplicateValues" dxfId="1023" priority="1143"/>
+    <cfRule type="duplicateValues" dxfId="1022" priority="1143"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C248:C293 F222:F239 C218 C220:C221 C1:C6 C240:C246 C295:C1048576 C12:C47 C175:C176 C171:C173 C178:C216 C49:C151 C153:C169 C8:C10">
-    <cfRule type="duplicateValues" dxfId="1022" priority="1196"/>
+    <cfRule type="duplicateValues" dxfId="1021" priority="1196"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C294">
-    <cfRule type="duplicateValues" dxfId="1021" priority="765"/>
-    <cfRule type="duplicateValues" dxfId="1020" priority="766"/>
-    <cfRule type="duplicateValues" dxfId="1019" priority="767"/>
-    <cfRule type="duplicateValues" dxfId="1018" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="1020" priority="768"/>
+    <cfRule type="duplicateValues" dxfId="1019" priority="765"/>
+    <cfRule type="duplicateValues" dxfId="1018" priority="767"/>
     <cfRule type="duplicateValues" dxfId="1017" priority="769"/>
+    <cfRule type="duplicateValues" dxfId="1016" priority="766"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1">
-    <cfRule type="duplicateValues" dxfId="1016" priority="1221"/>
+    <cfRule type="duplicateValues" dxfId="1015" priority="1221"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E1">
-    <cfRule type="duplicateValues" dxfId="1015" priority="1226"/>
-    <cfRule type="duplicateValues" dxfId="1014" priority="1228"/>
-    <cfRule type="duplicateValues" dxfId="1013" priority="1230"/>
-    <cfRule type="duplicateValues" dxfId="1012" priority="1231"/>
-    <cfRule type="duplicateValues" dxfId="1011" priority="1232"/>
+    <cfRule type="duplicateValues" dxfId="1014" priority="1231"/>
+    <cfRule type="duplicateValues" dxfId="1013" priority="1226"/>
+    <cfRule type="duplicateValues" dxfId="1012" priority="1228"/>
+    <cfRule type="duplicateValues" dxfId="1011" priority="1230"/>
+    <cfRule type="duplicateValues" dxfId="1010" priority="1232"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1">
-    <cfRule type="duplicateValues" dxfId="1010" priority="1199"/>
-    <cfRule type="duplicateValues" dxfId="1009" priority="1201"/>
-    <cfRule type="duplicateValues" dxfId="1008" priority="1203"/>
-    <cfRule type="duplicateValues" dxfId="1007" priority="1204"/>
-    <cfRule type="duplicateValues" dxfId="1006" priority="1205"/>
-    <cfRule type="duplicateValues" dxfId="1005" priority="1206"/>
-    <cfRule type="duplicateValues" dxfId="1004" priority="1208"/>
-    <cfRule type="duplicateValues" dxfId="1003" priority="1211"/>
-    <cfRule type="duplicateValues" dxfId="1002" priority="1213"/>
-    <cfRule type="duplicateValues" dxfId="1001" priority="1215"/>
-    <cfRule type="duplicateValues" dxfId="1000" priority="1217"/>
+    <cfRule type="duplicateValues" dxfId="1009" priority="1208"/>
+    <cfRule type="duplicateValues" dxfId="1008" priority="1206"/>
+    <cfRule type="duplicateValues" dxfId="1007" priority="1213"/>
+    <cfRule type="duplicateValues" dxfId="1006" priority="1204"/>
+    <cfRule type="duplicateValues" dxfId="1005" priority="1203"/>
+    <cfRule type="duplicateValues" dxfId="1004" priority="1201"/>
+    <cfRule type="duplicateValues" dxfId="1003" priority="1199"/>
+    <cfRule type="duplicateValues" dxfId="1002" priority="1211"/>
+    <cfRule type="duplicateValues" dxfId="1001" priority="1217"/>
+    <cfRule type="duplicateValues" dxfId="1000" priority="1215"/>
+    <cfRule type="duplicateValues" dxfId="999" priority="1205"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F7">
+    <cfRule type="duplicateValues" dxfId="998" priority="4"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F8">
-    <cfRule type="duplicateValues" dxfId="999" priority="495"/>
-    <cfRule type="duplicateValues" dxfId="998" priority="496"/>
-    <cfRule type="duplicateValues" dxfId="997" priority="497"/>
-    <cfRule type="duplicateValues" dxfId="996" priority="498"/>
-    <cfRule type="duplicateValues" dxfId="995" priority="499"/>
-    <cfRule type="duplicateValues" dxfId="994" priority="500"/>
-    <cfRule type="duplicateValues" dxfId="993" priority="501"/>
-    <cfRule type="duplicateValues" dxfId="992" priority="502"/>
-    <cfRule type="duplicateValues" dxfId="991" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="997" priority="502"/>
+    <cfRule type="duplicateValues" dxfId="996" priority="503"/>
+    <cfRule type="duplicateValues" dxfId="995" priority="516"/>
+    <cfRule type="duplicateValues" dxfId="994" priority="509"/>
+    <cfRule type="duplicateValues" dxfId="993" priority="508"/>
+    <cfRule type="duplicateValues" dxfId="992" priority="499"/>
+    <cfRule type="duplicateValues" dxfId="991" priority="507"/>
     <cfRule type="duplicateValues" dxfId="990" priority="504"/>
-    <cfRule type="duplicateValues" dxfId="989" priority="505"/>
-    <cfRule type="duplicateValues" dxfId="988" priority="506"/>
-    <cfRule type="duplicateValues" dxfId="987" priority="507"/>
-    <cfRule type="duplicateValues" dxfId="986" priority="508"/>
-    <cfRule type="duplicateValues" dxfId="985" priority="509"/>
-    <cfRule type="duplicateValues" dxfId="984" priority="510"/>
-    <cfRule type="duplicateValues" dxfId="983" priority="511"/>
-    <cfRule type="duplicateValues" dxfId="982" priority="512"/>
-    <cfRule type="duplicateValues" dxfId="981" priority="513"/>
-    <cfRule type="duplicateValues" dxfId="980" priority="514"/>
-    <cfRule type="duplicateValues" dxfId="979" priority="515"/>
-    <cfRule type="duplicateValues" dxfId="978" priority="516"/>
-    <cfRule type="duplicateValues" dxfId="977" priority="517"/>
-    <cfRule type="duplicateValues" dxfId="976" priority="518"/>
-    <cfRule type="duplicateValues" dxfId="975" priority="519"/>
-    <cfRule type="duplicateValues" dxfId="974" priority="520"/>
-    <cfRule type="duplicateValues" dxfId="973" priority="521"/>
-    <cfRule type="duplicateValues" dxfId="972" priority="522"/>
-    <cfRule type="duplicateValues" dxfId="971" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="989" priority="498"/>
+    <cfRule type="duplicateValues" dxfId="988" priority="497"/>
+    <cfRule type="duplicateValues" dxfId="987" priority="496"/>
+    <cfRule type="duplicateValues" dxfId="986" priority="495"/>
+    <cfRule type="duplicateValues" dxfId="985" priority="500"/>
+    <cfRule type="duplicateValues" dxfId="984" priority="512"/>
+    <cfRule type="duplicateValues" dxfId="983" priority="513"/>
+    <cfRule type="duplicateValues" dxfId="982" priority="514"/>
+    <cfRule type="duplicateValues" dxfId="981" priority="515"/>
+    <cfRule type="duplicateValues" dxfId="980" priority="505"/>
+    <cfRule type="duplicateValues" dxfId="979" priority="517"/>
+    <cfRule type="duplicateValues" dxfId="978" priority="518"/>
+    <cfRule type="duplicateValues" dxfId="977" priority="519"/>
+    <cfRule type="duplicateValues" dxfId="976" priority="520"/>
+    <cfRule type="duplicateValues" dxfId="975" priority="521"/>
+    <cfRule type="duplicateValues" dxfId="974" priority="522"/>
+    <cfRule type="duplicateValues" dxfId="973" priority="523"/>
+    <cfRule type="duplicateValues" dxfId="972" priority="506"/>
+    <cfRule type="duplicateValues" dxfId="971" priority="501"/>
+    <cfRule type="duplicateValues" dxfId="970" priority="510"/>
+    <cfRule type="duplicateValues" dxfId="969" priority="511"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F11">
-    <cfRule type="duplicateValues" dxfId="970" priority="1110"/>
+    <cfRule type="duplicateValues" dxfId="968" priority="1110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F12">
-    <cfRule type="duplicateValues" dxfId="969" priority="614"/>
-    <cfRule type="duplicateValues" dxfId="968" priority="615"/>
-    <cfRule type="duplicateValues" dxfId="967" priority="616"/>
-    <cfRule type="duplicateValues" dxfId="966" priority="617"/>
-    <cfRule type="duplicateValues" dxfId="965" priority="618"/>
-    <cfRule type="duplicateValues" dxfId="964" priority="619"/>
-    <cfRule type="duplicateValues" dxfId="963" priority="620"/>
-    <cfRule type="duplicateValues" dxfId="962" priority="621"/>
-    <cfRule type="duplicateValues" dxfId="961" priority="622"/>
-    <cfRule type="duplicateValues" dxfId="960" priority="623"/>
-    <cfRule type="duplicateValues" dxfId="959" priority="624"/>
-    <cfRule type="duplicateValues" dxfId="958" priority="625"/>
-    <cfRule type="duplicateValues" dxfId="957" priority="626"/>
-    <cfRule type="duplicateValues" dxfId="956" priority="627"/>
-    <cfRule type="duplicateValues" dxfId="955" priority="628"/>
-    <cfRule type="duplicateValues" dxfId="954" priority="629"/>
-    <cfRule type="duplicateValues" dxfId="953" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="967" priority="615"/>
+    <cfRule type="duplicateValues" dxfId="966" priority="614"/>
+    <cfRule type="duplicateValues" dxfId="965" priority="620"/>
+    <cfRule type="duplicateValues" dxfId="964" priority="626"/>
+    <cfRule type="duplicateValues" dxfId="963" priority="630"/>
+    <cfRule type="duplicateValues" dxfId="962" priority="629"/>
+    <cfRule type="duplicateValues" dxfId="961" priority="628"/>
+    <cfRule type="duplicateValues" dxfId="960" priority="627"/>
+    <cfRule type="duplicateValues" dxfId="959" priority="625"/>
+    <cfRule type="duplicateValues" dxfId="958" priority="624"/>
+    <cfRule type="duplicateValues" dxfId="957" priority="623"/>
+    <cfRule type="duplicateValues" dxfId="956" priority="622"/>
+    <cfRule type="duplicateValues" dxfId="955" priority="621"/>
+    <cfRule type="duplicateValues" dxfId="954" priority="619"/>
+    <cfRule type="duplicateValues" dxfId="953" priority="618"/>
+    <cfRule type="duplicateValues" dxfId="952" priority="617"/>
+    <cfRule type="duplicateValues" dxfId="951" priority="616"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15">
-    <cfRule type="duplicateValues" dxfId="952" priority="993"/>
-    <cfRule type="duplicateValues" dxfId="951" priority="994"/>
-    <cfRule type="duplicateValues" dxfId="950" priority="995"/>
-    <cfRule type="duplicateValues" dxfId="949" priority="996"/>
-    <cfRule type="duplicateValues" dxfId="948" priority="997"/>
-    <cfRule type="duplicateValues" dxfId="947" priority="998"/>
-    <cfRule type="duplicateValues" dxfId="946" priority="999"/>
+    <cfRule type="duplicateValues" dxfId="950" priority="998"/>
+    <cfRule type="duplicateValues" dxfId="949" priority="997"/>
+    <cfRule type="duplicateValues" dxfId="948" priority="996"/>
+    <cfRule type="duplicateValues" dxfId="947" priority="993"/>
+    <cfRule type="duplicateValues" dxfId="946" priority="994"/>
     <cfRule type="duplicateValues" dxfId="945" priority="1000"/>
+    <cfRule type="duplicateValues" dxfId="944" priority="995"/>
+    <cfRule type="duplicateValues" dxfId="943" priority="999"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F17">
-    <cfRule type="duplicateValues" dxfId="944" priority="473"/>
+    <cfRule type="duplicateValues" dxfId="942" priority="473"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="943" priority="193"/>
-    <cfRule type="duplicateValues" dxfId="942" priority="194"/>
-    <cfRule type="duplicateValues" dxfId="941" priority="195"/>
-    <cfRule type="duplicateValues" dxfId="940" priority="196"/>
-    <cfRule type="duplicateValues" dxfId="939" priority="197"/>
-    <cfRule type="duplicateValues" dxfId="938" priority="198"/>
-    <cfRule type="duplicateValues" dxfId="937" priority="199"/>
-    <cfRule type="duplicateValues" dxfId="936" priority="200"/>
-    <cfRule type="duplicateValues" dxfId="935" priority="201"/>
-    <cfRule type="duplicateValues" dxfId="934" priority="202"/>
-    <cfRule type="duplicateValues" dxfId="933" priority="203"/>
-    <cfRule type="duplicateValues" dxfId="932" priority="204"/>
-    <cfRule type="duplicateValues" dxfId="931" priority="205"/>
-    <cfRule type="duplicateValues" dxfId="930" priority="206"/>
-    <cfRule type="duplicateValues" dxfId="929" priority="207"/>
-    <cfRule type="duplicateValues" dxfId="928" priority="208"/>
-    <cfRule type="duplicateValues" dxfId="927" priority="209"/>
-    <cfRule type="duplicateValues" dxfId="926" priority="210"/>
-    <cfRule type="duplicateValues" dxfId="925" priority="211"/>
-    <cfRule type="duplicateValues" dxfId="924" priority="212"/>
-    <cfRule type="duplicateValues" dxfId="923" priority="213"/>
-    <cfRule type="duplicateValues" dxfId="922" priority="214"/>
-    <cfRule type="duplicateValues" dxfId="921" priority="215"/>
-    <cfRule type="duplicateValues" dxfId="920" priority="216"/>
-    <cfRule type="duplicateValues" dxfId="919" priority="217"/>
-    <cfRule type="duplicateValues" dxfId="918" priority="218"/>
-    <cfRule type="duplicateValues" dxfId="917" priority="219"/>
-    <cfRule type="duplicateValues" dxfId="916" priority="220"/>
-    <cfRule type="duplicateValues" dxfId="915" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="941" priority="193"/>
+    <cfRule type="duplicateValues" dxfId="940" priority="194"/>
+    <cfRule type="duplicateValues" dxfId="939" priority="218"/>
+    <cfRule type="duplicateValues" dxfId="938" priority="217"/>
+    <cfRule type="duplicateValues" dxfId="937" priority="216"/>
+    <cfRule type="duplicateValues" dxfId="936" priority="213"/>
+    <cfRule type="duplicateValues" dxfId="935" priority="212"/>
+    <cfRule type="duplicateValues" dxfId="934" priority="211"/>
+    <cfRule type="duplicateValues" dxfId="933" priority="210"/>
+    <cfRule type="duplicateValues" dxfId="932" priority="208"/>
+    <cfRule type="duplicateValues" dxfId="931" priority="201"/>
+    <cfRule type="duplicateValues" dxfId="930" priority="200"/>
+    <cfRule type="duplicateValues" dxfId="929" priority="199"/>
+    <cfRule type="duplicateValues" dxfId="928" priority="198"/>
+    <cfRule type="duplicateValues" dxfId="927" priority="197"/>
+    <cfRule type="duplicateValues" dxfId="926" priority="196"/>
+    <cfRule type="duplicateValues" dxfId="925" priority="195"/>
+    <cfRule type="duplicateValues" dxfId="924" priority="207"/>
+    <cfRule type="duplicateValues" dxfId="923" priority="215"/>
+    <cfRule type="duplicateValues" dxfId="922" priority="206"/>
+    <cfRule type="duplicateValues" dxfId="921" priority="205"/>
+    <cfRule type="duplicateValues" dxfId="920" priority="209"/>
+    <cfRule type="duplicateValues" dxfId="919" priority="214"/>
+    <cfRule type="duplicateValues" dxfId="918" priority="221"/>
+    <cfRule type="duplicateValues" dxfId="917" priority="220"/>
+    <cfRule type="duplicateValues" dxfId="916" priority="219"/>
+    <cfRule type="duplicateValues" dxfId="915" priority="204"/>
+    <cfRule type="duplicateValues" dxfId="914" priority="203"/>
+    <cfRule type="duplicateValues" dxfId="913" priority="202"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F21">
-    <cfRule type="duplicateValues" dxfId="914" priority="651"/>
-    <cfRule type="duplicateValues" dxfId="913" priority="652"/>
-    <cfRule type="duplicateValues" dxfId="912" priority="653"/>
-    <cfRule type="duplicateValues" dxfId="911" priority="654"/>
-    <cfRule type="duplicateValues" dxfId="910" priority="655"/>
-    <cfRule type="duplicateValues" dxfId="909" priority="656"/>
-    <cfRule type="duplicateValues" dxfId="908" priority="657"/>
-    <cfRule type="duplicateValues" dxfId="907" priority="658"/>
-    <cfRule type="duplicateValues" dxfId="906" priority="659"/>
-    <cfRule type="duplicateValues" dxfId="905" priority="660"/>
-    <cfRule type="duplicateValues" dxfId="904" priority="661"/>
-    <cfRule type="duplicateValues" dxfId="903" priority="662"/>
-    <cfRule type="duplicateValues" dxfId="902" priority="663"/>
-    <cfRule type="duplicateValues" dxfId="901" priority="664"/>
-    <cfRule type="duplicateValues" dxfId="900" priority="665"/>
-    <cfRule type="duplicateValues" dxfId="899" priority="666"/>
-    <cfRule type="duplicateValues" dxfId="898" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="912" priority="664"/>
+    <cfRule type="duplicateValues" dxfId="911" priority="663"/>
+    <cfRule type="duplicateValues" dxfId="910" priority="662"/>
+    <cfRule type="duplicateValues" dxfId="909" priority="661"/>
+    <cfRule type="duplicateValues" dxfId="908" priority="660"/>
+    <cfRule type="duplicateValues" dxfId="907" priority="659"/>
+    <cfRule type="duplicateValues" dxfId="906" priority="658"/>
+    <cfRule type="duplicateValues" dxfId="905" priority="667"/>
+    <cfRule type="duplicateValues" dxfId="904" priority="651"/>
+    <cfRule type="duplicateValues" dxfId="903" priority="666"/>
+    <cfRule type="duplicateValues" dxfId="902" priority="665"/>
+    <cfRule type="duplicateValues" dxfId="901" priority="653"/>
+    <cfRule type="duplicateValues" dxfId="900" priority="654"/>
+    <cfRule type="duplicateValues" dxfId="899" priority="655"/>
+    <cfRule type="duplicateValues" dxfId="898" priority="657"/>
+    <cfRule type="duplicateValues" dxfId="897" priority="652"/>
+    <cfRule type="duplicateValues" dxfId="896" priority="656"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F26">
-    <cfRule type="duplicateValues" dxfId="897" priority="251"/>
-    <cfRule type="duplicateValues" dxfId="896" priority="252"/>
-    <cfRule type="duplicateValues" dxfId="895" priority="253"/>
-    <cfRule type="duplicateValues" dxfId="894" priority="254"/>
-    <cfRule type="duplicateValues" dxfId="893" priority="255"/>
-    <cfRule type="duplicateValues" dxfId="892" priority="256"/>
-    <cfRule type="duplicateValues" dxfId="891" priority="257"/>
-    <cfRule type="duplicateValues" dxfId="890" priority="258"/>
-    <cfRule type="duplicateValues" dxfId="889" priority="259"/>
-    <cfRule type="duplicateValues" dxfId="888" priority="260"/>
-    <cfRule type="duplicateValues" dxfId="887" priority="261"/>
-    <cfRule type="duplicateValues" dxfId="886" priority="262"/>
-    <cfRule type="duplicateValues" dxfId="885" priority="263"/>
-    <cfRule type="duplicateValues" dxfId="884" priority="264"/>
-    <cfRule type="duplicateValues" dxfId="883" priority="265"/>
-    <cfRule type="duplicateValues" dxfId="882" priority="266"/>
-    <cfRule type="duplicateValues" dxfId="881" priority="267"/>
-    <cfRule type="duplicateValues" dxfId="880" priority="268"/>
-    <cfRule type="duplicateValues" dxfId="879" priority="269"/>
-    <cfRule type="duplicateValues" dxfId="878" priority="270"/>
-    <cfRule type="duplicateValues" dxfId="877" priority="271"/>
-    <cfRule type="duplicateValues" dxfId="876" priority="272"/>
-    <cfRule type="duplicateValues" dxfId="875" priority="273"/>
-    <cfRule type="duplicateValues" dxfId="874" priority="274"/>
-    <cfRule type="duplicateValues" dxfId="873" priority="275"/>
-    <cfRule type="duplicateValues" dxfId="872" priority="276"/>
-    <cfRule type="duplicateValues" dxfId="871" priority="277"/>
-    <cfRule type="duplicateValues" dxfId="870" priority="278"/>
-    <cfRule type="duplicateValues" dxfId="869" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="895" priority="268"/>
+    <cfRule type="duplicateValues" dxfId="894" priority="269"/>
+    <cfRule type="duplicateValues" dxfId="893" priority="270"/>
+    <cfRule type="duplicateValues" dxfId="892" priority="271"/>
+    <cfRule type="duplicateValues" dxfId="891" priority="272"/>
+    <cfRule type="duplicateValues" dxfId="890" priority="274"/>
+    <cfRule type="duplicateValues" dxfId="889" priority="275"/>
+    <cfRule type="duplicateValues" dxfId="888" priority="276"/>
+    <cfRule type="duplicateValues" dxfId="887" priority="277"/>
+    <cfRule type="duplicateValues" dxfId="886" priority="278"/>
+    <cfRule type="duplicateValues" dxfId="885" priority="279"/>
+    <cfRule type="duplicateValues" dxfId="884" priority="273"/>
+    <cfRule type="duplicateValues" dxfId="883" priority="251"/>
+    <cfRule type="duplicateValues" dxfId="882" priority="252"/>
+    <cfRule type="duplicateValues" dxfId="881" priority="253"/>
+    <cfRule type="duplicateValues" dxfId="880" priority="254"/>
+    <cfRule type="duplicateValues" dxfId="879" priority="255"/>
+    <cfRule type="duplicateValues" dxfId="878" priority="256"/>
+    <cfRule type="duplicateValues" dxfId="877" priority="257"/>
+    <cfRule type="duplicateValues" dxfId="876" priority="258"/>
+    <cfRule type="duplicateValues" dxfId="875" priority="259"/>
+    <cfRule type="duplicateValues" dxfId="874" priority="260"/>
+    <cfRule type="duplicateValues" dxfId="873" priority="261"/>
+    <cfRule type="duplicateValues" dxfId="872" priority="262"/>
+    <cfRule type="duplicateValues" dxfId="871" priority="263"/>
+    <cfRule type="duplicateValues" dxfId="870" priority="264"/>
+    <cfRule type="duplicateValues" dxfId="869" priority="265"/>
+    <cfRule type="duplicateValues" dxfId="868" priority="266"/>
+    <cfRule type="duplicateValues" dxfId="867" priority="267"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F93:F94">
-    <cfRule type="duplicateValues" dxfId="868" priority="883"/>
-    <cfRule type="duplicateValues" dxfId="867" priority="884"/>
+    <cfRule type="duplicateValues" dxfId="866" priority="883"/>
+    <cfRule type="duplicateValues" dxfId="865" priority="884"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F108:F109">
-    <cfRule type="duplicateValues" dxfId="866" priority="985"/>
-    <cfRule type="duplicateValues" dxfId="865" priority="986"/>
-    <cfRule type="duplicateValues" dxfId="864" priority="987"/>
-    <cfRule type="duplicateValues" dxfId="863" priority="988"/>
-    <cfRule type="duplicateValues" dxfId="862" priority="989"/>
-    <cfRule type="duplicateValues" dxfId="861" priority="990"/>
-    <cfRule type="duplicateValues" dxfId="860" priority="991"/>
-    <cfRule type="duplicateValues" dxfId="859" priority="992"/>
+    <cfRule type="duplicateValues" dxfId="864" priority="985"/>
+    <cfRule type="duplicateValues" dxfId="863" priority="990"/>
+    <cfRule type="duplicateValues" dxfId="862" priority="986"/>
+    <cfRule type="duplicateValues" dxfId="861" priority="991"/>
+    <cfRule type="duplicateValues" dxfId="860" priority="987"/>
+    <cfRule type="duplicateValues" dxfId="859" priority="988"/>
+    <cfRule type="duplicateValues" dxfId="858" priority="989"/>
+    <cfRule type="duplicateValues" dxfId="857" priority="992"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F129">
-    <cfRule type="duplicateValues" dxfId="858" priority="612"/>
-    <cfRule type="duplicateValues" dxfId="857" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="856" priority="613"/>
+    <cfRule type="duplicateValues" dxfId="855" priority="612"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F134">
-    <cfRule type="duplicateValues" dxfId="856" priority="538"/>
-    <cfRule type="duplicateValues" dxfId="855" priority="539"/>
-    <cfRule type="duplicateValues" dxfId="854" priority="540"/>
-    <cfRule type="duplicateValues" dxfId="853" priority="541"/>
-    <cfRule type="duplicateValues" dxfId="852" priority="542"/>
-    <cfRule type="duplicateValues" dxfId="851" priority="543"/>
-    <cfRule type="duplicateValues" dxfId="850" priority="544"/>
-    <cfRule type="duplicateValues" dxfId="849" priority="545"/>
-    <cfRule type="duplicateValues" dxfId="848" priority="546"/>
-    <cfRule type="duplicateValues" dxfId="847" priority="547"/>
-    <cfRule type="duplicateValues" dxfId="846" priority="548"/>
-    <cfRule type="duplicateValues" dxfId="845" priority="549"/>
-    <cfRule type="duplicateValues" dxfId="844" priority="550"/>
-    <cfRule type="duplicateValues" dxfId="843" priority="551"/>
-    <cfRule type="duplicateValues" dxfId="842" priority="552"/>
-    <cfRule type="duplicateValues" dxfId="841" priority="553"/>
-    <cfRule type="duplicateValues" dxfId="840" priority="554"/>
-    <cfRule type="duplicateValues" dxfId="839" priority="555"/>
-    <cfRule type="duplicateValues" dxfId="838" priority="556"/>
-    <cfRule type="duplicateValues" dxfId="837" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="854" priority="541"/>
+    <cfRule type="duplicateValues" dxfId="853" priority="552"/>
+    <cfRule type="duplicateValues" dxfId="852" priority="547"/>
+    <cfRule type="duplicateValues" dxfId="851" priority="553"/>
+    <cfRule type="duplicateValues" dxfId="850" priority="554"/>
+    <cfRule type="duplicateValues" dxfId="849" priority="555"/>
+    <cfRule type="duplicateValues" dxfId="848" priority="556"/>
+    <cfRule type="duplicateValues" dxfId="847" priority="557"/>
+    <cfRule type="duplicateValues" dxfId="846" priority="551"/>
+    <cfRule type="duplicateValues" dxfId="845" priority="545"/>
+    <cfRule type="duplicateValues" dxfId="844" priority="546"/>
+    <cfRule type="duplicateValues" dxfId="843" priority="540"/>
+    <cfRule type="duplicateValues" dxfId="842" priority="539"/>
+    <cfRule type="duplicateValues" dxfId="841" priority="550"/>
+    <cfRule type="duplicateValues" dxfId="840" priority="538"/>
+    <cfRule type="duplicateValues" dxfId="839" priority="548"/>
+    <cfRule type="duplicateValues" dxfId="838" priority="549"/>
+    <cfRule type="duplicateValues" dxfId="837" priority="544"/>
+    <cfRule type="duplicateValues" dxfId="836" priority="543"/>
+    <cfRule type="duplicateValues" dxfId="835" priority="542"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140">
-    <cfRule type="duplicateValues" dxfId="836" priority="846"/>
-    <cfRule type="duplicateValues" dxfId="835" priority="847"/>
+    <cfRule type="duplicateValues" dxfId="834" priority="846"/>
+    <cfRule type="duplicateValues" dxfId="833" priority="847"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F142">
-    <cfRule type="duplicateValues" dxfId="834" priority="835"/>
-    <cfRule type="duplicateValues" dxfId="833" priority="836"/>
     <cfRule type="duplicateValues" dxfId="832" priority="837"/>
-    <cfRule type="duplicateValues" dxfId="831" priority="838"/>
-    <cfRule type="duplicateValues" dxfId="830" priority="839"/>
-    <cfRule type="duplicateValues" dxfId="829" priority="840"/>
-    <cfRule type="duplicateValues" dxfId="828" priority="841"/>
-    <cfRule type="duplicateValues" dxfId="827" priority="842"/>
-    <cfRule type="duplicateValues" dxfId="826" priority="843"/>
+    <cfRule type="duplicateValues" dxfId="831" priority="839"/>
+    <cfRule type="duplicateValues" dxfId="830" priority="840"/>
+    <cfRule type="duplicateValues" dxfId="829" priority="841"/>
+    <cfRule type="duplicateValues" dxfId="828" priority="842"/>
+    <cfRule type="duplicateValues" dxfId="827" priority="843"/>
+    <cfRule type="duplicateValues" dxfId="826" priority="838"/>
     <cfRule type="duplicateValues" dxfId="825" priority="844"/>
+    <cfRule type="duplicateValues" dxfId="824" priority="835"/>
+    <cfRule type="duplicateValues" dxfId="823" priority="836"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F150">
-    <cfRule type="duplicateValues" dxfId="824" priority="292"/>
-    <cfRule type="duplicateValues" dxfId="823" priority="293"/>
-    <cfRule type="duplicateValues" dxfId="822" priority="294"/>
-    <cfRule type="duplicateValues" dxfId="821" priority="295"/>
-    <cfRule type="duplicateValues" dxfId="820" priority="296"/>
-    <cfRule type="duplicateValues" dxfId="819" priority="297"/>
-    <cfRule type="duplicateValues" dxfId="818" priority="298"/>
-    <cfRule type="duplicateValues" dxfId="817" priority="299"/>
-    <cfRule type="duplicateValues" dxfId="816" priority="300"/>
-    <cfRule type="duplicateValues" dxfId="815" priority="301"/>
-    <cfRule type="duplicateValues" dxfId="814" priority="302"/>
-    <cfRule type="duplicateValues" dxfId="813" priority="303"/>
-    <cfRule type="duplicateValues" dxfId="812" priority="304"/>
-    <cfRule type="duplicateValues" dxfId="811" priority="305"/>
-    <cfRule type="duplicateValues" dxfId="810" priority="306"/>
-    <cfRule type="duplicateValues" dxfId="809" priority="307"/>
-    <cfRule type="duplicateValues" dxfId="808" priority="308"/>
-    <cfRule type="duplicateValues" dxfId="807" priority="309"/>
-    <cfRule type="duplicateValues" dxfId="806" priority="310"/>
-    <cfRule type="duplicateValues" dxfId="805" priority="311"/>
-    <cfRule type="duplicateValues" dxfId="804" priority="312"/>
-    <cfRule type="duplicateValues" dxfId="803" priority="313"/>
-    <cfRule type="duplicateValues" dxfId="802" priority="314"/>
-    <cfRule type="duplicateValues" dxfId="801" priority="315"/>
-    <cfRule type="duplicateValues" dxfId="800" priority="316"/>
-    <cfRule type="duplicateValues" dxfId="799" priority="317"/>
-    <cfRule type="duplicateValues" dxfId="798" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="822" priority="292"/>
+    <cfRule type="duplicateValues" dxfId="821" priority="293"/>
+    <cfRule type="duplicateValues" dxfId="820" priority="294"/>
+    <cfRule type="duplicateValues" dxfId="819" priority="295"/>
+    <cfRule type="duplicateValues" dxfId="818" priority="301"/>
+    <cfRule type="duplicateValues" dxfId="817" priority="300"/>
+    <cfRule type="duplicateValues" dxfId="816" priority="303"/>
+    <cfRule type="duplicateValues" dxfId="815" priority="305"/>
+    <cfRule type="duplicateValues" dxfId="814" priority="296"/>
+    <cfRule type="duplicateValues" dxfId="813" priority="299"/>
+    <cfRule type="duplicateValues" dxfId="812" priority="310"/>
+    <cfRule type="duplicateValues" dxfId="811" priority="311"/>
+    <cfRule type="duplicateValues" dxfId="810" priority="304"/>
+    <cfRule type="duplicateValues" dxfId="809" priority="302"/>
+    <cfRule type="duplicateValues" dxfId="808" priority="298"/>
+    <cfRule type="duplicateValues" dxfId="807" priority="297"/>
+    <cfRule type="duplicateValues" dxfId="806" priority="306"/>
+    <cfRule type="duplicateValues" dxfId="805" priority="313"/>
+    <cfRule type="duplicateValues" dxfId="804" priority="314"/>
+    <cfRule type="duplicateValues" dxfId="803" priority="315"/>
+    <cfRule type="duplicateValues" dxfId="802" priority="316"/>
+    <cfRule type="duplicateValues" dxfId="801" priority="317"/>
+    <cfRule type="duplicateValues" dxfId="800" priority="318"/>
+    <cfRule type="duplicateValues" dxfId="799" priority="307"/>
+    <cfRule type="duplicateValues" dxfId="798" priority="308"/>
+    <cfRule type="duplicateValues" dxfId="797" priority="309"/>
+    <cfRule type="duplicateValues" dxfId="796" priority="312"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F151">
-    <cfRule type="duplicateValues" dxfId="797" priority="289"/>
-    <cfRule type="duplicateValues" dxfId="796" priority="290"/>
-    <cfRule type="duplicateValues" dxfId="795" priority="291"/>
+    <cfRule type="duplicateValues" dxfId="795" priority="289"/>
+    <cfRule type="duplicateValues" dxfId="794" priority="290"/>
+    <cfRule type="duplicateValues" dxfId="793" priority="291"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F170">
-    <cfRule type="duplicateValues" dxfId="794" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="792" priority="86"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F174">
-    <cfRule type="duplicateValues" dxfId="793" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="791" priority="88"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F176">
-    <cfRule type="duplicateValues" dxfId="792" priority="1096"/>
-    <cfRule type="duplicateValues" dxfId="791" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="790" priority="1097"/>
+    <cfRule type="duplicateValues" dxfId="789" priority="1096"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F177">
-    <cfRule type="duplicateValues" dxfId="790" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="788" priority="85"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F204:F206">
-    <cfRule type="duplicateValues" dxfId="789" priority="881"/>
-    <cfRule type="duplicateValues" dxfId="788" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="787" priority="882"/>
+    <cfRule type="duplicateValues" dxfId="786" priority="881"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F211">
-    <cfRule type="duplicateValues" dxfId="787" priority="909"/>
-    <cfRule type="duplicateValues" dxfId="786" priority="910"/>
-    <cfRule type="duplicateValues" dxfId="785" priority="911"/>
-    <cfRule type="duplicateValues" dxfId="784" priority="912"/>
-    <cfRule type="duplicateValues" dxfId="783" priority="913"/>
-    <cfRule type="duplicateValues" dxfId="782" priority="914"/>
-    <cfRule type="duplicateValues" dxfId="781" priority="915"/>
-    <cfRule type="duplicateValues" dxfId="780" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="785" priority="914"/>
+    <cfRule type="duplicateValues" dxfId="784" priority="915"/>
+    <cfRule type="duplicateValues" dxfId="783" priority="916"/>
+    <cfRule type="duplicateValues" dxfId="782" priority="909"/>
+    <cfRule type="duplicateValues" dxfId="781" priority="910"/>
+    <cfRule type="duplicateValues" dxfId="780" priority="911"/>
+    <cfRule type="duplicateValues" dxfId="779" priority="912"/>
+    <cfRule type="duplicateValues" dxfId="778" priority="913"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F247">
-    <cfRule type="duplicateValues" dxfId="779" priority="524"/>
-    <cfRule type="duplicateValues" dxfId="778" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="777" priority="525"/>
+    <cfRule type="duplicateValues" dxfId="776" priority="524"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F248:F282 F1:F6 F9:F16 F34:F54 F200:F246 F135:F142 F153:F169 F18 F284:F330 F332:F1048576 F27:F32 F20:F25 G48 F175:F176 F171:F173 F178:F198 F144:F148 F56:F133">
-    <cfRule type="duplicateValues" dxfId="777" priority="581"/>
+    <cfRule type="duplicateValues" dxfId="775" priority="581"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F266">
-    <cfRule type="duplicateValues" dxfId="776" priority="1127"/>
-    <cfRule type="duplicateValues" dxfId="775" priority="1128"/>
-    <cfRule type="duplicateValues" dxfId="774" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="774" priority="1127"/>
+    <cfRule type="duplicateValues" dxfId="773" priority="1129"/>
+    <cfRule type="duplicateValues" dxfId="772" priority="1128"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F277">
-    <cfRule type="duplicateValues" dxfId="773" priority="1190"/>
+    <cfRule type="duplicateValues" dxfId="771" priority="1190"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F282">
-    <cfRule type="duplicateValues" dxfId="772" priority="1010"/>
-    <cfRule type="duplicateValues" dxfId="771" priority="1011"/>
-    <cfRule type="duplicateValues" dxfId="770" priority="1012"/>
-    <cfRule type="duplicateValues" dxfId="769" priority="1013"/>
-    <cfRule type="duplicateValues" dxfId="768" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="770" priority="1013"/>
+    <cfRule type="duplicateValues" dxfId="769" priority="1017"/>
+    <cfRule type="duplicateValues" dxfId="768" priority="1016"/>
     <cfRule type="duplicateValues" dxfId="767" priority="1015"/>
-    <cfRule type="duplicateValues" dxfId="766" priority="1016"/>
-    <cfRule type="duplicateValues" dxfId="765" priority="1017"/>
-    <cfRule type="duplicateValues" dxfId="764" priority="1018"/>
-    <cfRule type="duplicateValues" dxfId="763" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="766" priority="1014"/>
+    <cfRule type="duplicateValues" dxfId="765" priority="1012"/>
+    <cfRule type="duplicateValues" dxfId="764" priority="1011"/>
+    <cfRule type="duplicateValues" dxfId="763" priority="1010"/>
+    <cfRule type="duplicateValues" dxfId="762" priority="1019"/>
+    <cfRule type="duplicateValues" dxfId="761" priority="1018"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F284:F330 F1:F6 F153:F169 F332:F1048576 F20:F25 G48 F175:F176 F171:F173 F178:F282 F27:F149 F8:F18">
-    <cfRule type="duplicateValues" dxfId="762" priority="425"/>
+    <cfRule type="duplicateValues" dxfId="760" priority="425"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F289">
-    <cfRule type="duplicateValues" dxfId="761" priority="1186"/>
+    <cfRule type="duplicateValues" dxfId="759" priority="1186"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F290">
-    <cfRule type="duplicateValues" dxfId="760" priority="1184"/>
+    <cfRule type="duplicateValues" dxfId="758" priority="1184"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F292">
-    <cfRule type="duplicateValues" dxfId="759" priority="1178"/>
+    <cfRule type="duplicateValues" dxfId="757" priority="1178"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F293">
-    <cfRule type="duplicateValues" dxfId="758" priority="1170"/>
+    <cfRule type="duplicateValues" dxfId="756" priority="1170"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F294">
-    <cfRule type="duplicateValues" dxfId="757" priority="748"/>
-    <cfRule type="duplicateValues" dxfId="756" priority="749"/>
-    <cfRule type="duplicateValues" dxfId="755" priority="750"/>
-    <cfRule type="duplicateValues" dxfId="754" priority="751"/>
-    <cfRule type="duplicateValues" dxfId="753" priority="752"/>
-    <cfRule type="duplicateValues" dxfId="752" priority="753"/>
-    <cfRule type="duplicateValues" dxfId="751" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="755" priority="748"/>
+    <cfRule type="duplicateValues" dxfId="754" priority="760"/>
+    <cfRule type="duplicateValues" dxfId="753" priority="758"/>
+    <cfRule type="duplicateValues" dxfId="752" priority="757"/>
+    <cfRule type="duplicateValues" dxfId="751" priority="756"/>
     <cfRule type="duplicateValues" dxfId="750" priority="755"/>
-    <cfRule type="duplicateValues" dxfId="749" priority="756"/>
-    <cfRule type="duplicateValues" dxfId="748" priority="757"/>
-    <cfRule type="duplicateValues" dxfId="747" priority="758"/>
-    <cfRule type="duplicateValues" dxfId="746" priority="759"/>
-    <cfRule type="duplicateValues" dxfId="745" priority="760"/>
-    <cfRule type="duplicateValues" dxfId="744" priority="761"/>
-    <cfRule type="duplicateValues" dxfId="743" priority="762"/>
-    <cfRule type="duplicateValues" dxfId="742" priority="763"/>
-    <cfRule type="duplicateValues" dxfId="741" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="749" priority="754"/>
+    <cfRule type="duplicateValues" dxfId="748" priority="752"/>
+    <cfRule type="duplicateValues" dxfId="747" priority="751"/>
+    <cfRule type="duplicateValues" dxfId="746" priority="750"/>
+    <cfRule type="duplicateValues" dxfId="745" priority="749"/>
+    <cfRule type="duplicateValues" dxfId="744" priority="753"/>
+    <cfRule type="duplicateValues" dxfId="743" priority="761"/>
+    <cfRule type="duplicateValues" dxfId="742" priority="764"/>
+    <cfRule type="duplicateValues" dxfId="741" priority="763"/>
+    <cfRule type="duplicateValues" dxfId="740" priority="762"/>
+    <cfRule type="duplicateValues" dxfId="739" priority="759"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F295:F320 F130:F133 F13:F16 F1:F6 F22:F25 F322:F330 F135:F141 F248:F282 F9:F11 F34:F54 F200:F246 F153:F169 F18 F284:F293 F332:F1048576 F27:F32 F20 G48 F175:F176 F171:F173 F178:F198 F144:F148 F56:F128">
-    <cfRule type="duplicateValues" dxfId="740" priority="845"/>
+    <cfRule type="duplicateValues" dxfId="738" priority="845"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F296">
-    <cfRule type="duplicateValues" dxfId="739" priority="1168"/>
+    <cfRule type="duplicateValues" dxfId="737" priority="1168"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F303:F304">
-    <cfRule type="duplicateValues" dxfId="738" priority="1104"/>
-    <cfRule type="duplicateValues" dxfId="737" priority="1105"/>
+    <cfRule type="duplicateValues" dxfId="736" priority="1104"/>
+    <cfRule type="duplicateValues" dxfId="735" priority="1105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F305:F306">
-    <cfRule type="duplicateValues" dxfId="736" priority="1102"/>
-    <cfRule type="duplicateValues" dxfId="735" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="734" priority="1103"/>
+    <cfRule type="duplicateValues" dxfId="733" priority="1102"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F309">
-    <cfRule type="duplicateValues" dxfId="734" priority="1089"/>
-    <cfRule type="duplicateValues" dxfId="733" priority="1090"/>
-    <cfRule type="duplicateValues" dxfId="732" priority="1091"/>
-    <cfRule type="duplicateValues" dxfId="731" priority="1092"/>
-    <cfRule type="duplicateValues" dxfId="730" priority="1093"/>
-    <cfRule type="duplicateValues" dxfId="729" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="732" priority="1092"/>
+    <cfRule type="duplicateValues" dxfId="731" priority="1091"/>
+    <cfRule type="duplicateValues" dxfId="730" priority="1090"/>
+    <cfRule type="duplicateValues" dxfId="729" priority="1089"/>
     <cfRule type="duplicateValues" dxfId="728" priority="1095"/>
+    <cfRule type="duplicateValues" dxfId="727" priority="1094"/>
+    <cfRule type="duplicateValues" dxfId="726" priority="1093"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F332">
-    <cfRule type="duplicateValues" dxfId="727" priority="849"/>
+    <cfRule type="duplicateValues" dxfId="725" priority="849"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 F31:F32 F1:F6 F307:F308 F295:F302 F161:F169 F310:F316 F110 F39:F54 F178:F198 F284:F293 F240:F246 F207:F210 G324 F336:F1048576 F326:F330 F141 F16 F267:F281 F212:F221 F22:F25 F13:F14 F112:F128 F130:F133 F319:F320 F322:F324 F135:F139 F248:F265 F9:F10 F34:F37 F200:F203 F153:F159 F18 F56:F92 F27:F29 F20 G48 F175 F171:F173 F144:F148 F95:F107">
-    <cfRule type="duplicateValues" dxfId="726" priority="1166"/>
+    <cfRule type="duplicateValues" dxfId="724" priority="1166"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 F110 F39:F54 F161:F169 F207:F210 G324 F336:F1048576 F326:F330 F141 F284:F293 F16 F295:F316 F212:F246 F22:F25 F1:F6 F13:F14 F112:F128 F130:F133 F319:F320 F322:F324 F135:F139 F248:F281 F9:F11 F34:F37 F200:F203 F153:F159 F18 F56:F92 F27:F32 F20 G48 F175:F176 F171:F173 F178:F198 F144:F148 F95:F107">
-    <cfRule type="duplicateValues" dxfId="725" priority="1080"/>
+    <cfRule type="duplicateValues" dxfId="723" priority="1080"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 F297:F302 F295 F31:F32 F1:F6 F307:F308 F161:F169 F310:F316 F110 F39:F54 F178:F198 F284:F291 F240:F246 F207:F210 G324 F336:F1048576 F326:F330 F141 F16 F267:F281 F212:F221 F22:F25 F13:F14 F112:F128 F130:F133 F319:F320 F322:F324 F135:F139 F248:F265 F9:F10 F34:F37 F200:F203 F153:F159 F18 F56:F92 F27:F29 F20 G48 F175 F171:F173 F144:F148 F95:F107">
-    <cfRule type="duplicateValues" dxfId="724" priority="1179"/>
+    <cfRule type="duplicateValues" dxfId="722" priority="1179"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 F297:F302 F295 F31:F32 F1:F6 F307:F308 F161:F169 F310:F316 F110 F39:F54 F178:F198 F284:F292 F240:F246 F207:F210 G324 F336:F1048576 F326:F330 F141 F16 F267:F281 F212:F221 F22:F25 F13:F14 F112:F128 F130:F133 F319:F320 F322:F324 F135:F139 F248:F265 F9:F10 F34:F37 F200:F203 F153:F159 F18 F56:F92 F27:F29 F20 G48 F175 F171:F173 F144:F148 F95:F107">
-    <cfRule type="duplicateValues" dxfId="723" priority="1177"/>
+    <cfRule type="duplicateValues" dxfId="721" priority="1177"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 F297:F302 F295 F291 C218:C221 F267:F276 C1:C6 F31:F32 F1:F6 F307:F308 F161:F169 F310:F316 F110 F284:F288 F39:F54 F178:F198 G324 F336:F1048576 F326:F330 F16 F278:F281 C240:C246 F22:F25 F13:F14 F112:F133 F319:F320 F322:F324 F135:F141 F212:F265 C248:C293 F9:F10 F34:F37 F200:F210 F153:F159 C295:C1048576 F18 F27:F29 F20 C12:C47 G48 C175:C176 F175 C171:C173 F171:F173 C178:C216 C49:C151 C153:C169 F144:F148 F56:F107 C8:C10">
-    <cfRule type="duplicateValues" dxfId="722" priority="1198"/>
+    <cfRule type="duplicateValues" dxfId="720" priority="1198"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 F297:F302 F295 F291 F31:F32 F1:F6 F307:F308 F161:F169 F310:F316 F110 F39:F54 F178:F198 F284:F289 F240:F246 F207:F210 G324 F336:F1048576 F326:F330 F141 F16 F267:F281 F212:F221 F22:F25 F13:F14 F112:F128 F130:F133 F319:F320 F322:F324 F135:F139 F248:F265 F9:F10 F34:F37 F200:F203 F153:F159 F18 F56:F92 F27:F29 F20 G48 F175 F171:F173 F144:F148 F95:F107">
-    <cfRule type="duplicateValues" dxfId="721" priority="1185"/>
+    <cfRule type="duplicateValues" dxfId="719" priority="1185"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 F297:F302 F295 F291 F267:F276 F31:F32 F1:F6 F307:F308 F161:F169 F310:F316 F110 F39:F54 F178:F198 F284:F288 F240:F246 F207:F210 G324 F336:F1048576 F326:F330 F141 F16 F278:F281 F212:F221 F22:F25 F13:F14 F112:F128 F130:F133 F319:F320 F322:F324 F135:F139 F248:F265 F9:F10 F34:F37 F200:F203 F153:F159 F18 F56:F92 F27:F29 F20 G48 F175 F171:F173 F144:F148 F95:F107">
-    <cfRule type="duplicateValues" dxfId="720" priority="1194"/>
-    <cfRule type="duplicateValues" dxfId="719" priority="1195"/>
+    <cfRule type="duplicateValues" dxfId="718" priority="1194"/>
+    <cfRule type="duplicateValues" dxfId="717" priority="1195"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F333:F334 E325 G324 F336:F1048576 F326:F330 F141 F1:F6 F13:F16 F22:F25 F130:F133 F295:F320 F322:F324 F135:F139 F248:F282 F9:F11 F34:F54 F200:F246 F153:F169 F18 F284:F293 F27:F32 F20 G48 F175:F176 F171:F173 F178:F198 F144:F148 F56:F128">
-    <cfRule type="duplicateValues" dxfId="718" priority="850"/>
+    <cfRule type="duplicateValues" dxfId="716" priority="850"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F335">
-    <cfRule type="duplicateValues" dxfId="717" priority="848"/>
+    <cfRule type="duplicateValues" dxfId="715" priority="848"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F55:G55">
-    <cfRule type="duplicateValues" dxfId="716" priority="526"/>
+    <cfRule type="duplicateValues" dxfId="714" priority="526"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F152:G152">
-    <cfRule type="duplicateValues" dxfId="715" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="714" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="713" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="712" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="711" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="710" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="709" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="708" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="707" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="706" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="705" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="704" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="703" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="702" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="701" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="700" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="699" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="698" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="697" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="713" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="712" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="711" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="710" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="709" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="708" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="707" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="706" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="705" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="704" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="703" priority="32"/>
+    <cfRule type="duplicateValues" dxfId="702" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="701" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="700" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="699" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="698" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="697" priority="26"/>
     <cfRule type="duplicateValues" dxfId="696" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="695" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="694" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="693" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="692" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="691" priority="30"/>
-    <cfRule type="duplicateValues" dxfId="690" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="689" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="688" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="687" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="686" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="685" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="684" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="683" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="682" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="681" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="680" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="679" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="695" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="694" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="693" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="692" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="691" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="690" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="689" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="688" priority="17"/>
+    <cfRule type="duplicateValues" dxfId="687" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="686" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="685" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="684" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="683" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="682" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="681" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="680" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="679" priority="14"/>
     <cfRule type="duplicateValues" dxfId="678" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="677" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="677" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="676" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="675" priority="44"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F317:G317">
-    <cfRule type="duplicateValues" dxfId="676" priority="1009"/>
+    <cfRule type="duplicateValues" dxfId="674" priority="1009"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="G321:G322">
-    <cfRule type="duplicateValues" dxfId="675" priority="851"/>
+    <cfRule type="duplicateValues" dxfId="673" priority="851"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1">
-    <cfRule type="duplicateValues" dxfId="674" priority="1210"/>
-    <cfRule type="duplicateValues" dxfId="673" priority="1219"/>
-    <cfRule type="duplicateValues" dxfId="672" priority="1220"/>
+    <cfRule type="duplicateValues" dxfId="672" priority="1219"/>
+    <cfRule type="duplicateValues" dxfId="671" priority="1210"/>
+    <cfRule type="duplicateValues" dxfId="670" priority="1220"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J8">
+    <cfRule type="duplicateValues" dxfId="669" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J9">
+    <cfRule type="duplicateValues" dxfId="668" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J10">
+    <cfRule type="duplicateValues" dxfId="667" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J47">
-    <cfRule type="duplicateValues" dxfId="671" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="670" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="669" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="668" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="667" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="666" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="665" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="664" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="666" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="665" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="664" priority="99"/>
     <cfRule type="duplicateValues" dxfId="663" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="662" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="661" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="660" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="662" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="661" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="660" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="659" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="658" priority="92"/>
+    <cfRule type="duplicateValues" dxfId="657" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="656" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="655" priority="97"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J160">
-    <cfRule type="duplicateValues" dxfId="659" priority="770"/>
-    <cfRule type="duplicateValues" dxfId="658" priority="771"/>
-    <cfRule type="duplicateValues" dxfId="657" priority="772"/>
-    <cfRule type="duplicateValues" dxfId="656" priority="773"/>
-    <cfRule type="duplicateValues" dxfId="655" priority="774"/>
-    <cfRule type="duplicateValues" dxfId="654" priority="775"/>
-    <cfRule type="duplicateValues" dxfId="653" priority="776"/>
-    <cfRule type="duplicateValues" dxfId="652" priority="777"/>
-    <cfRule type="duplicateValues" dxfId="651" priority="778"/>
-    <cfRule type="duplicateValues" dxfId="650" priority="779"/>
+    <cfRule type="duplicateValues" dxfId="654" priority="776"/>
+    <cfRule type="duplicateValues" dxfId="653" priority="775"/>
+    <cfRule type="duplicateValues" dxfId="652" priority="774"/>
+    <cfRule type="duplicateValues" dxfId="651" priority="773"/>
+    <cfRule type="duplicateValues" dxfId="650" priority="772"/>
+    <cfRule type="duplicateValues" dxfId="649" priority="771"/>
+    <cfRule type="duplicateValues" dxfId="648" priority="770"/>
+    <cfRule type="duplicateValues" dxfId="647" priority="778"/>
+    <cfRule type="duplicateValues" dxfId="646" priority="777"/>
+    <cfRule type="duplicateValues" dxfId="645" priority="779"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J242">
-    <cfRule type="duplicateValues" dxfId="649" priority="1001"/>
-    <cfRule type="duplicateValues" dxfId="648" priority="1002"/>
-    <cfRule type="duplicateValues" dxfId="647" priority="1003"/>
-    <cfRule type="duplicateValues" dxfId="646" priority="1004"/>
-    <cfRule type="duplicateValues" dxfId="645" priority="1005"/>
-    <cfRule type="duplicateValues" dxfId="644" priority="1006"/>
-    <cfRule type="duplicateValues" dxfId="643" priority="1007"/>
+    <cfRule type="duplicateValues" dxfId="644" priority="1001"/>
+    <cfRule type="duplicateValues" dxfId="643" priority="1002"/>
     <cfRule type="duplicateValues" dxfId="642" priority="1008"/>
+    <cfRule type="duplicateValues" dxfId="641" priority="1003"/>
+    <cfRule type="duplicateValues" dxfId="640" priority="1007"/>
+    <cfRule type="duplicateValues" dxfId="639" priority="1006"/>
+    <cfRule type="duplicateValues" dxfId="638" priority="1005"/>
+    <cfRule type="duplicateValues" dxfId="637" priority="1004"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J253">
-    <cfRule type="duplicateValues" dxfId="641" priority="527"/>
-    <cfRule type="duplicateValues" dxfId="640" priority="528"/>
-    <cfRule type="duplicateValues" dxfId="639" priority="529"/>
-    <cfRule type="duplicateValues" dxfId="638" priority="530"/>
-    <cfRule type="duplicateValues" dxfId="637" priority="531"/>
-    <cfRule type="duplicateValues" dxfId="636" priority="532"/>
-    <cfRule type="duplicateValues" dxfId="635" priority="533"/>
-    <cfRule type="duplicateValues" dxfId="634" priority="534"/>
-    <cfRule type="duplicateValues" dxfId="633" priority="535"/>
-    <cfRule type="duplicateValues" dxfId="632" priority="536"/>
-    <cfRule type="duplicateValues" dxfId="631" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="636" priority="536"/>
+    <cfRule type="duplicateValues" dxfId="635" priority="537"/>
+    <cfRule type="duplicateValues" dxfId="634" priority="532"/>
+    <cfRule type="duplicateValues" dxfId="633" priority="531"/>
+    <cfRule type="duplicateValues" dxfId="632" priority="530"/>
+    <cfRule type="duplicateValues" dxfId="631" priority="529"/>
+    <cfRule type="duplicateValues" dxfId="630" priority="528"/>
+    <cfRule type="duplicateValues" dxfId="629" priority="527"/>
+    <cfRule type="duplicateValues" dxfId="628" priority="533"/>
+    <cfRule type="duplicateValues" dxfId="627" priority="534"/>
+    <cfRule type="duplicateValues" dxfId="626" priority="535"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J333:J1048576 J254:J278 J243:J252 J214:J241 J158 J280:J287 J289:J330 J1:J7 J161:J211 J48:J153 J11:J46">
-    <cfRule type="duplicateValues" dxfId="630" priority="1197"/>
+    <cfRule type="duplicateValues" dxfId="625" priority="1197"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:K1">
-    <cfRule type="duplicateValues" dxfId="629" priority="1224"/>
+    <cfRule type="duplicateValues" dxfId="624" priority="1224"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N16:N17">
-    <cfRule type="duplicateValues" dxfId="628" priority="1594"/>
-    <cfRule type="duplicateValues" dxfId="627" priority="1595"/>
-    <cfRule type="duplicateValues" dxfId="626" priority="1596"/>
-    <cfRule type="duplicateValues" dxfId="625" priority="1597"/>
-    <cfRule type="duplicateValues" dxfId="624" priority="1598"/>
-    <cfRule type="duplicateValues" dxfId="623" priority="1599"/>
-    <cfRule type="duplicateValues" dxfId="622" priority="1600"/>
-    <cfRule type="duplicateValues" dxfId="621" priority="1601"/>
+    <cfRule type="duplicateValues" dxfId="623" priority="1601"/>
+    <cfRule type="duplicateValues" dxfId="622" priority="1594"/>
+    <cfRule type="duplicateValues" dxfId="621" priority="1595"/>
+    <cfRule type="duplicateValues" dxfId="620" priority="1596"/>
+    <cfRule type="duplicateValues" dxfId="619" priority="1597"/>
+    <cfRule type="duplicateValues" dxfId="618" priority="1598"/>
+    <cfRule type="duplicateValues" dxfId="617" priority="1599"/>
+    <cfRule type="duplicateValues" dxfId="616" priority="1600"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N21">
-    <cfRule type="duplicateValues" dxfId="620" priority="668"/>
-    <cfRule type="duplicateValues" dxfId="619" priority="669"/>
-    <cfRule type="duplicateValues" dxfId="618" priority="670"/>
-    <cfRule type="duplicateValues" dxfId="617" priority="671"/>
-    <cfRule type="duplicateValues" dxfId="616" priority="672"/>
-    <cfRule type="duplicateValues" dxfId="615" priority="673"/>
-    <cfRule type="duplicateValues" dxfId="614" priority="674"/>
-    <cfRule type="duplicateValues" dxfId="613" priority="675"/>
-    <cfRule type="duplicateValues" dxfId="612" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="615" priority="670"/>
+    <cfRule type="duplicateValues" dxfId="614" priority="671"/>
+    <cfRule type="duplicateValues" dxfId="613" priority="669"/>
+    <cfRule type="duplicateValues" dxfId="612" priority="668"/>
     <cfRule type="duplicateValues" dxfId="611" priority="677"/>
+    <cfRule type="duplicateValues" dxfId="610" priority="676"/>
+    <cfRule type="duplicateValues" dxfId="609" priority="675"/>
+    <cfRule type="duplicateValues" dxfId="608" priority="674"/>
+    <cfRule type="duplicateValues" dxfId="607" priority="673"/>
+    <cfRule type="duplicateValues" dxfId="606" priority="672"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N22:N23">
-    <cfRule type="duplicateValues" dxfId="610" priority="860"/>
-    <cfRule type="duplicateValues" dxfId="609" priority="861"/>
-    <cfRule type="duplicateValues" dxfId="608" priority="862"/>
-    <cfRule type="duplicateValues" dxfId="607" priority="863"/>
-    <cfRule type="duplicateValues" dxfId="606" priority="864"/>
-    <cfRule type="duplicateValues" dxfId="605" priority="865"/>
-    <cfRule type="duplicateValues" dxfId="604" priority="866"/>
-    <cfRule type="duplicateValues" dxfId="603" priority="867"/>
-    <cfRule type="duplicateValues" dxfId="602" priority="868"/>
-    <cfRule type="duplicateValues" dxfId="601" priority="869"/>
-    <cfRule type="duplicateValues" dxfId="600" priority="870"/>
-    <cfRule type="duplicateValues" dxfId="599" priority="871"/>
-    <cfRule type="duplicateValues" dxfId="598" priority="872"/>
-    <cfRule type="duplicateValues" dxfId="597" priority="873"/>
-    <cfRule type="duplicateValues" dxfId="596" priority="874"/>
-    <cfRule type="duplicateValues" dxfId="595" priority="875"/>
-    <cfRule type="duplicateValues" dxfId="594" priority="876"/>
-    <cfRule type="duplicateValues" dxfId="593" priority="877"/>
-    <cfRule type="duplicateValues" dxfId="592" priority="878"/>
-    <cfRule type="duplicateValues" dxfId="591" priority="879"/>
-    <cfRule type="duplicateValues" dxfId="590" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="605" priority="871"/>
+    <cfRule type="duplicateValues" dxfId="604" priority="872"/>
+    <cfRule type="duplicateValues" dxfId="603" priority="873"/>
+    <cfRule type="duplicateValues" dxfId="602" priority="874"/>
+    <cfRule type="duplicateValues" dxfId="601" priority="875"/>
+    <cfRule type="duplicateValues" dxfId="600" priority="877"/>
+    <cfRule type="duplicateValues" dxfId="599" priority="878"/>
+    <cfRule type="duplicateValues" dxfId="598" priority="879"/>
+    <cfRule type="duplicateValues" dxfId="597" priority="862"/>
+    <cfRule type="duplicateValues" dxfId="596" priority="861"/>
+    <cfRule type="duplicateValues" dxfId="595" priority="860"/>
+    <cfRule type="duplicateValues" dxfId="594" priority="880"/>
+    <cfRule type="duplicateValues" dxfId="593" priority="876"/>
+    <cfRule type="duplicateValues" dxfId="592" priority="863"/>
+    <cfRule type="duplicateValues" dxfId="591" priority="864"/>
+    <cfRule type="duplicateValues" dxfId="590" priority="865"/>
+    <cfRule type="duplicateValues" dxfId="589" priority="866"/>
+    <cfRule type="duplicateValues" dxfId="588" priority="867"/>
+    <cfRule type="duplicateValues" dxfId="587" priority="868"/>
+    <cfRule type="duplicateValues" dxfId="586" priority="869"/>
+    <cfRule type="duplicateValues" dxfId="585" priority="870"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N25">
-    <cfRule type="duplicateValues" dxfId="589" priority="280"/>
-    <cfRule type="duplicateValues" dxfId="588" priority="281"/>
-    <cfRule type="duplicateValues" dxfId="587" priority="282"/>
-    <cfRule type="duplicateValues" dxfId="586" priority="283"/>
-    <cfRule type="duplicateValues" dxfId="585" priority="284"/>
-    <cfRule type="duplicateValues" dxfId="584" priority="285"/>
+    <cfRule type="duplicateValues" dxfId="584" priority="281"/>
+    <cfRule type="duplicateValues" dxfId="583" priority="283"/>
+    <cfRule type="duplicateValues" dxfId="582" priority="280"/>
+    <cfRule type="duplicateValues" dxfId="581" priority="282"/>
+    <cfRule type="duplicateValues" dxfId="580" priority="284"/>
+    <cfRule type="duplicateValues" dxfId="579" priority="285"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N26">
-    <cfRule type="duplicateValues" dxfId="583" priority="222"/>
-    <cfRule type="duplicateValues" dxfId="582" priority="223"/>
-    <cfRule type="duplicateValues" dxfId="581" priority="224"/>
-    <cfRule type="duplicateValues" dxfId="580" priority="225"/>
-    <cfRule type="duplicateValues" dxfId="579" priority="226"/>
-    <cfRule type="duplicateValues" dxfId="578" priority="227"/>
-    <cfRule type="duplicateValues" dxfId="577" priority="228"/>
-    <cfRule type="duplicateValues" dxfId="576" priority="229"/>
-    <cfRule type="duplicateValues" dxfId="575" priority="230"/>
-    <cfRule type="duplicateValues" dxfId="574" priority="231"/>
-    <cfRule type="duplicateValues" dxfId="573" priority="232"/>
-    <cfRule type="duplicateValues" dxfId="572" priority="233"/>
-    <cfRule type="duplicateValues" dxfId="571" priority="234"/>
-    <cfRule type="duplicateValues" dxfId="570" priority="235"/>
-    <cfRule type="duplicateValues" dxfId="569" priority="236"/>
-    <cfRule type="duplicateValues" dxfId="568" priority="237"/>
-    <cfRule type="duplicateValues" dxfId="567" priority="238"/>
-    <cfRule type="duplicateValues" dxfId="566" priority="239"/>
-    <cfRule type="duplicateValues" dxfId="565" priority="240"/>
-    <cfRule type="duplicateValues" dxfId="564" priority="241"/>
-    <cfRule type="duplicateValues" dxfId="563" priority="242"/>
-    <cfRule type="duplicateValues" dxfId="562" priority="243"/>
-    <cfRule type="duplicateValues" dxfId="561" priority="244"/>
-    <cfRule type="duplicateValues" dxfId="560" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="578" priority="231"/>
+    <cfRule type="duplicateValues" dxfId="577" priority="232"/>
+    <cfRule type="duplicateValues" dxfId="576" priority="233"/>
+    <cfRule type="duplicateValues" dxfId="575" priority="234"/>
+    <cfRule type="duplicateValues" dxfId="574" priority="235"/>
+    <cfRule type="duplicateValues" dxfId="573" priority="236"/>
+    <cfRule type="duplicateValues" dxfId="572" priority="237"/>
+    <cfRule type="duplicateValues" dxfId="571" priority="229"/>
+    <cfRule type="duplicateValues" dxfId="570" priority="238"/>
+    <cfRule type="duplicateValues" dxfId="569" priority="239"/>
+    <cfRule type="duplicateValues" dxfId="568" priority="240"/>
+    <cfRule type="duplicateValues" dxfId="567" priority="241"/>
+    <cfRule type="duplicateValues" dxfId="566" priority="242"/>
+    <cfRule type="duplicateValues" dxfId="565" priority="243"/>
+    <cfRule type="duplicateValues" dxfId="564" priority="245"/>
+    <cfRule type="duplicateValues" dxfId="563" priority="247"/>
+    <cfRule type="duplicateValues" dxfId="562" priority="248"/>
+    <cfRule type="duplicateValues" dxfId="561" priority="249"/>
+    <cfRule type="duplicateValues" dxfId="560" priority="250"/>
     <cfRule type="duplicateValues" dxfId="559" priority="246"/>
-    <cfRule type="duplicateValues" dxfId="558" priority="247"/>
-    <cfRule type="duplicateValues" dxfId="557" priority="248"/>
-    <cfRule type="duplicateValues" dxfId="556" priority="249"/>
-    <cfRule type="duplicateValues" dxfId="555" priority="250"/>
+    <cfRule type="duplicateValues" dxfId="558" priority="223"/>
+    <cfRule type="duplicateValues" dxfId="557" priority="230"/>
+    <cfRule type="duplicateValues" dxfId="556" priority="224"/>
+    <cfRule type="duplicateValues" dxfId="555" priority="222"/>
+    <cfRule type="duplicateValues" dxfId="554" priority="244"/>
+    <cfRule type="duplicateValues" dxfId="553" priority="228"/>
+    <cfRule type="duplicateValues" dxfId="552" priority="227"/>
+    <cfRule type="duplicateValues" dxfId="551" priority="226"/>
+    <cfRule type="duplicateValues" dxfId="550" priority="225"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N28">
-    <cfRule type="duplicateValues" dxfId="554" priority="1072"/>
-    <cfRule type="duplicateValues" dxfId="553" priority="1073"/>
-    <cfRule type="duplicateValues" dxfId="552" priority="1074"/>
-    <cfRule type="duplicateValues" dxfId="551" priority="1075"/>
-    <cfRule type="duplicateValues" dxfId="550" priority="1076"/>
-    <cfRule type="duplicateValues" dxfId="549" priority="1077"/>
-    <cfRule type="duplicateValues" dxfId="548" priority="1078"/>
-    <cfRule type="duplicateValues" dxfId="547" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="549" priority="1079"/>
+    <cfRule type="duplicateValues" dxfId="548" priority="1075"/>
+    <cfRule type="duplicateValues" dxfId="547" priority="1078"/>
+    <cfRule type="duplicateValues" dxfId="546" priority="1074"/>
+    <cfRule type="duplicateValues" dxfId="545" priority="1076"/>
+    <cfRule type="duplicateValues" dxfId="544" priority="1077"/>
+    <cfRule type="duplicateValues" dxfId="543" priority="1072"/>
+    <cfRule type="duplicateValues" dxfId="542" priority="1073"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N30">
-    <cfRule type="duplicateValues" dxfId="546" priority="1144"/>
-    <cfRule type="duplicateValues" dxfId="545" priority="1145"/>
-    <cfRule type="duplicateValues" dxfId="544" priority="1146"/>
-    <cfRule type="duplicateValues" dxfId="543" priority="1147"/>
-    <cfRule type="duplicateValues" dxfId="542" priority="1148"/>
-    <cfRule type="duplicateValues" dxfId="541" priority="1149"/>
-    <cfRule type="duplicateValues" dxfId="540" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="541" priority="1145"/>
+    <cfRule type="duplicateValues" dxfId="540" priority="1144"/>
+    <cfRule type="duplicateValues" dxfId="539" priority="1149"/>
+    <cfRule type="duplicateValues" dxfId="538" priority="1148"/>
+    <cfRule type="duplicateValues" dxfId="537" priority="1150"/>
+    <cfRule type="duplicateValues" dxfId="536" priority="1146"/>
+    <cfRule type="duplicateValues" dxfId="535" priority="1147"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N32">
-    <cfRule type="duplicateValues" dxfId="539" priority="170"/>
-    <cfRule type="duplicateValues" dxfId="538" priority="171"/>
-    <cfRule type="duplicateValues" dxfId="537" priority="172"/>
-    <cfRule type="duplicateValues" dxfId="536" priority="173"/>
-    <cfRule type="duplicateValues" dxfId="535" priority="174"/>
     <cfRule type="duplicateValues" dxfId="534" priority="175"/>
     <cfRule type="duplicateValues" dxfId="533" priority="176"/>
     <cfRule type="duplicateValues" dxfId="532" priority="177"/>
     <cfRule type="duplicateValues" dxfId="531" priority="178"/>
     <cfRule type="duplicateValues" dxfId="530" priority="179"/>
     <cfRule type="duplicateValues" dxfId="529" priority="180"/>
-    <cfRule type="duplicateValues" dxfId="528" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="528" priority="170"/>
+    <cfRule type="duplicateValues" dxfId="527" priority="181"/>
+    <cfRule type="duplicateValues" dxfId="526" priority="171"/>
+    <cfRule type="duplicateValues" dxfId="525" priority="172"/>
+    <cfRule type="duplicateValues" dxfId="524" priority="173"/>
+    <cfRule type="duplicateValues" dxfId="523" priority="174"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N33">
-    <cfRule type="duplicateValues" dxfId="527" priority="182"/>
+    <cfRule type="duplicateValues" dxfId="522" priority="182"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N34">
-    <cfRule type="duplicateValues" dxfId="526" priority="115"/>
-    <cfRule type="duplicateValues" dxfId="525" priority="116"/>
-    <cfRule type="duplicateValues" dxfId="524" priority="117"/>
-    <cfRule type="duplicateValues" dxfId="523" priority="118"/>
-    <cfRule type="duplicateValues" dxfId="522" priority="119"/>
-    <cfRule type="duplicateValues" dxfId="521" priority="120"/>
-    <cfRule type="duplicateValues" dxfId="520" priority="121"/>
-    <cfRule type="duplicateValues" dxfId="519" priority="122"/>
-    <cfRule type="duplicateValues" dxfId="518" priority="123"/>
-    <cfRule type="duplicateValues" dxfId="517" priority="124"/>
-    <cfRule type="duplicateValues" dxfId="516" priority="125"/>
-    <cfRule type="duplicateValues" dxfId="515" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="521" priority="123"/>
+    <cfRule type="duplicateValues" dxfId="520" priority="124"/>
+    <cfRule type="duplicateValues" dxfId="519" priority="115"/>
+    <cfRule type="duplicateValues" dxfId="518" priority="122"/>
+    <cfRule type="duplicateValues" dxfId="517" priority="121"/>
+    <cfRule type="duplicateValues" dxfId="516" priority="119"/>
+    <cfRule type="duplicateValues" dxfId="515" priority="118"/>
+    <cfRule type="duplicateValues" dxfId="514" priority="117"/>
+    <cfRule type="duplicateValues" dxfId="513" priority="120"/>
+    <cfRule type="duplicateValues" dxfId="512" priority="126"/>
+    <cfRule type="duplicateValues" dxfId="511" priority="125"/>
+    <cfRule type="duplicateValues" dxfId="510" priority="116"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N59">
-    <cfRule type="duplicateValues" dxfId="514" priority="1191"/>
-    <cfRule type="duplicateValues" dxfId="513" priority="1192"/>
-    <cfRule type="duplicateValues" dxfId="512" priority="1193"/>
+    <cfRule type="duplicateValues" dxfId="509" priority="1191"/>
+    <cfRule type="duplicateValues" dxfId="508" priority="1192"/>
+    <cfRule type="duplicateValues" dxfId="507" priority="1193"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N106">
-    <cfRule type="duplicateValues" dxfId="511" priority="893"/>
-    <cfRule type="duplicateValues" dxfId="510" priority="894"/>
-    <cfRule type="duplicateValues" dxfId="509" priority="895"/>
-    <cfRule type="duplicateValues" dxfId="508" priority="896"/>
-    <cfRule type="duplicateValues" dxfId="507" priority="897"/>
-    <cfRule type="duplicateValues" dxfId="506" priority="898"/>
-    <cfRule type="duplicateValues" dxfId="505" priority="899"/>
-    <cfRule type="duplicateValues" dxfId="504" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="506" priority="897"/>
+    <cfRule type="duplicateValues" dxfId="505" priority="898"/>
+    <cfRule type="duplicateValues" dxfId="504" priority="894"/>
+    <cfRule type="duplicateValues" dxfId="503" priority="893"/>
+    <cfRule type="duplicateValues" dxfId="502" priority="895"/>
+    <cfRule type="duplicateValues" dxfId="501" priority="899"/>
+    <cfRule type="duplicateValues" dxfId="500" priority="900"/>
+    <cfRule type="duplicateValues" dxfId="499" priority="896"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N110">
-    <cfRule type="duplicateValues" dxfId="503" priority="1036"/>
-    <cfRule type="duplicateValues" dxfId="502" priority="1037"/>
-    <cfRule type="duplicateValues" dxfId="501" priority="1038"/>
-    <cfRule type="duplicateValues" dxfId="500" priority="1039"/>
-    <cfRule type="duplicateValues" dxfId="499" priority="1040"/>
     <cfRule type="duplicateValues" dxfId="498" priority="1041"/>
-    <cfRule type="duplicateValues" dxfId="497" priority="1042"/>
-    <cfRule type="duplicateValues" dxfId="496" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="497" priority="1043"/>
+    <cfRule type="duplicateValues" dxfId="496" priority="1036"/>
+    <cfRule type="duplicateValues" dxfId="495" priority="1037"/>
+    <cfRule type="duplicateValues" dxfId="494" priority="1038"/>
+    <cfRule type="duplicateValues" dxfId="493" priority="1039"/>
+    <cfRule type="duplicateValues" dxfId="492" priority="1040"/>
+    <cfRule type="duplicateValues" dxfId="491" priority="1042"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N116">
-    <cfRule type="duplicateValues" dxfId="495" priority="698"/>
-    <cfRule type="duplicateValues" dxfId="494" priority="699"/>
-    <cfRule type="duplicateValues" dxfId="493" priority="700"/>
-    <cfRule type="duplicateValues" dxfId="492" priority="701"/>
-    <cfRule type="duplicateValues" dxfId="491" priority="702"/>
     <cfRule type="duplicateValues" dxfId="490" priority="703"/>
     <cfRule type="duplicateValues" dxfId="489" priority="704"/>
     <cfRule type="duplicateValues" dxfId="488" priority="705"/>
-    <cfRule type="duplicateValues" dxfId="487" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="487" priority="701"/>
     <cfRule type="duplicateValues" dxfId="486" priority="707"/>
+    <cfRule type="duplicateValues" dxfId="485" priority="702"/>
+    <cfRule type="duplicateValues" dxfId="484" priority="706"/>
+    <cfRule type="duplicateValues" dxfId="483" priority="700"/>
+    <cfRule type="duplicateValues" dxfId="482" priority="699"/>
+    <cfRule type="duplicateValues" dxfId="481" priority="698"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N126">
-    <cfRule type="duplicateValues" dxfId="485" priority="728"/>
-    <cfRule type="duplicateValues" dxfId="484" priority="729"/>
-    <cfRule type="duplicateValues" dxfId="483" priority="730"/>
-    <cfRule type="duplicateValues" dxfId="482" priority="731"/>
-    <cfRule type="duplicateValues" dxfId="481" priority="732"/>
-    <cfRule type="duplicateValues" dxfId="480" priority="733"/>
-    <cfRule type="duplicateValues" dxfId="479" priority="734"/>
-    <cfRule type="duplicateValues" dxfId="478" priority="735"/>
-    <cfRule type="duplicateValues" dxfId="477" priority="736"/>
-    <cfRule type="duplicateValues" dxfId="476" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="480" priority="728"/>
+    <cfRule type="duplicateValues" dxfId="479" priority="737"/>
+    <cfRule type="duplicateValues" dxfId="478" priority="736"/>
+    <cfRule type="duplicateValues" dxfId="477" priority="735"/>
+    <cfRule type="duplicateValues" dxfId="476" priority="734"/>
+    <cfRule type="duplicateValues" dxfId="475" priority="733"/>
+    <cfRule type="duplicateValues" dxfId="474" priority="732"/>
+    <cfRule type="duplicateValues" dxfId="473" priority="731"/>
+    <cfRule type="duplicateValues" dxfId="472" priority="730"/>
+    <cfRule type="duplicateValues" dxfId="471" priority="729"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N127:N128">
-    <cfRule type="duplicateValues" dxfId="475" priority="1052"/>
-    <cfRule type="duplicateValues" dxfId="474" priority="1053"/>
-    <cfRule type="duplicateValues" dxfId="473" priority="1054"/>
-    <cfRule type="duplicateValues" dxfId="472" priority="1055"/>
-    <cfRule type="duplicateValues" dxfId="471" priority="1056"/>
-    <cfRule type="duplicateValues" dxfId="470" priority="1057"/>
-    <cfRule type="duplicateValues" dxfId="469" priority="1058"/>
-    <cfRule type="duplicateValues" dxfId="468" priority="1059"/>
+    <cfRule type="duplicateValues" dxfId="470" priority="1054"/>
+    <cfRule type="duplicateValues" dxfId="469" priority="1052"/>
+    <cfRule type="duplicateValues" dxfId="468" priority="1053"/>
+    <cfRule type="duplicateValues" dxfId="467" priority="1055"/>
+    <cfRule type="duplicateValues" dxfId="466" priority="1056"/>
+    <cfRule type="duplicateValues" dxfId="465" priority="1057"/>
+    <cfRule type="duplicateValues" dxfId="464" priority="1058"/>
+    <cfRule type="duplicateValues" dxfId="463" priority="1059"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N131">
-    <cfRule type="duplicateValues" dxfId="467" priority="708"/>
-    <cfRule type="duplicateValues" dxfId="466" priority="709"/>
-    <cfRule type="duplicateValues" dxfId="465" priority="710"/>
-    <cfRule type="duplicateValues" dxfId="464" priority="711"/>
-    <cfRule type="duplicateValues" dxfId="463" priority="712"/>
-    <cfRule type="duplicateValues" dxfId="462" priority="713"/>
-    <cfRule type="duplicateValues" dxfId="461" priority="714"/>
-    <cfRule type="duplicateValues" dxfId="460" priority="715"/>
-    <cfRule type="duplicateValues" dxfId="459" priority="716"/>
-    <cfRule type="duplicateValues" dxfId="458" priority="717"/>
+    <cfRule type="duplicateValues" dxfId="462" priority="716"/>
+    <cfRule type="duplicateValues" dxfId="461" priority="715"/>
+    <cfRule type="duplicateValues" dxfId="460" priority="714"/>
+    <cfRule type="duplicateValues" dxfId="459" priority="713"/>
+    <cfRule type="duplicateValues" dxfId="458" priority="712"/>
+    <cfRule type="duplicateValues" dxfId="457" priority="710"/>
+    <cfRule type="duplicateValues" dxfId="456" priority="709"/>
+    <cfRule type="duplicateValues" dxfId="455" priority="708"/>
+    <cfRule type="duplicateValues" dxfId="454" priority="711"/>
+    <cfRule type="duplicateValues" dxfId="453" priority="717"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N134">
-    <cfRule type="duplicateValues" dxfId="457" priority="558"/>
-    <cfRule type="duplicateValues" dxfId="456" priority="559"/>
-    <cfRule type="duplicateValues" dxfId="455" priority="560"/>
-    <cfRule type="duplicateValues" dxfId="454" priority="561"/>
-    <cfRule type="duplicateValues" dxfId="453" priority="562"/>
-    <cfRule type="duplicateValues" dxfId="452" priority="563"/>
-    <cfRule type="duplicateValues" dxfId="451" priority="564"/>
-    <cfRule type="duplicateValues" dxfId="450" priority="565"/>
-    <cfRule type="duplicateValues" dxfId="449" priority="566"/>
-    <cfRule type="duplicateValues" dxfId="448" priority="567"/>
-    <cfRule type="duplicateValues" dxfId="447" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="452" priority="567"/>
+    <cfRule type="duplicateValues" dxfId="451" priority="568"/>
+    <cfRule type="duplicateValues" dxfId="450" priority="558"/>
+    <cfRule type="duplicateValues" dxfId="449" priority="560"/>
+    <cfRule type="duplicateValues" dxfId="448" priority="562"/>
+    <cfRule type="duplicateValues" dxfId="447" priority="563"/>
+    <cfRule type="duplicateValues" dxfId="446" priority="564"/>
+    <cfRule type="duplicateValues" dxfId="445" priority="565"/>
+    <cfRule type="duplicateValues" dxfId="444" priority="559"/>
+    <cfRule type="duplicateValues" dxfId="443" priority="566"/>
+    <cfRule type="duplicateValues" dxfId="442" priority="561"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N137">
-    <cfRule type="duplicateValues" dxfId="446" priority="977"/>
-    <cfRule type="duplicateValues" dxfId="445" priority="978"/>
-    <cfRule type="duplicateValues" dxfId="444" priority="979"/>
-    <cfRule type="duplicateValues" dxfId="443" priority="980"/>
-    <cfRule type="duplicateValues" dxfId="442" priority="981"/>
-    <cfRule type="duplicateValues" dxfId="441" priority="982"/>
-    <cfRule type="duplicateValues" dxfId="440" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="441" priority="977"/>
+    <cfRule type="duplicateValues" dxfId="440" priority="979"/>
     <cfRule type="duplicateValues" dxfId="439" priority="984"/>
+    <cfRule type="duplicateValues" dxfId="438" priority="983"/>
+    <cfRule type="duplicateValues" dxfId="437" priority="982"/>
+    <cfRule type="duplicateValues" dxfId="436" priority="981"/>
+    <cfRule type="duplicateValues" dxfId="435" priority="980"/>
+    <cfRule type="duplicateValues" dxfId="434" priority="978"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N147">
-    <cfRule type="duplicateValues" dxfId="438" priority="364"/>
-    <cfRule type="duplicateValues" dxfId="437" priority="365"/>
-    <cfRule type="duplicateValues" dxfId="436" priority="366"/>
-    <cfRule type="duplicateValues" dxfId="435" priority="367"/>
-    <cfRule type="duplicateValues" dxfId="434" priority="368"/>
-    <cfRule type="duplicateValues" dxfId="433" priority="369"/>
-    <cfRule type="duplicateValues" dxfId="432" priority="370"/>
-    <cfRule type="duplicateValues" dxfId="431" priority="371"/>
-    <cfRule type="duplicateValues" dxfId="430" priority="372"/>
-    <cfRule type="duplicateValues" dxfId="429" priority="373"/>
-    <cfRule type="duplicateValues" dxfId="428" priority="374"/>
-    <cfRule type="duplicateValues" dxfId="427" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="433" priority="370"/>
+    <cfRule type="duplicateValues" dxfId="432" priority="364"/>
+    <cfRule type="duplicateValues" dxfId="431" priority="372"/>
+    <cfRule type="duplicateValues" dxfId="430" priority="373"/>
+    <cfRule type="duplicateValues" dxfId="429" priority="374"/>
+    <cfRule type="duplicateValues" dxfId="428" priority="375"/>
+    <cfRule type="duplicateValues" dxfId="427" priority="369"/>
+    <cfRule type="duplicateValues" dxfId="426" priority="368"/>
+    <cfRule type="duplicateValues" dxfId="425" priority="367"/>
+    <cfRule type="duplicateValues" dxfId="424" priority="366"/>
+    <cfRule type="duplicateValues" dxfId="423" priority="371"/>
+    <cfRule type="duplicateValues" dxfId="422" priority="365"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N149:N150">
-    <cfRule type="duplicateValues" dxfId="426" priority="376"/>
+    <cfRule type="duplicateValues" dxfId="421" priority="376"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N151:N152">
-    <cfRule type="duplicateValues" dxfId="425" priority="286"/>
-    <cfRule type="duplicateValues" dxfId="424" priority="287"/>
-    <cfRule type="duplicateValues" dxfId="423" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="420" priority="286"/>
+    <cfRule type="duplicateValues" dxfId="419" priority="288"/>
+    <cfRule type="duplicateValues" dxfId="418" priority="287"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N159">
-    <cfRule type="duplicateValues" dxfId="422" priority="825"/>
-    <cfRule type="duplicateValues" dxfId="421" priority="826"/>
-    <cfRule type="duplicateValues" dxfId="420" priority="827"/>
-    <cfRule type="duplicateValues" dxfId="419" priority="828"/>
-    <cfRule type="duplicateValues" dxfId="418" priority="829"/>
-    <cfRule type="duplicateValues" dxfId="417" priority="830"/>
-    <cfRule type="duplicateValues" dxfId="416" priority="831"/>
-    <cfRule type="duplicateValues" dxfId="415" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="417" priority="826"/>
+    <cfRule type="duplicateValues" dxfId="416" priority="825"/>
+    <cfRule type="duplicateValues" dxfId="415" priority="828"/>
     <cfRule type="duplicateValues" dxfId="414" priority="833"/>
-    <cfRule type="duplicateValues" dxfId="413" priority="834"/>
+    <cfRule type="duplicateValues" dxfId="413" priority="829"/>
+    <cfRule type="duplicateValues" dxfId="412" priority="832"/>
+    <cfRule type="duplicateValues" dxfId="411" priority="831"/>
+    <cfRule type="duplicateValues" dxfId="410" priority="830"/>
+    <cfRule type="duplicateValues" dxfId="409" priority="827"/>
+    <cfRule type="duplicateValues" dxfId="408" priority="834"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N160">
-    <cfRule type="duplicateValues" dxfId="412" priority="790"/>
-    <cfRule type="duplicateValues" dxfId="411" priority="791"/>
-    <cfRule type="duplicateValues" dxfId="410" priority="792"/>
-    <cfRule type="duplicateValues" dxfId="409" priority="793"/>
-    <cfRule type="duplicateValues" dxfId="408" priority="794"/>
-    <cfRule type="duplicateValues" dxfId="407" priority="795"/>
-    <cfRule type="duplicateValues" dxfId="406" priority="796"/>
-    <cfRule type="duplicateValues" dxfId="405" priority="797"/>
-    <cfRule type="duplicateValues" dxfId="404" priority="798"/>
-    <cfRule type="duplicateValues" dxfId="403" priority="799"/>
-    <cfRule type="duplicateValues" dxfId="402" priority="800"/>
-    <cfRule type="duplicateValues" dxfId="401" priority="801"/>
-    <cfRule type="duplicateValues" dxfId="400" priority="802"/>
-    <cfRule type="duplicateValues" dxfId="399" priority="803"/>
-    <cfRule type="duplicateValues" dxfId="398" priority="804"/>
-    <cfRule type="duplicateValues" dxfId="397" priority="805"/>
-    <cfRule type="duplicateValues" dxfId="396" priority="806"/>
-    <cfRule type="duplicateValues" dxfId="395" priority="807"/>
-    <cfRule type="duplicateValues" dxfId="394" priority="808"/>
-    <cfRule type="duplicateValues" dxfId="393" priority="809"/>
-    <cfRule type="duplicateValues" dxfId="392" priority="810"/>
-    <cfRule type="duplicateValues" dxfId="391" priority="811"/>
-    <cfRule type="duplicateValues" dxfId="390" priority="812"/>
-    <cfRule type="duplicateValues" dxfId="389" priority="813"/>
-    <cfRule type="duplicateValues" dxfId="388" priority="814"/>
-    <cfRule type="duplicateValues" dxfId="387" priority="815"/>
-    <cfRule type="duplicateValues" dxfId="386" priority="816"/>
-    <cfRule type="duplicateValues" dxfId="385" priority="817"/>
-    <cfRule type="duplicateValues" dxfId="384" priority="818"/>
-    <cfRule type="duplicateValues" dxfId="383" priority="819"/>
-    <cfRule type="duplicateValues" dxfId="382" priority="820"/>
-    <cfRule type="duplicateValues" dxfId="381" priority="821"/>
-    <cfRule type="duplicateValues" dxfId="380" priority="822"/>
-    <cfRule type="duplicateValues" dxfId="379" priority="823"/>
-    <cfRule type="duplicateValues" dxfId="378" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="407" priority="822"/>
+    <cfRule type="duplicateValues" dxfId="406" priority="821"/>
+    <cfRule type="duplicateValues" dxfId="405" priority="819"/>
+    <cfRule type="duplicateValues" dxfId="404" priority="818"/>
+    <cfRule type="duplicateValues" dxfId="403" priority="816"/>
+    <cfRule type="duplicateValues" dxfId="402" priority="815"/>
+    <cfRule type="duplicateValues" dxfId="401" priority="814"/>
+    <cfRule type="duplicateValues" dxfId="400" priority="813"/>
+    <cfRule type="duplicateValues" dxfId="399" priority="791"/>
+    <cfRule type="duplicateValues" dxfId="398" priority="793"/>
+    <cfRule type="duplicateValues" dxfId="397" priority="794"/>
+    <cfRule type="duplicateValues" dxfId="396" priority="795"/>
+    <cfRule type="duplicateValues" dxfId="395" priority="796"/>
+    <cfRule type="duplicateValues" dxfId="394" priority="812"/>
+    <cfRule type="duplicateValues" dxfId="393" priority="797"/>
+    <cfRule type="duplicateValues" dxfId="392" priority="811"/>
+    <cfRule type="duplicateValues" dxfId="391" priority="810"/>
+    <cfRule type="duplicateValues" dxfId="390" priority="809"/>
+    <cfRule type="duplicateValues" dxfId="389" priority="808"/>
+    <cfRule type="duplicateValues" dxfId="388" priority="807"/>
+    <cfRule type="duplicateValues" dxfId="387" priority="806"/>
+    <cfRule type="duplicateValues" dxfId="386" priority="820"/>
+    <cfRule type="duplicateValues" dxfId="385" priority="804"/>
+    <cfRule type="duplicateValues" dxfId="384" priority="803"/>
+    <cfRule type="duplicateValues" dxfId="383" priority="802"/>
+    <cfRule type="duplicateValues" dxfId="382" priority="801"/>
+    <cfRule type="duplicateValues" dxfId="381" priority="798"/>
+    <cfRule type="duplicateValues" dxfId="380" priority="800"/>
+    <cfRule type="duplicateValues" dxfId="379" priority="799"/>
+    <cfRule type="duplicateValues" dxfId="378" priority="790"/>
+    <cfRule type="duplicateValues" dxfId="377" priority="824"/>
+    <cfRule type="duplicateValues" dxfId="376" priority="792"/>
+    <cfRule type="duplicateValues" dxfId="375" priority="805"/>
+    <cfRule type="duplicateValues" dxfId="374" priority="823"/>
+    <cfRule type="duplicateValues" dxfId="373" priority="817"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N191">
-    <cfRule type="duplicateValues" dxfId="377" priority="319"/>
-    <cfRule type="duplicateValues" dxfId="376" priority="320"/>
-    <cfRule type="duplicateValues" dxfId="375" priority="321"/>
-    <cfRule type="duplicateValues" dxfId="374" priority="322"/>
-    <cfRule type="duplicateValues" dxfId="373" priority="323"/>
-    <cfRule type="duplicateValues" dxfId="372" priority="324"/>
-    <cfRule type="duplicateValues" dxfId="371" priority="325"/>
-    <cfRule type="duplicateValues" dxfId="370" priority="326"/>
-    <cfRule type="duplicateValues" dxfId="369" priority="327"/>
-    <cfRule type="duplicateValues" dxfId="368" priority="328"/>
-    <cfRule type="duplicateValues" dxfId="367" priority="329"/>
-    <cfRule type="duplicateValues" dxfId="366" priority="330"/>
-    <cfRule type="duplicateValues" dxfId="365" priority="331"/>
-    <cfRule type="duplicateValues" dxfId="364" priority="332"/>
-    <cfRule type="duplicateValues" dxfId="363" priority="333"/>
-    <cfRule type="duplicateValues" dxfId="362" priority="334"/>
-    <cfRule type="duplicateValues" dxfId="361" priority="335"/>
-    <cfRule type="duplicateValues" dxfId="360" priority="336"/>
-    <cfRule type="duplicateValues" dxfId="359" priority="337"/>
-    <cfRule type="duplicateValues" dxfId="358" priority="338"/>
-    <cfRule type="duplicateValues" dxfId="357" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="372" priority="337"/>
+    <cfRule type="duplicateValues" dxfId="371" priority="336"/>
+    <cfRule type="duplicateValues" dxfId="370" priority="335"/>
+    <cfRule type="duplicateValues" dxfId="369" priority="334"/>
+    <cfRule type="duplicateValues" dxfId="368" priority="333"/>
+    <cfRule type="duplicateValues" dxfId="367" priority="326"/>
+    <cfRule type="duplicateValues" dxfId="366" priority="325"/>
+    <cfRule type="duplicateValues" dxfId="365" priority="324"/>
+    <cfRule type="duplicateValues" dxfId="364" priority="323"/>
+    <cfRule type="duplicateValues" dxfId="363" priority="332"/>
+    <cfRule type="duplicateValues" dxfId="362" priority="322"/>
+    <cfRule type="duplicateValues" dxfId="361" priority="321"/>
+    <cfRule type="duplicateValues" dxfId="360" priority="320"/>
+    <cfRule type="duplicateValues" dxfId="359" priority="319"/>
+    <cfRule type="duplicateValues" dxfId="358" priority="339"/>
+    <cfRule type="duplicateValues" dxfId="357" priority="338"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="327"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="331"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="330"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="329"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="328"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N201">
-    <cfRule type="duplicateValues" dxfId="356" priority="340"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="341"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="342"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="343"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="344"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="345"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="346"/>
-    <cfRule type="duplicateValues" dxfId="349" priority="347"/>
-    <cfRule type="duplicateValues" dxfId="348" priority="348"/>
-    <cfRule type="duplicateValues" dxfId="347" priority="349"/>
-    <cfRule type="duplicateValues" dxfId="346" priority="350"/>
-    <cfRule type="duplicateValues" dxfId="345" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="344"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="343"/>
+    <cfRule type="duplicateValues" dxfId="349" priority="342"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="346"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="347"/>
+    <cfRule type="duplicateValues" dxfId="346" priority="348"/>
+    <cfRule type="duplicateValues" dxfId="345" priority="349"/>
+    <cfRule type="duplicateValues" dxfId="344" priority="350"/>
+    <cfRule type="duplicateValues" dxfId="343" priority="351"/>
+    <cfRule type="duplicateValues" dxfId="342" priority="341"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="340"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="345"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N211">
-    <cfRule type="duplicateValues" dxfId="344" priority="901"/>
-    <cfRule type="duplicateValues" dxfId="343" priority="902"/>
-    <cfRule type="duplicateValues" dxfId="342" priority="903"/>
-    <cfRule type="duplicateValues" dxfId="341" priority="904"/>
-    <cfRule type="duplicateValues" dxfId="340" priority="905"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="906"/>
-    <cfRule type="duplicateValues" dxfId="338" priority="907"/>
-    <cfRule type="duplicateValues" dxfId="337" priority="908"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="907"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="906"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="905"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="904"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="903"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="901"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="902"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="908"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N212">
-    <cfRule type="duplicateValues" dxfId="336" priority="401"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="402"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="403"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="404"/>
-    <cfRule type="duplicateValues" dxfId="332" priority="405"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="406"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="407"/>
-    <cfRule type="duplicateValues" dxfId="329" priority="408"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="409"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="410"/>
-    <cfRule type="duplicateValues" dxfId="326" priority="411"/>
-    <cfRule type="duplicateValues" dxfId="325" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="412"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="408"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="407"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="406"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="405"/>
+    <cfRule type="duplicateValues" dxfId="326" priority="404"/>
+    <cfRule type="duplicateValues" dxfId="325" priority="411"/>
+    <cfRule type="duplicateValues" dxfId="324" priority="403"/>
+    <cfRule type="duplicateValues" dxfId="323" priority="402"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="409"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="401"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="410"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N213">
-    <cfRule type="duplicateValues" dxfId="324" priority="1108"/>
-    <cfRule type="duplicateValues" dxfId="323" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="1109"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="1108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N214">
-    <cfRule type="duplicateValues" dxfId="322" priority="1028"/>
-    <cfRule type="duplicateValues" dxfId="321" priority="1029"/>
-    <cfRule type="duplicateValues" dxfId="320" priority="1030"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="1031"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="1032"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="1033"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="1034"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="1032"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="1031"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="1030"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="1035"/>
+    <cfRule type="duplicateValues" dxfId="313" priority="1034"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="1028"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="1029"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="1033"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N219:N220">
-    <cfRule type="duplicateValues" dxfId="314" priority="1171"/>
-    <cfRule type="duplicateValues" dxfId="313" priority="1172"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="1173"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="1174"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="1175"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="1176"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="1173"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="1174"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="1176"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="1175"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="1171"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="1172"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N246">
-    <cfRule type="duplicateValues" dxfId="308" priority="1081"/>
-    <cfRule type="duplicateValues" dxfId="307" priority="1082"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="1083"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="1084"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="1085"/>
     <cfRule type="duplicateValues" dxfId="303" priority="1086"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="1081"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="1083"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="1084"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="1085"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="1087"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="1082"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N253">
-    <cfRule type="duplicateValues" dxfId="301" priority="352"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="353"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="354"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="355"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="356"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="357"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="358"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="359"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="360"/>
-    <cfRule type="duplicateValues" dxfId="292" priority="361"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="362"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="354"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="355"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="352"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="356"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="353"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="363"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="361"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="360"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="359"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="358"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="357"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="362"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N266">
-    <cfRule type="duplicateValues" dxfId="289" priority="949"/>
-    <cfRule type="duplicateValues" dxfId="288" priority="950"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="951"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="951"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="952"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="950"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="949"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N269">
-    <cfRule type="duplicateValues" dxfId="285" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="109"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="277" priority="111"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="112"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="113"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="110"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="111"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="112"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="113"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="114"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="105"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N285">
-    <cfRule type="duplicateValues" dxfId="273" priority="688"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="689"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="690"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="691"/>
-    <cfRule type="duplicateValues" dxfId="269" priority="692"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="693"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="694"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="695"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="696"/>
-    <cfRule type="duplicateValues" dxfId="264" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="694"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="696"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="697"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="695"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="688"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="689"/>
+    <cfRule type="duplicateValues" dxfId="262" priority="690"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="691"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="692"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="693"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N289">
-    <cfRule type="duplicateValues" dxfId="263" priority="183"/>
-    <cfRule type="duplicateValues" dxfId="262" priority="184"/>
-    <cfRule type="duplicateValues" dxfId="261" priority="185"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="186"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="187"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="188"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="189"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="190"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="191"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="184"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="190"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="191"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="192"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="188"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="187"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="186"/>
+    <cfRule type="duplicateValues" dxfId="251" priority="185"/>
+    <cfRule type="duplicateValues" dxfId="250" priority="189"/>
+    <cfRule type="duplicateValues" dxfId="249" priority="183"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N299">
-    <cfRule type="duplicateValues" dxfId="253" priority="569"/>
+    <cfRule type="duplicateValues" dxfId="248" priority="569"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N309">
-    <cfRule type="duplicateValues" dxfId="252" priority="941"/>
-    <cfRule type="duplicateValues" dxfId="251" priority="942"/>
-    <cfRule type="duplicateValues" dxfId="250" priority="943"/>
-    <cfRule type="duplicateValues" dxfId="249" priority="944"/>
-    <cfRule type="duplicateValues" dxfId="248" priority="945"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="946"/>
-    <cfRule type="duplicateValues" dxfId="246" priority="947"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="948"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="944"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="941"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="942"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="943"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="945"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="946"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="947"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="N310">
-    <cfRule type="duplicateValues" dxfId="244" priority="885"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="886"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="887"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="888"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="889"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="890"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="891"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="888"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="892"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="885"/>
+    <cfRule type="duplicateValues" dxfId="236" priority="887"/>
+    <cfRule type="duplicateValues" dxfId="235" priority="891"/>
+    <cfRule type="duplicateValues" dxfId="234" priority="890"/>
+    <cfRule type="duplicateValues" dxfId="233" priority="889"/>
+    <cfRule type="duplicateValues" dxfId="232" priority="886"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q6:Q10">
-    <cfRule type="duplicateValues" dxfId="236" priority="1113"/>
-    <cfRule type="duplicateValues" dxfId="235" priority="1114"/>
-    <cfRule type="duplicateValues" dxfId="234" priority="1115"/>
-    <cfRule type="duplicateValues" dxfId="233" priority="1116"/>
-    <cfRule type="duplicateValues" dxfId="232" priority="1117"/>
-    <cfRule type="duplicateValues" dxfId="231" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="1117"/>
     <cfRule type="duplicateValues" dxfId="230" priority="1119"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="1115"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="1113"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="1118"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="1116"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="1114"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q15">
-    <cfRule type="duplicateValues" dxfId="229" priority="852"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="853"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="854"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="855"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="856"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="859"/>
     <cfRule type="duplicateValues" dxfId="223" priority="858"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="859"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="857"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="856"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="854"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="853"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="852"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="855"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q21">
-    <cfRule type="duplicateValues" dxfId="221" priority="641"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="642"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="643"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="644"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="645"/>
-    <cfRule type="duplicateValues" dxfId="216" priority="646"/>
-    <cfRule type="duplicateValues" dxfId="215" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="216" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="215" priority="649"/>
     <cfRule type="duplicateValues" dxfId="214" priority="648"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="649"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="650"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="647"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="646"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="645"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="643"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="644"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="641"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="642"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q30">
-    <cfRule type="duplicateValues" dxfId="211" priority="1151"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="1152"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="1153"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="1154"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="1155"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="1156"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="1152"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="1151"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="1154"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="1155"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="1153"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="1157"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="1156"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q95">
-    <cfRule type="duplicateValues" dxfId="204" priority="1180"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="1181"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="1182"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="1181"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="1183"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="1182"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="1180"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q97">
-    <cfRule type="duplicateValues" dxfId="200" priority="961"/>
-    <cfRule type="duplicateValues" dxfId="199" priority="962"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="963"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="964"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="965"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="966"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="962"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="961"/>
     <cfRule type="duplicateValues" dxfId="193" priority="968"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="967"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="966"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="965"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="964"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="963"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q108:Q109">
-    <cfRule type="duplicateValues" dxfId="192" priority="718"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="719"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="720"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="721"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="722"/>
     <cfRule type="duplicateValues" dxfId="187" priority="723"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="724"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="725"/>
-    <cfRule type="duplicateValues" dxfId="184" priority="726"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="721"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="720"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="719"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="718"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="725"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="722"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="727"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="726"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="724"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q135">
-    <cfRule type="duplicateValues" dxfId="182" priority="570"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="571"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="572"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="573"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="574"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="575"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="576"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="577"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="578"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="579"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="576"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="573"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="578"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="579"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="577"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="572"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="574"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="580"/>
+    <cfRule type="duplicateValues" dxfId="169" priority="575"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="570"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="571"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q160">
-    <cfRule type="duplicateValues" dxfId="171" priority="780"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="781"/>
-    <cfRule type="duplicateValues" dxfId="169" priority="782"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="783"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="784"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="785"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="786"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="787"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="788"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="781"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="780"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="782"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="789"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="788"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="787"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="786"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="785"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="784"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="783"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q176:Q177">
-    <cfRule type="duplicateValues" dxfId="161" priority="1098"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="1099"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="1098"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="1099"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q180">
-    <cfRule type="duplicateValues" dxfId="159" priority="158"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="159"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="160"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="161"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="162"/>
-    <cfRule type="duplicateValues" dxfId="154" priority="163"/>
-    <cfRule type="duplicateValues" dxfId="153" priority="164"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="154" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="168"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="167"/>
     <cfRule type="duplicateValues" dxfId="151" priority="166"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="167"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="168"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="169"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="165"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="164"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="159"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="163"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="162"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="161"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="160"/>
+    <cfRule type="duplicateValues" dxfId="143" priority="158"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q246">
-    <cfRule type="duplicateValues" dxfId="147" priority="969"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="970"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="971"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="972"/>
-    <cfRule type="duplicateValues" dxfId="143" priority="973"/>
-    <cfRule type="duplicateValues" dxfId="142" priority="974"/>
-    <cfRule type="duplicateValues" dxfId="141" priority="975"/>
-    <cfRule type="duplicateValues" dxfId="140" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="142" priority="969"/>
+    <cfRule type="duplicateValues" dxfId="141" priority="973"/>
+    <cfRule type="duplicateValues" dxfId="140" priority="974"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="975"/>
+    <cfRule type="duplicateValues" dxfId="138" priority="976"/>
+    <cfRule type="duplicateValues" dxfId="137" priority="972"/>
+    <cfRule type="duplicateValues" dxfId="136" priority="970"/>
+    <cfRule type="duplicateValues" dxfId="135" priority="971"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q266">
-    <cfRule type="duplicateValues" dxfId="139" priority="1130"/>
-    <cfRule type="duplicateValues" dxfId="138" priority="1131"/>
-    <cfRule type="duplicateValues" dxfId="137" priority="1132"/>
-    <cfRule type="duplicateValues" dxfId="136" priority="1133"/>
-    <cfRule type="duplicateValues" dxfId="135" priority="1134"/>
-    <cfRule type="duplicateValues" dxfId="134" priority="1135"/>
+    <cfRule type="duplicateValues" dxfId="134" priority="1134"/>
     <cfRule type="duplicateValues" dxfId="133" priority="1136"/>
+    <cfRule type="duplicateValues" dxfId="132" priority="1130"/>
+    <cfRule type="duplicateValues" dxfId="131" priority="1131"/>
+    <cfRule type="duplicateValues" dxfId="130" priority="1132"/>
+    <cfRule type="duplicateValues" dxfId="129" priority="1133"/>
+    <cfRule type="duplicateValues" dxfId="128" priority="1135"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="Q283:Q284">
-    <cfRule type="duplicateValues" dxfId="132" priority="377"/>
-    <cfRule type="duplicateValues" dxfId="131" priority="378"/>
-    <cfRule type="duplicateValues" dxfId="130" priority="379"/>
-    <cfRule type="duplicateValues" dxfId="129" priority="380"/>
-    <cfRule type="duplicateValues" dxfId="128" priority="381"/>
-    <cfRule type="duplicateValues" dxfId="127" priority="382"/>
-    <cfRule type="duplicateValues" dxfId="126" priority="383"/>
-    <cfRule type="duplicateValues" dxfId="125" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="127" priority="378"/>
+    <cfRule type="duplicateValues" dxfId="126" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="125" priority="387"/>
     <cfRule type="duplicateValues" dxfId="124" priority="385"/>
-    <cfRule type="duplicateValues" dxfId="123" priority="386"/>
-    <cfRule type="duplicateValues" dxfId="122" priority="387"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="388"/>
+    <cfRule type="duplicateValues" dxfId="123" priority="384"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="383"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="382"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="377"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="386"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="380"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="381"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="379"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T20">
-    <cfRule type="duplicateValues" dxfId="120" priority="678"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="679"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="680"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="681"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="682"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="683"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="684"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="685"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="686"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="686"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="685"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="687"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="684"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="678"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="683"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="682"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="681"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="680"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="679"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T21">
-    <cfRule type="duplicateValues" dxfId="110" priority="485"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="486"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="487"/>
-    <cfRule type="duplicateValues" dxfId="107" priority="488"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="489"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="490"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="491"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="492"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="493"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="491"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="490"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="494"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="485"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="486"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="493"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="492"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="487"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="488"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="489"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T24">
-    <cfRule type="duplicateValues" dxfId="100" priority="631"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="632"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="633"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="634"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="635"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="636"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="637"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="638"/>
-    <cfRule type="duplicateValues" dxfId="92" priority="639"/>
-    <cfRule type="duplicateValues" dxfId="91" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="635"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="631"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="632"/>
+    <cfRule type="duplicateValues" dxfId="92" priority="636"/>
+    <cfRule type="duplicateValues" dxfId="91" priority="637"/>
+    <cfRule type="duplicateValues" dxfId="90" priority="638"/>
+    <cfRule type="duplicateValues" dxfId="89" priority="633"/>
+    <cfRule type="duplicateValues" dxfId="88" priority="639"/>
+    <cfRule type="duplicateValues" dxfId="87" priority="640"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="634"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T176:T177">
-    <cfRule type="duplicateValues" dxfId="90" priority="127"/>
-    <cfRule type="duplicateValues" dxfId="89" priority="128"/>
-    <cfRule type="duplicateValues" dxfId="88" priority="129"/>
-    <cfRule type="duplicateValues" dxfId="87" priority="130"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="131"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="132"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="128"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="127"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="130"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="133"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="132"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="131"/>
+    <cfRule type="duplicateValues" dxfId="79" priority="129"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T180">
-    <cfRule type="duplicateValues" dxfId="83" priority="146"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="147"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="148"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="149"/>
-    <cfRule type="duplicateValues" dxfId="79" priority="150"/>
     <cfRule type="duplicateValues" dxfId="78" priority="151"/>
-    <cfRule type="duplicateValues" dxfId="77" priority="152"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="153"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="154"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="155"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="156"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="77" priority="149"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="155"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="157"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="156"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="154"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="153"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="152"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="147"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="146"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="150"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="148"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="T213">
-    <cfRule type="duplicateValues" dxfId="71" priority="413"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="414"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="415"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="416"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="417"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="418"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="419"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="420"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="421"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="418"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="419"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="420"/>
     <cfRule type="duplicateValues" dxfId="62" priority="422"/>
     <cfRule type="duplicateValues" dxfId="61" priority="423"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="424"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="413"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="414"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="415"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="416"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="417"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="421"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W20">
-    <cfRule type="duplicateValues" dxfId="59" priority="474"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="475"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="476"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="477"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="478"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="479"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="480"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="481"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="482"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="483"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="474"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="475"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="476"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="484"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="478"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="480"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="479"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="477"/>
+    <cfRule type="duplicateValues" dxfId="46" priority="482"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="481"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="483"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W70">
-    <cfRule type="duplicateValues" dxfId="48" priority="389"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="390"/>
-    <cfRule type="duplicateValues" dxfId="46" priority="391"/>
-    <cfRule type="duplicateValues" dxfId="45" priority="392"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="393"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="394"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="395"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="396"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="397"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="398"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="399"/>
-    <cfRule type="duplicateValues" dxfId="37" priority="400"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="389"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="393"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="392"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="391"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="390"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="397"/>
+    <cfRule type="duplicateValues" dxfId="37" priority="395"/>
+    <cfRule type="duplicateValues" dxfId="36" priority="394"/>
+    <cfRule type="duplicateValues" dxfId="35" priority="396"/>
+    <cfRule type="duplicateValues" dxfId="34" priority="398"/>
+    <cfRule type="duplicateValues" dxfId="33" priority="399"/>
+    <cfRule type="duplicateValues" dxfId="32" priority="400"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W142:W143">
-    <cfRule type="duplicateValues" dxfId="36" priority="582"/>
-    <cfRule type="duplicateValues" dxfId="35" priority="583"/>
-    <cfRule type="duplicateValues" dxfId="34" priority="584"/>
-    <cfRule type="duplicateValues" dxfId="33" priority="585"/>
-    <cfRule type="duplicateValues" dxfId="32" priority="586"/>
-    <cfRule type="duplicateValues" dxfId="31" priority="587"/>
-    <cfRule type="duplicateValues" dxfId="30" priority="588"/>
-    <cfRule type="duplicateValues" dxfId="29" priority="589"/>
-    <cfRule type="duplicateValues" dxfId="28" priority="590"/>
-    <cfRule type="duplicateValues" dxfId="27" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="31" priority="584"/>
+    <cfRule type="duplicateValues" dxfId="30" priority="582"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="583"/>
+    <cfRule type="duplicateValues" dxfId="28" priority="586"/>
+    <cfRule type="duplicateValues" dxfId="27" priority="587"/>
+    <cfRule type="duplicateValues" dxfId="26" priority="589"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="590"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="591"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="588"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="585"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W180">
-    <cfRule type="duplicateValues" dxfId="26" priority="134"/>
-    <cfRule type="duplicateValues" dxfId="25" priority="135"/>
-    <cfRule type="duplicateValues" dxfId="24" priority="136"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="137"/>
-    <cfRule type="duplicateValues" dxfId="22" priority="138"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="139"/>
-    <cfRule type="duplicateValues" dxfId="20" priority="140"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="141"/>
-    <cfRule type="duplicateValues" dxfId="18" priority="142"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="143"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="136"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="138"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="139"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="140"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="141"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="137"/>
     <cfRule type="duplicateValues" dxfId="15" priority="145"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="144"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="134"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="143"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="135"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="142"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="W317">
-    <cfRule type="duplicateValues" dxfId="14" priority="592"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="593"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="594"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="595"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="596"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="597"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="598"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="599"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="600"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="601"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C7">
-    <cfRule type="duplicateValues" dxfId="4" priority="5"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F7">
-    <cfRule type="duplicateValues" dxfId="3" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J8">
-    <cfRule type="duplicateValues" dxfId="2" priority="3"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J9">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J10">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="592"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="601"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="600"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="593"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="594"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="595"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="596"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="597"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="598"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="599"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
